--- a/Selenium_Testing_Report.xlsx
+++ b/Selenium_Testing_Report.xlsx
@@ -482,7 +482,7 @@
         <v>High</v>
       </c>
       <c r="E2" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F2" t="str">
         <v>Verify page loads</v>
@@ -506,16 +506,16 @@
         <v>Verify page loads on Dashboard completes successfully without errors</v>
       </c>
       <c r="L2">
-        <v>563</v>
+        <v>1758</v>
       </c>
       <c r="M2" t="str">
         <v>Yes</v>
       </c>
       <c r="N2" t="str">
-        <v>id</v>
+        <v>xpath</v>
       </c>
       <c r="O2" t="str">
-        <v>#dashboard_element_1</v>
+        <v>//div[@id='dashboard_1']</v>
       </c>
       <c r="P2" t="str">
         <v>Pass</v>
@@ -559,7 +559,7 @@
         <v>Click button on Inventory completes successfully without errors</v>
       </c>
       <c r="L3">
-        <v>694</v>
+        <v>2651</v>
       </c>
       <c r="M3" t="str">
         <v>Yes</v>
@@ -588,7 +588,7 @@
         <v>Low</v>
       </c>
       <c r="E4" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F4" t="str">
         <v>Enter valid input</v>
@@ -612,13 +612,13 @@
         <v>Enter valid input on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L4">
-        <v>3309</v>
+        <v>1690</v>
       </c>
       <c r="M4" t="str">
         <v>Yes</v>
       </c>
       <c r="N4" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O4" t="str">
         <v>#barcode_scanner_element_3</v>
@@ -641,7 +641,7 @@
         <v>Critical</v>
       </c>
       <c r="E5" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F5" t="str">
         <v>Enter invalid input</v>
@@ -665,16 +665,16 @@
         <v>Enter invalid input on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L5">
-        <v>2367</v>
+        <v>1101</v>
       </c>
       <c r="M5" t="str">
         <v>Yes</v>
       </c>
       <c r="N5" t="str">
-        <v>xpath</v>
+        <v>id</v>
       </c>
       <c r="O5" t="str">
-        <v>//div[@id='recipe_suggestions_4']</v>
+        <v>#recipe_suggestions_element_4</v>
       </c>
       <c r="P5" t="str">
         <v>Pass</v>
@@ -718,16 +718,16 @@
         <v>Submit form on Family Sync completes successfully without errors</v>
       </c>
       <c r="L6">
-        <v>1543</v>
+        <v>2135</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
       </c>
       <c r="N6" t="str">
-        <v>xpath</v>
+        <v>className</v>
       </c>
       <c r="O6" t="str">
-        <v>//div[@id='family_sync_5']</v>
+        <v>#family_sync_element_5</v>
       </c>
       <c r="P6" t="str">
         <v>Pass</v>
@@ -747,7 +747,7 @@
         <v>Medium</v>
       </c>
       <c r="E7" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F7" t="str">
         <v>Verify error message</v>
@@ -771,13 +771,13 @@
         <v>Verify error message on Shopping List completes successfully without errors</v>
       </c>
       <c r="L7">
-        <v>1817</v>
+        <v>1155</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
       </c>
       <c r="N7" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O7" t="str">
         <v>#shopping_list_element_6</v>
@@ -800,7 +800,7 @@
         <v>Low</v>
       </c>
       <c r="E8" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F8" t="str">
         <v>Verify success message</v>
@@ -824,13 +824,13 @@
         <v>Verify success message on User Profile completes successfully without errors</v>
       </c>
       <c r="L8">
-        <v>1817</v>
+        <v>3000</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
       </c>
       <c r="N8" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O8" t="str">
         <v>#user_profile_element_7</v>
@@ -853,7 +853,7 @@
         <v>Critical</v>
       </c>
       <c r="E9" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F9" t="str">
         <v>Verify redirect</v>
@@ -877,16 +877,16 @@
         <v>Verify redirect on Settings completes successfully without errors</v>
       </c>
       <c r="L9">
-        <v>364</v>
+        <v>2239</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
       </c>
       <c r="N9" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O9" t="str">
-        <v>//div[@id='settings_8']</v>
+        <v>#settings_element_8</v>
       </c>
       <c r="P9" t="str">
         <v>Pass</v>
@@ -930,13 +930,13 @@
         <v>Verify element visible on Notifications completes successfully without errors</v>
       </c>
       <c r="L10">
-        <v>2088</v>
+        <v>1252</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
       </c>
       <c r="N10" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O10" t="str">
         <v>#notifications_element_9</v>
@@ -959,7 +959,7 @@
         <v>Medium</v>
       </c>
       <c r="E11" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F11" t="str">
         <v>Verify element hidden</v>
@@ -983,13 +983,13 @@
         <v>Verify element hidden on Search completes successfully without errors</v>
       </c>
       <c r="L11">
-        <v>962</v>
+        <v>512</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
       </c>
       <c r="N11" t="str">
-        <v>tagName</v>
+        <v>linkText</v>
       </c>
       <c r="O11" t="str">
         <v>#search_element_10</v>
@@ -1012,7 +1012,7 @@
         <v>Low</v>
       </c>
       <c r="E12" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F12" t="str">
         <v>Verify element disabled</v>
@@ -1036,16 +1036,16 @@
         <v>Verify element disabled on Reports completes successfully without errors</v>
       </c>
       <c r="L12">
-        <v>2580</v>
+        <v>1961</v>
       </c>
       <c r="M12" t="str">
         <v>Yes</v>
       </c>
       <c r="N12" t="str">
-        <v>xpath</v>
+        <v>id</v>
       </c>
       <c r="O12" t="str">
-        <v>//div[@id='reports_11']</v>
+        <v>#reports_element_11</v>
       </c>
       <c r="P12" t="str">
         <v>Pass</v>
@@ -1089,13 +1089,13 @@
         <v>Verify element enabled on Analytics completes successfully without errors</v>
       </c>
       <c r="L13">
-        <v>322</v>
+        <v>2665</v>
       </c>
       <c r="M13" t="str">
         <v>Yes</v>
       </c>
       <c r="N13" t="str">
-        <v>className</v>
+        <v>css</v>
       </c>
       <c r="O13" t="str">
         <v>#analytics_element_12</v>
@@ -1118,7 +1118,7 @@
         <v>High</v>
       </c>
       <c r="E14" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F14" t="str">
         <v>Hover over element</v>
@@ -1142,13 +1142,13 @@
         <v>Hover over element on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L14">
-        <v>3047</v>
+        <v>641</v>
       </c>
       <c r="M14" t="str">
         <v>Yes</v>
       </c>
       <c r="N14" t="str">
-        <v>name</v>
+        <v>className</v>
       </c>
       <c r="O14" t="str">
         <v>#storage_locations_element_13</v>
@@ -1171,7 +1171,7 @@
         <v>Medium</v>
       </c>
       <c r="E15" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F15" t="str">
         <v>Click dropdown</v>
@@ -1195,16 +1195,16 @@
         <v>Click dropdown on Categories completes successfully without errors</v>
       </c>
       <c r="L15">
-        <v>2518</v>
+        <v>791</v>
       </c>
       <c r="M15" t="str">
         <v>Yes</v>
       </c>
       <c r="N15" t="str">
-        <v>xpath</v>
+        <v>className</v>
       </c>
       <c r="O15" t="str">
-        <v>//div[@id='categories_14']</v>
+        <v>#categories_element_14</v>
       </c>
       <c r="P15" t="str">
         <v>Pass</v>
@@ -1248,16 +1248,16 @@
         <v>Select option from dropdown on Export completes successfully without errors</v>
       </c>
       <c r="L16">
-        <v>2282</v>
+        <v>900</v>
       </c>
       <c r="M16" t="str">
         <v>Yes</v>
       </c>
       <c r="N16" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O16" t="str">
-        <v>//div[@id='export_15']</v>
+        <v>#export_element_15</v>
       </c>
       <c r="P16" t="str">
         <v>Pass</v>
@@ -1277,7 +1277,7 @@
         <v>Critical</v>
       </c>
       <c r="E17" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F17" t="str">
         <v>Verify dropdown options</v>
@@ -1301,16 +1301,16 @@
         <v>Verify dropdown options on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L17">
-        <v>706</v>
+        <v>3389</v>
       </c>
       <c r="M17" t="str">
         <v>Yes</v>
       </c>
       <c r="N17" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O17" t="str">
-        <v>#admin_panel_element_16</v>
+        <v>//div[@id='admin_panel_16']</v>
       </c>
       <c r="P17" t="str">
         <v>Pass</v>
@@ -1354,16 +1354,16 @@
         <v>Scroll to element on Onboarding completes successfully without errors</v>
       </c>
       <c r="L18">
-        <v>902</v>
+        <v>473</v>
       </c>
       <c r="M18" t="str">
         <v>Yes</v>
       </c>
       <c r="N18" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O18" t="str">
-        <v>//div[@id='onboarding_17']</v>
+        <v>#onboarding_element_17</v>
       </c>
       <c r="P18" t="str">
         <v>Pass</v>
@@ -1383,7 +1383,7 @@
         <v>Medium</v>
       </c>
       <c r="E19" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F19" t="str">
         <v>Take screenshot</v>
@@ -1407,7 +1407,7 @@
         <v>Take screenshot on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L19">
-        <v>3477</v>
+        <v>250</v>
       </c>
       <c r="M19" t="str">
         <v>Yes</v>
@@ -1436,7 +1436,7 @@
         <v>Low</v>
       </c>
       <c r="E20" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F20" t="str">
         <v>Verify URL</v>
@@ -1460,13 +1460,13 @@
         <v>Verify URL on Session Management completes successfully without errors</v>
       </c>
       <c r="L20">
-        <v>2178</v>
+        <v>1201</v>
       </c>
       <c r="M20" t="str">
         <v>Yes</v>
       </c>
       <c r="N20" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O20" t="str">
         <v>#session_management_element_19</v>
@@ -1489,7 +1489,7 @@
         <v>Critical</v>
       </c>
       <c r="E21" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F21" t="str">
         <v>Verify breadcrumb</v>
@@ -1513,13 +1513,13 @@
         <v>Verify breadcrumb on Authentication completes successfully without errors</v>
       </c>
       <c r="L21">
-        <v>2980</v>
+        <v>218</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
       </c>
       <c r="N21" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O21" t="str">
         <v>#authentication_element_20</v>
@@ -1542,7 +1542,7 @@
         <v>High</v>
       </c>
       <c r="E22" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F22" t="str">
         <v>Verify table data</v>
@@ -1566,13 +1566,13 @@
         <v>Verify table data on Dashboard completes successfully without errors</v>
       </c>
       <c r="L22">
-        <v>259</v>
+        <v>3396</v>
       </c>
       <c r="M22" t="str">
         <v>Yes</v>
       </c>
       <c r="N22" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O22" t="str">
         <v>#dashboard_element_21</v>
@@ -1595,7 +1595,7 @@
         <v>Medium</v>
       </c>
       <c r="E23" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F23" t="str">
         <v>Sort table column</v>
@@ -1619,13 +1619,13 @@
         <v>Sort table column on Inventory completes successfully without errors</v>
       </c>
       <c r="L23">
-        <v>2534</v>
+        <v>2660</v>
       </c>
       <c r="M23" t="str">
         <v>Yes</v>
       </c>
       <c r="N23" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O23" t="str">
         <v>#inventory_element_22</v>
@@ -1672,13 +1672,13 @@
         <v>Filter table on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L24">
-        <v>697</v>
+        <v>1975</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
       </c>
       <c r="N24" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O24" t="str">
         <v>#barcode_scanner_element_23</v>
@@ -1701,7 +1701,7 @@
         <v>Critical</v>
       </c>
       <c r="E25" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F25" t="str">
         <v>Verify pagination</v>
@@ -1725,7 +1725,7 @@
         <v>Verify pagination on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L25">
-        <v>1063</v>
+        <v>900</v>
       </c>
       <c r="M25" t="str">
         <v>Yes</v>
@@ -1754,7 +1754,7 @@
         <v>High</v>
       </c>
       <c r="E26" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F26" t="str">
         <v>Click pagination next</v>
@@ -1778,13 +1778,13 @@
         <v>Click pagination next on Family Sync completes successfully without errors</v>
       </c>
       <c r="L26">
-        <v>3640</v>
+        <v>1976</v>
       </c>
       <c r="M26" t="str">
         <v>Yes</v>
       </c>
       <c r="N26" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O26" t="str">
         <v>#family_sync_element_25</v>
@@ -1807,7 +1807,7 @@
         <v>Medium</v>
       </c>
       <c r="E27" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F27" t="str">
         <v>Click pagination prev</v>
@@ -1831,16 +1831,16 @@
         <v>Click pagination prev on Shopping List completes successfully without errors</v>
       </c>
       <c r="L27">
-        <v>3221</v>
+        <v>800</v>
       </c>
       <c r="M27" t="str">
         <v>Yes</v>
       </c>
       <c r="N27" t="str">
-        <v>className</v>
+        <v>xpath</v>
       </c>
       <c r="O27" t="str">
-        <v>#shopping_list_element_26</v>
+        <v>//div[@id='shopping_list_26']</v>
       </c>
       <c r="P27" t="str">
         <v>Pass</v>
@@ -1860,7 +1860,7 @@
         <v>Low</v>
       </c>
       <c r="E28" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F28" t="str">
         <v>Verify modal opens</v>
@@ -1884,13 +1884,13 @@
         <v>Verify modal opens on User Profile completes successfully without errors</v>
       </c>
       <c r="L28">
-        <v>1961</v>
+        <v>3247</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
       </c>
       <c r="N28" t="str">
-        <v>tagName</v>
+        <v>css</v>
       </c>
       <c r="O28" t="str">
         <v>#user_profile_element_27</v>
@@ -1913,7 +1913,7 @@
         <v>Critical</v>
       </c>
       <c r="E29" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F29" t="str">
         <v>Verify modal closes</v>
@@ -1937,13 +1937,13 @@
         <v>Verify modal closes on Settings completes successfully without errors</v>
       </c>
       <c r="L29">
-        <v>2995</v>
+        <v>1420</v>
       </c>
       <c r="M29" t="str">
         <v>Yes</v>
       </c>
       <c r="N29" t="str">
-        <v>id</v>
+        <v>linkText</v>
       </c>
       <c r="O29" t="str">
         <v>#settings_element_28</v>
@@ -1966,7 +1966,7 @@
         <v>High</v>
       </c>
       <c r="E30" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F30" t="str">
         <v>Verify toast notification</v>
@@ -1990,13 +1990,13 @@
         <v>Verify toast notification on Notifications completes successfully without errors</v>
       </c>
       <c r="L30">
-        <v>1198</v>
+        <v>477</v>
       </c>
       <c r="M30" t="str">
         <v>Yes</v>
       </c>
       <c r="N30" t="str">
-        <v>className</v>
+        <v>css</v>
       </c>
       <c r="O30" t="str">
         <v>#notifications_element_29</v>
@@ -2019,7 +2019,7 @@
         <v>Medium</v>
       </c>
       <c r="E31" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F31" t="str">
         <v>Verify alert dialog</v>
@@ -2043,7 +2043,7 @@
         <v>Verify alert dialog on Search completes successfully without errors</v>
       </c>
       <c r="L31">
-        <v>2453</v>
+        <v>2315</v>
       </c>
       <c r="M31" t="str">
         <v>Yes</v>
@@ -2072,7 +2072,7 @@
         <v>Low</v>
       </c>
       <c r="E32" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F32" t="str">
         <v>Accept alert</v>
@@ -2096,13 +2096,13 @@
         <v>Accept alert on Reports completes successfully without errors</v>
       </c>
       <c r="L32">
-        <v>621</v>
+        <v>3531</v>
       </c>
       <c r="M32" t="str">
         <v>Yes</v>
       </c>
       <c r="N32" t="str">
-        <v>css</v>
+        <v>id</v>
       </c>
       <c r="O32" t="str">
         <v>#reports_element_31</v>
@@ -2149,13 +2149,13 @@
         <v>Dismiss alert on Analytics completes successfully without errors</v>
       </c>
       <c r="L33">
-        <v>435</v>
+        <v>3205</v>
       </c>
       <c r="M33" t="str">
         <v>Yes</v>
       </c>
       <c r="N33" t="str">
-        <v>id</v>
+        <v>tagName</v>
       </c>
       <c r="O33" t="str">
         <v>#analytics_element_32</v>
@@ -2178,7 +2178,7 @@
         <v>High</v>
       </c>
       <c r="E34" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F34" t="str">
         <v>Verify placeholder text</v>
@@ -2202,13 +2202,13 @@
         <v>Verify placeholder text on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L34">
-        <v>3192</v>
+        <v>1713</v>
       </c>
       <c r="M34" t="str">
         <v>Yes</v>
       </c>
       <c r="N34" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O34" t="str">
         <v>#storage_locations_element_33</v>
@@ -2231,7 +2231,7 @@
         <v>Medium</v>
       </c>
       <c r="E35" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F35" t="str">
         <v>Clear input field</v>
@@ -2255,7 +2255,7 @@
         <v>Clear input field on Categories completes successfully without errors</v>
       </c>
       <c r="L35">
-        <v>3906</v>
+        <v>3201</v>
       </c>
       <c r="M35" t="str">
         <v>Yes</v>
@@ -2284,7 +2284,7 @@
         <v>Low</v>
       </c>
       <c r="E36" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F36" t="str">
         <v>Tab through fields</v>
@@ -2308,13 +2308,13 @@
         <v>Tab through fields on Export completes successfully without errors</v>
       </c>
       <c r="L36">
-        <v>359</v>
+        <v>2025</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
       </c>
       <c r="N36" t="str">
-        <v>name</v>
+        <v>className</v>
       </c>
       <c r="O36" t="str">
         <v>#export_element_35</v>
@@ -2337,7 +2337,7 @@
         <v>Critical</v>
       </c>
       <c r="E37" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F37" t="str">
         <v>Verify field validation</v>
@@ -2361,13 +2361,13 @@
         <v>Verify field validation on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L37">
-        <v>3264</v>
+        <v>3668</v>
       </c>
       <c r="M37" t="str">
         <v>Yes</v>
       </c>
       <c r="N37" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O37" t="str">
         <v>#admin_panel_element_36</v>
@@ -2390,7 +2390,7 @@
         <v>High</v>
       </c>
       <c r="E38" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F38" t="str">
         <v>Upload file</v>
@@ -2414,13 +2414,13 @@
         <v>Upload file on Onboarding completes successfully without errors</v>
       </c>
       <c r="L38">
-        <v>556</v>
+        <v>3976</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
       </c>
       <c r="N38" t="str">
-        <v>css</v>
+        <v>className</v>
       </c>
       <c r="O38" t="str">
         <v>#onboarding_element_37</v>
@@ -2443,7 +2443,7 @@
         <v>Medium</v>
       </c>
       <c r="E39" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F39" t="str">
         <v>Verify file upload success</v>
@@ -2467,7 +2467,7 @@
         <v>Verify file upload success on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L39">
-        <v>646</v>
+        <v>2761</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2520,7 +2520,7 @@
         <v>Download file on Session Management completes successfully without errors</v>
       </c>
       <c r="L40">
-        <v>1765</v>
+        <v>2584</v>
       </c>
       <c r="M40" t="str">
         <v>Yes</v>
@@ -2549,7 +2549,7 @@
         <v>Critical</v>
       </c>
       <c r="E41" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F41" t="str">
         <v>Verify download</v>
@@ -2573,13 +2573,13 @@
         <v>Verify download on Authentication completes successfully without errors</v>
       </c>
       <c r="L41">
-        <v>2814</v>
+        <v>3184</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
       </c>
       <c r="N41" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O41" t="str">
         <v>#authentication_element_40</v>
@@ -2602,7 +2602,7 @@
         <v>High</v>
       </c>
       <c r="E42" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F42" t="str">
         <v>Resize window to mobile</v>
@@ -2626,13 +2626,13 @@
         <v>Resize window to mobile on Dashboard completes successfully without errors</v>
       </c>
       <c r="L42">
-        <v>2300</v>
+        <v>2599</v>
       </c>
       <c r="M42" t="str">
         <v>Yes</v>
       </c>
       <c r="N42" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O42" t="str">
         <v>#dashboard_element_41</v>
@@ -2655,7 +2655,7 @@
         <v>Medium</v>
       </c>
       <c r="E43" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F43" t="str">
         <v>Resize window to tablet</v>
@@ -2679,7 +2679,7 @@
         <v>Resize window to tablet on Inventory completes successfully without errors</v>
       </c>
       <c r="L43">
-        <v>3832</v>
+        <v>2532</v>
       </c>
       <c r="M43" t="str">
         <v>Yes</v>
@@ -2708,7 +2708,7 @@
         <v>Low</v>
       </c>
       <c r="E44" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F44" t="str">
         <v>Resize window to desktop</v>
@@ -2732,13 +2732,13 @@
         <v>Resize window to desktop on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L44">
-        <v>844</v>
+        <v>2815</v>
       </c>
       <c r="M44" t="str">
         <v>Yes</v>
       </c>
       <c r="N44" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O44" t="str">
         <v>#barcode_scanner_element_43</v>
@@ -2785,16 +2785,16 @@
         <v>Verify responsive layout on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L45">
-        <v>1424</v>
+        <v>2492</v>
       </c>
       <c r="M45" t="str">
         <v>Yes</v>
       </c>
       <c r="N45" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O45" t="str">
-        <v>#recipe_suggestions_element_44</v>
+        <v>//div[@id='recipe_suggestions_44']</v>
       </c>
       <c r="P45" t="str">
         <v>Pass</v>
@@ -2838,13 +2838,13 @@
         <v>Keyboard navigation on Family Sync completes successfully without errors</v>
       </c>
       <c r="L46">
-        <v>2031</v>
+        <v>917</v>
       </c>
       <c r="M46" t="str">
         <v>Yes</v>
       </c>
       <c r="N46" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O46" t="str">
         <v>#family_sync_element_45</v>
@@ -2867,7 +2867,7 @@
         <v>Medium</v>
       </c>
       <c r="E47" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F47" t="str">
         <v>Verify focus state</v>
@@ -2891,16 +2891,16 @@
         <v>Verify focus state on Shopping List completes successfully without errors</v>
       </c>
       <c r="L47">
-        <v>2765</v>
+        <v>2471</v>
       </c>
       <c r="M47" t="str">
         <v>Yes</v>
       </c>
       <c r="N47" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O47" t="str">
-        <v>#shopping_list_element_46</v>
+        <v>//div[@id='shopping_list_46']</v>
       </c>
       <c r="P47" t="str">
         <v>Pass</v>
@@ -2920,7 +2920,7 @@
         <v>Low</v>
       </c>
       <c r="E48" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F48" t="str">
         <v>Verify hover state</v>
@@ -2944,16 +2944,16 @@
         <v>Verify hover state on User Profile completes successfully without errors</v>
       </c>
       <c r="L48">
-        <v>1328</v>
+        <v>513</v>
       </c>
       <c r="M48" t="str">
         <v>Yes</v>
       </c>
       <c r="N48" t="str">
-        <v>id</v>
+        <v>xpath</v>
       </c>
       <c r="O48" t="str">
-        <v>#user_profile_element_47</v>
+        <v>//div[@id='user_profile_47']</v>
       </c>
       <c r="P48" t="str">
         <v>Pass</v>
@@ -2973,7 +2973,7 @@
         <v>Critical</v>
       </c>
       <c r="E49" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F49" t="str">
         <v>Verify active state</v>
@@ -2997,13 +2997,13 @@
         <v>Verify active state on Settings completes successfully without errors</v>
       </c>
       <c r="L49">
-        <v>1059</v>
+        <v>1196</v>
       </c>
       <c r="M49" t="str">
         <v>Yes</v>
       </c>
       <c r="N49" t="str">
-        <v>css</v>
+        <v>id</v>
       </c>
       <c r="O49" t="str">
         <v>#settings_element_48</v>
@@ -3026,7 +3026,7 @@
         <v>High</v>
       </c>
       <c r="E50" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F50" t="str">
         <v>Verify disabled state</v>
@@ -3050,13 +3050,13 @@
         <v>Verify disabled state on Notifications completes successfully without errors</v>
       </c>
       <c r="L50">
-        <v>1422</v>
+        <v>2669</v>
       </c>
       <c r="M50" t="str">
         <v>Yes</v>
       </c>
       <c r="N50" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O50" t="str">
         <v>#notifications_element_49</v>
@@ -3079,7 +3079,7 @@
         <v>Medium</v>
       </c>
       <c r="E51" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F51" t="str">
         <v>Verify loading spinner</v>
@@ -3103,7 +3103,7 @@
         <v>Verify loading spinner on Search completes successfully without errors</v>
       </c>
       <c r="L51">
-        <v>710</v>
+        <v>3680</v>
       </c>
       <c r="M51" t="str">
         <v>Yes</v>
@@ -3132,7 +3132,7 @@
         <v>Low</v>
       </c>
       <c r="E52" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F52" t="str">
         <v>Verify skeleton loader</v>
@@ -3156,7 +3156,7 @@
         <v>Verify skeleton loader on Reports completes successfully without errors</v>
       </c>
       <c r="L52">
-        <v>3369</v>
+        <v>1687</v>
       </c>
       <c r="M52" t="str">
         <v>Yes</v>
@@ -3185,7 +3185,7 @@
         <v>Critical</v>
       </c>
       <c r="E53" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F53" t="str">
         <v>Verify empty state</v>
@@ -3209,13 +3209,13 @@
         <v>Verify empty state on Analytics completes successfully without errors</v>
       </c>
       <c r="L53">
-        <v>2130</v>
+        <v>1657</v>
       </c>
       <c r="M53" t="str">
         <v>Yes</v>
       </c>
       <c r="N53" t="str">
-        <v>id</v>
+        <v>linkText</v>
       </c>
       <c r="O53" t="str">
         <v>#analytics_element_52</v>
@@ -3238,7 +3238,7 @@
         <v>High</v>
       </c>
       <c r="E54" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F54" t="str">
         <v>Verify error state</v>
@@ -3262,13 +3262,13 @@
         <v>Verify error state on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L54">
-        <v>1694</v>
+        <v>1539</v>
       </c>
       <c r="M54" t="str">
         <v>Yes</v>
       </c>
       <c r="N54" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O54" t="str">
         <v>#storage_locations_element_53</v>
@@ -3291,7 +3291,7 @@
         <v>Medium</v>
       </c>
       <c r="E55" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F55" t="str">
         <v>Verify 404 page</v>
@@ -3315,13 +3315,13 @@
         <v>Verify 404 page on Categories completes successfully without errors</v>
       </c>
       <c r="L55">
-        <v>497</v>
+        <v>440</v>
       </c>
       <c r="M55" t="str">
         <v>Yes</v>
       </c>
       <c r="N55" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O55" t="str">
         <v>#categories_element_54</v>
@@ -3344,7 +3344,7 @@
         <v>Low</v>
       </c>
       <c r="E56" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F56" t="str">
         <v>Verify back navigation</v>
@@ -3368,7 +3368,7 @@
         <v>Verify back navigation on Export completes successfully without errors</v>
       </c>
       <c r="L56">
-        <v>2550</v>
+        <v>300</v>
       </c>
       <c r="M56" t="str">
         <v>Yes</v>
@@ -3397,7 +3397,7 @@
         <v>Critical</v>
       </c>
       <c r="E57" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F57" t="str">
         <v>Verify forward navigation</v>
@@ -3421,13 +3421,13 @@
         <v>Verify forward navigation on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L57">
-        <v>3700</v>
+        <v>1603</v>
       </c>
       <c r="M57" t="str">
         <v>Yes</v>
       </c>
       <c r="N57" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O57" t="str">
         <v>#admin_panel_element_56</v>
@@ -3450,7 +3450,7 @@
         <v>High</v>
       </c>
       <c r="E58" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F58" t="str">
         <v>Refresh page</v>
@@ -3474,13 +3474,13 @@
         <v>Refresh page on Onboarding completes successfully without errors</v>
       </c>
       <c r="L58">
-        <v>843</v>
+        <v>2694</v>
       </c>
       <c r="M58" t="str">
         <v>Yes</v>
       </c>
       <c r="N58" t="str">
-        <v>id</v>
+        <v>css</v>
       </c>
       <c r="O58" t="str">
         <v>#onboarding_element_57</v>
@@ -3503,7 +3503,7 @@
         <v>Medium</v>
       </c>
       <c r="E59" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F59" t="str">
         <v>Verify session persistence</v>
@@ -3527,13 +3527,13 @@
         <v>Verify session persistence on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L59">
-        <v>2887</v>
+        <v>2511</v>
       </c>
       <c r="M59" t="str">
         <v>Yes</v>
       </c>
       <c r="N59" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O59" t="str">
         <v>#help_&amp;_support_element_58</v>
@@ -3556,7 +3556,7 @@
         <v>Low</v>
       </c>
       <c r="E60" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F60" t="str">
         <v>Verify logout clears session</v>
@@ -3580,16 +3580,16 @@
         <v>Verify logout clears session on Session Management completes successfully without errors</v>
       </c>
       <c r="L60">
-        <v>1552</v>
+        <v>2405</v>
       </c>
       <c r="M60" t="str">
         <v>Yes</v>
       </c>
       <c r="N60" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O60" t="str">
-        <v>//div[@id='session_management_59']</v>
+        <v>#session_management_element_59</v>
       </c>
       <c r="P60" t="str">
         <v>Pass</v>
@@ -3609,7 +3609,7 @@
         <v>Critical</v>
       </c>
       <c r="E61" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F61" t="str">
         <v>Verify remember me</v>
@@ -3633,13 +3633,13 @@
         <v>Verify remember me on Authentication completes successfully without errors</v>
       </c>
       <c r="L61">
-        <v>358</v>
+        <v>1937</v>
       </c>
       <c r="M61" t="str">
         <v>Yes</v>
       </c>
       <c r="N61" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O61" t="str">
         <v>#authentication_element_60</v>
@@ -3662,7 +3662,7 @@
         <v>High</v>
       </c>
       <c r="E62" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F62" t="str">
         <v>Verify auto-logout</v>
@@ -3686,16 +3686,16 @@
         <v>Verify auto-logout on Dashboard completes successfully without errors</v>
       </c>
       <c r="L62">
-        <v>3260</v>
+        <v>2709</v>
       </c>
       <c r="M62" t="str">
         <v>Yes</v>
       </c>
       <c r="N62" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O62" t="str">
-        <v>#dashboard_element_61</v>
+        <v>//div[@id='dashboard_61']</v>
       </c>
       <c r="P62" t="str">
         <v>Pass</v>
@@ -3715,7 +3715,7 @@
         <v>Medium</v>
       </c>
       <c r="E63" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F63" t="str">
         <v>Verify concurrent session</v>
@@ -3739,16 +3739,16 @@
         <v>Verify concurrent session on Inventory completes successfully without errors</v>
       </c>
       <c r="L63">
-        <v>2928</v>
+        <v>2941</v>
       </c>
       <c r="M63" t="str">
         <v>Yes</v>
       </c>
       <c r="N63" t="str">
-        <v>xpath</v>
+        <v>className</v>
       </c>
       <c r="O63" t="str">
-        <v>//div[@id='inventory_62']</v>
+        <v>#inventory_element_62</v>
       </c>
       <c r="P63" t="str">
         <v>Pass</v>
@@ -3768,7 +3768,7 @@
         <v>Low</v>
       </c>
       <c r="E64" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F64" t="str">
         <v>Verify page title</v>
@@ -3792,13 +3792,13 @@
         <v>Verify page title on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L64">
-        <v>1576</v>
+        <v>1153</v>
       </c>
       <c r="M64" t="str">
         <v>Yes</v>
       </c>
       <c r="N64" t="str">
-        <v>className</v>
+        <v>name</v>
       </c>
       <c r="O64" t="str">
         <v>#barcode_scanner_element_63</v>
@@ -3845,13 +3845,13 @@
         <v>Verify page loads on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L65">
-        <v>2487</v>
+        <v>2776</v>
       </c>
       <c r="M65" t="str">
         <v>Yes</v>
       </c>
       <c r="N65" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O65" t="str">
         <v>#recipe_suggestions_element_64</v>
@@ -3874,7 +3874,7 @@
         <v>High</v>
       </c>
       <c r="E66" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F66" t="str">
         <v>Click button</v>
@@ -3898,7 +3898,7 @@
         <v>Click button on Family Sync completes successfully without errors</v>
       </c>
       <c r="L66">
-        <v>2883</v>
+        <v>3648</v>
       </c>
       <c r="M66" t="str">
         <v>Yes</v>
@@ -3951,16 +3951,16 @@
         <v>Enter valid input on Shopping List completes successfully without errors</v>
       </c>
       <c r="L67">
-        <v>2278</v>
+        <v>1715</v>
       </c>
       <c r="M67" t="str">
         <v>Yes</v>
       </c>
       <c r="N67" t="str">
-        <v>xpath</v>
+        <v>className</v>
       </c>
       <c r="O67" t="str">
-        <v>//div[@id='shopping_list_66']</v>
+        <v>#shopping_list_element_66</v>
       </c>
       <c r="P67" t="str">
         <v>Pass</v>
@@ -3980,7 +3980,7 @@
         <v>Low</v>
       </c>
       <c r="E68" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F68" t="str">
         <v>Enter invalid input</v>
@@ -4004,16 +4004,16 @@
         <v>Enter invalid input on User Profile completes successfully without errors</v>
       </c>
       <c r="L68">
-        <v>1208</v>
+        <v>3638</v>
       </c>
       <c r="M68" t="str">
         <v>Yes</v>
       </c>
       <c r="N68" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O68" t="str">
-        <v>#user_profile_element_67</v>
+        <v>//div[@id='user_profile_67']</v>
       </c>
       <c r="P68" t="str">
         <v>Pass</v>
@@ -4033,7 +4033,7 @@
         <v>Critical</v>
       </c>
       <c r="E69" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F69" t="str">
         <v>Submit form</v>
@@ -4057,13 +4057,13 @@
         <v>Submit form on Settings completes successfully without errors</v>
       </c>
       <c r="L69">
-        <v>3580</v>
+        <v>2999</v>
       </c>
       <c r="M69" t="str">
         <v>Yes</v>
       </c>
       <c r="N69" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O69" t="str">
         <v>#settings_element_68</v>
@@ -4086,7 +4086,7 @@
         <v>High</v>
       </c>
       <c r="E70" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F70" t="str">
         <v>Verify error message</v>
@@ -4110,16 +4110,16 @@
         <v>Verify error message on Notifications completes successfully without errors</v>
       </c>
       <c r="L70">
-        <v>638</v>
+        <v>743</v>
       </c>
       <c r="M70" t="str">
         <v>Yes</v>
       </c>
       <c r="N70" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O70" t="str">
-        <v>#notifications_element_69</v>
+        <v>//div[@id='notifications_69']</v>
       </c>
       <c r="P70" t="str">
         <v>Pass</v>
@@ -4163,13 +4163,13 @@
         <v>Verify success message on Search completes successfully without errors</v>
       </c>
       <c r="L71">
-        <v>2830</v>
+        <v>3300</v>
       </c>
       <c r="M71" t="str">
         <v>Yes</v>
       </c>
       <c r="N71" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O71" t="str">
         <v>#search_element_70</v>
@@ -4192,7 +4192,7 @@
         <v>Low</v>
       </c>
       <c r="E72" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F72" t="str">
         <v>Verify redirect</v>
@@ -4216,13 +4216,13 @@
         <v>Verify redirect on Reports completes successfully without errors</v>
       </c>
       <c r="L72">
-        <v>3061</v>
+        <v>1171</v>
       </c>
       <c r="M72" t="str">
         <v>Yes</v>
       </c>
       <c r="N72" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O72" t="str">
         <v>#reports_element_71</v>
@@ -4269,13 +4269,13 @@
         <v>Verify element visible on Analytics completes successfully without errors</v>
       </c>
       <c r="L73">
-        <v>2944</v>
+        <v>3932</v>
       </c>
       <c r="M73" t="str">
         <v>Yes</v>
       </c>
       <c r="N73" t="str">
-        <v>tagName</v>
+        <v>css</v>
       </c>
       <c r="O73" t="str">
         <v>#analytics_element_72</v>
@@ -4298,7 +4298,7 @@
         <v>High</v>
       </c>
       <c r="E74" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F74" t="str">
         <v>Verify element hidden</v>
@@ -4322,13 +4322,13 @@
         <v>Verify element hidden on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L74">
-        <v>2584</v>
+        <v>3574</v>
       </c>
       <c r="M74" t="str">
         <v>Yes</v>
       </c>
       <c r="N74" t="str">
-        <v>css</v>
+        <v>className</v>
       </c>
       <c r="O74" t="str">
         <v>#storage_locations_element_73</v>
@@ -4351,7 +4351,7 @@
         <v>Medium</v>
       </c>
       <c r="E75" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F75" t="str">
         <v>Verify element disabled</v>
@@ -4375,13 +4375,13 @@
         <v>Verify element disabled on Categories completes successfully without errors</v>
       </c>
       <c r="L75">
-        <v>1640</v>
+        <v>1927</v>
       </c>
       <c r="M75" t="str">
         <v>Yes</v>
       </c>
       <c r="N75" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O75" t="str">
         <v>#categories_element_74</v>
@@ -4428,13 +4428,13 @@
         <v>Verify element enabled on Export completes successfully without errors</v>
       </c>
       <c r="L76">
-        <v>2114</v>
+        <v>2418</v>
       </c>
       <c r="M76" t="str">
         <v>Yes</v>
       </c>
       <c r="N76" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O76" t="str">
         <v>#export_element_75</v>
@@ -4457,7 +4457,7 @@
         <v>Critical</v>
       </c>
       <c r="E77" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F77" t="str">
         <v>Hover over element</v>
@@ -4481,7 +4481,7 @@
         <v>Hover over element on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L77">
-        <v>3931</v>
+        <v>3051</v>
       </c>
       <c r="M77" t="str">
         <v>Yes</v>
@@ -4510,7 +4510,7 @@
         <v>High</v>
       </c>
       <c r="E78" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F78" t="str">
         <v>Click dropdown</v>
@@ -4534,13 +4534,13 @@
         <v>Click dropdown on Onboarding completes successfully without errors</v>
       </c>
       <c r="L78">
-        <v>891</v>
+        <v>829</v>
       </c>
       <c r="M78" t="str">
         <v>Yes</v>
       </c>
       <c r="N78" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O78" t="str">
         <v>#onboarding_element_77</v>
@@ -4587,13 +4587,13 @@
         <v>Select option from dropdown on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L79">
-        <v>3706</v>
+        <v>2008</v>
       </c>
       <c r="M79" t="str">
         <v>Yes</v>
       </c>
       <c r="N79" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O79" t="str">
         <v>#help_&amp;_support_element_78</v>
@@ -4640,13 +4640,13 @@
         <v>Verify dropdown options on Session Management completes successfully without errors</v>
       </c>
       <c r="L80">
-        <v>1846</v>
+        <v>3574</v>
       </c>
       <c r="M80" t="str">
         <v>Yes</v>
       </c>
       <c r="N80" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O80" t="str">
         <v>#session_management_element_79</v>
@@ -4669,7 +4669,7 @@
         <v>Critical</v>
       </c>
       <c r="E81" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F81" t="str">
         <v>Scroll to element</v>
@@ -4693,16 +4693,16 @@
         <v>Scroll to element on Authentication completes successfully without errors</v>
       </c>
       <c r="L81">
-        <v>2665</v>
+        <v>1388</v>
       </c>
       <c r="M81" t="str">
         <v>Yes</v>
       </c>
       <c r="N81" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O81" t="str">
-        <v>#authentication_element_80</v>
+        <v>//div[@id='authentication_80']</v>
       </c>
       <c r="P81" t="str">
         <v>Pass</v>
@@ -4722,7 +4722,7 @@
         <v>High</v>
       </c>
       <c r="E82" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F82" t="str">
         <v>Take screenshot</v>
@@ -4746,13 +4746,13 @@
         <v>Take screenshot on Dashboard completes successfully without errors</v>
       </c>
       <c r="L82">
-        <v>597</v>
+        <v>2506</v>
       </c>
       <c r="M82" t="str">
         <v>Yes</v>
       </c>
       <c r="N82" t="str">
-        <v>css</v>
+        <v>className</v>
       </c>
       <c r="O82" t="str">
         <v>#dashboard_element_81</v>
@@ -4799,13 +4799,13 @@
         <v>Verify URL on Inventory completes successfully without errors</v>
       </c>
       <c r="L83">
-        <v>2632</v>
+        <v>573</v>
       </c>
       <c r="M83" t="str">
         <v>Yes</v>
       </c>
       <c r="N83" t="str">
-        <v>id</v>
+        <v>tagName</v>
       </c>
       <c r="O83" t="str">
         <v>#inventory_element_82</v>
@@ -4828,7 +4828,7 @@
         <v>Low</v>
       </c>
       <c r="E84" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F84" t="str">
         <v>Verify breadcrumb</v>
@@ -4852,16 +4852,16 @@
         <v>Verify breadcrumb on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L84">
-        <v>409</v>
+        <v>3043</v>
       </c>
       <c r="M84" t="str">
         <v>Yes</v>
       </c>
       <c r="N84" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O84" t="str">
-        <v>#barcode_scanner_element_83</v>
+        <v>//div[@id='barcode_scanner_83']</v>
       </c>
       <c r="P84" t="str">
         <v>Pass</v>
@@ -4881,7 +4881,7 @@
         <v>Critical</v>
       </c>
       <c r="E85" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F85" t="str">
         <v>Verify table data</v>
@@ -4905,13 +4905,13 @@
         <v>Verify table data on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L85">
-        <v>3589</v>
+        <v>1569</v>
       </c>
       <c r="M85" t="str">
         <v>Yes</v>
       </c>
       <c r="N85" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O85" t="str">
         <v>#recipe_suggestions_element_84</v>
@@ -4934,7 +4934,7 @@
         <v>High</v>
       </c>
       <c r="E86" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F86" t="str">
         <v>Sort table column</v>
@@ -4958,13 +4958,13 @@
         <v>Sort table column on Family Sync completes successfully without errors</v>
       </c>
       <c r="L86">
-        <v>339</v>
+        <v>1439</v>
       </c>
       <c r="M86" t="str">
         <v>Yes</v>
       </c>
       <c r="N86" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O86" t="str">
         <v>#family_sync_element_85</v>
@@ -5011,16 +5011,16 @@
         <v>Filter table on Shopping List completes successfully without errors</v>
       </c>
       <c r="L87">
-        <v>3366</v>
+        <v>2737</v>
       </c>
       <c r="M87" t="str">
         <v>Yes</v>
       </c>
       <c r="N87" t="str">
-        <v>xpath</v>
+        <v>tagName</v>
       </c>
       <c r="O87" t="str">
-        <v>//div[@id='shopping_list_86']</v>
+        <v>#shopping_list_element_86</v>
       </c>
       <c r="P87" t="str">
         <v>Pass</v>
@@ -5040,7 +5040,7 @@
         <v>Low</v>
       </c>
       <c r="E88" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F88" t="str">
         <v>Verify pagination</v>
@@ -5064,13 +5064,13 @@
         <v>Verify pagination on User Profile completes successfully without errors</v>
       </c>
       <c r="L88">
-        <v>1309</v>
+        <v>1446</v>
       </c>
       <c r="M88" t="str">
         <v>Yes</v>
       </c>
       <c r="N88" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O88" t="str">
         <v>#user_profile_element_87</v>
@@ -5117,13 +5117,13 @@
         <v>Click pagination next on Settings completes successfully without errors</v>
       </c>
       <c r="L89">
-        <v>526</v>
+        <v>1744</v>
       </c>
       <c r="M89" t="str">
         <v>Yes</v>
       </c>
       <c r="N89" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O89" t="str">
         <v>#settings_element_88</v>
@@ -5146,7 +5146,7 @@
         <v>High</v>
       </c>
       <c r="E90" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F90" t="str">
         <v>Click pagination prev</v>
@@ -5170,16 +5170,16 @@
         <v>Click pagination prev on Notifications completes successfully without errors</v>
       </c>
       <c r="L90">
-        <v>1139</v>
+        <v>1075</v>
       </c>
       <c r="M90" t="str">
         <v>Yes</v>
       </c>
       <c r="N90" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O90" t="str">
-        <v>#notifications_element_89</v>
+        <v>//div[@id='notifications_89']</v>
       </c>
       <c r="P90" t="str">
         <v>Pass</v>
@@ -5223,13 +5223,13 @@
         <v>Verify modal opens on Search completes successfully without errors</v>
       </c>
       <c r="L91">
-        <v>3920</v>
+        <v>3086</v>
       </c>
       <c r="M91" t="str">
         <v>Yes</v>
       </c>
       <c r="N91" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O91" t="str">
         <v>#search_element_90</v>
@@ -5252,7 +5252,7 @@
         <v>Low</v>
       </c>
       <c r="E92" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F92" t="str">
         <v>Verify modal closes</v>
@@ -5276,13 +5276,13 @@
         <v>Verify modal closes on Reports completes successfully without errors</v>
       </c>
       <c r="L92">
-        <v>1722</v>
+        <v>3608</v>
       </c>
       <c r="M92" t="str">
         <v>Yes</v>
       </c>
       <c r="N92" t="str">
-        <v>linkText</v>
+        <v>id</v>
       </c>
       <c r="O92" t="str">
         <v>#reports_element_91</v>
@@ -5305,7 +5305,7 @@
         <v>Critical</v>
       </c>
       <c r="E93" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F93" t="str">
         <v>Verify toast notification</v>
@@ -5329,16 +5329,16 @@
         <v>Verify toast notification on Analytics completes successfully without errors</v>
       </c>
       <c r="L93">
-        <v>3906</v>
+        <v>3599</v>
       </c>
       <c r="M93" t="str">
         <v>Yes</v>
       </c>
       <c r="N93" t="str">
-        <v>xpath</v>
+        <v>name</v>
       </c>
       <c r="O93" t="str">
-        <v>//div[@id='analytics_92']</v>
+        <v>#analytics_element_92</v>
       </c>
       <c r="P93" t="str">
         <v>Pass</v>
@@ -5382,13 +5382,13 @@
         <v>Verify alert dialog on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L94">
-        <v>778</v>
+        <v>2711</v>
       </c>
       <c r="M94" t="str">
         <v>Yes</v>
       </c>
       <c r="N94" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O94" t="str">
         <v>#storage_locations_element_93</v>
@@ -5411,7 +5411,7 @@
         <v>Medium</v>
       </c>
       <c r="E95" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F95" t="str">
         <v>Accept alert</v>
@@ -5435,7 +5435,7 @@
         <v>Accept alert on Categories completes successfully without errors</v>
       </c>
       <c r="L95">
-        <v>1097</v>
+        <v>1046</v>
       </c>
       <c r="M95" t="str">
         <v>Yes</v>
@@ -5464,7 +5464,7 @@
         <v>Low</v>
       </c>
       <c r="E96" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F96" t="str">
         <v>Dismiss alert</v>
@@ -5488,16 +5488,16 @@
         <v>Dismiss alert on Export completes successfully without errors</v>
       </c>
       <c r="L96">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="M96" t="str">
         <v>Yes</v>
       </c>
       <c r="N96" t="str">
-        <v>xpath</v>
+        <v>id</v>
       </c>
       <c r="O96" t="str">
-        <v>//div[@id='export_95']</v>
+        <v>#export_element_95</v>
       </c>
       <c r="P96" t="str">
         <v>Pass</v>
@@ -5517,7 +5517,7 @@
         <v>Critical</v>
       </c>
       <c r="E97" t="str">
-        <v>Chrome</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F97" t="str">
         <v>Verify placeholder text</v>
@@ -5541,13 +5541,13 @@
         <v>Verify placeholder text on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L97">
-        <v>1986</v>
+        <v>3024</v>
       </c>
       <c r="M97" t="str">
         <v>Yes</v>
       </c>
       <c r="N97" t="str">
-        <v>id</v>
+        <v>css</v>
       </c>
       <c r="O97" t="str">
         <v>#admin_panel_element_96</v>
@@ -5594,13 +5594,13 @@
         <v>Clear input field on Onboarding completes successfully without errors</v>
       </c>
       <c r="L98">
-        <v>1902</v>
+        <v>568</v>
       </c>
       <c r="M98" t="str">
         <v>Yes</v>
       </c>
       <c r="N98" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O98" t="str">
         <v>#onboarding_element_97</v>
@@ -5623,7 +5623,7 @@
         <v>Medium</v>
       </c>
       <c r="E99" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F99" t="str">
         <v>Tab through fields</v>
@@ -5647,13 +5647,13 @@
         <v>Tab through fields on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L99">
-        <v>1943</v>
+        <v>1051</v>
       </c>
       <c r="M99" t="str">
         <v>Yes</v>
       </c>
       <c r="N99" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O99" t="str">
         <v>#help_&amp;_support_element_98</v>
@@ -5700,13 +5700,13 @@
         <v>Verify field validation on Session Management completes successfully without errors</v>
       </c>
       <c r="L100">
-        <v>2248</v>
+        <v>532</v>
       </c>
       <c r="M100" t="str">
         <v>Yes</v>
       </c>
       <c r="N100" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O100" t="str">
         <v>#session_management_element_99</v>
@@ -5729,7 +5729,7 @@
         <v>Critical</v>
       </c>
       <c r="E101" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F101" t="str">
         <v>Upload file</v>
@@ -5753,13 +5753,13 @@
         <v>Upload file on Authentication completes successfully without errors</v>
       </c>
       <c r="L101">
-        <v>2000</v>
+        <v>2882</v>
       </c>
       <c r="M101" t="str">
         <v>Yes</v>
       </c>
       <c r="N101" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O101" t="str">
         <v>#authentication_element_100</v>
@@ -5806,13 +5806,13 @@
         <v>Verify file upload success on Dashboard completes successfully without errors</v>
       </c>
       <c r="L102">
-        <v>3064</v>
+        <v>593</v>
       </c>
       <c r="M102" t="str">
         <v>Yes</v>
       </c>
       <c r="N102" t="str">
-        <v>linkText</v>
+        <v>id</v>
       </c>
       <c r="O102" t="str">
         <v>#dashboard_element_101</v>
@@ -5835,7 +5835,7 @@
         <v>Medium</v>
       </c>
       <c r="E103" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F103" t="str">
         <v>Download file</v>
@@ -5859,16 +5859,16 @@
         <v>Download file on Inventory completes successfully without errors</v>
       </c>
       <c r="L103">
-        <v>534</v>
+        <v>968</v>
       </c>
       <c r="M103" t="str">
         <v>Yes</v>
       </c>
       <c r="N103" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O103" t="str">
-        <v>#inventory_element_102</v>
+        <v>//div[@id='inventory_102']</v>
       </c>
       <c r="P103" t="str">
         <v>Pass</v>
@@ -5912,13 +5912,13 @@
         <v>Verify download on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L104">
-        <v>3863</v>
+        <v>1102</v>
       </c>
       <c r="M104" t="str">
         <v>Yes</v>
       </c>
       <c r="N104" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O104" t="str">
         <v>#barcode_scanner_element_103</v>
@@ -5941,7 +5941,7 @@
         <v>Critical</v>
       </c>
       <c r="E105" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F105" t="str">
         <v>Resize window to mobile</v>
@@ -5965,16 +5965,16 @@
         <v>Resize window to mobile on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L105">
-        <v>2601</v>
+        <v>3638</v>
       </c>
       <c r="M105" t="str">
         <v>Yes</v>
       </c>
       <c r="N105" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O105" t="str">
-        <v>//div[@id='recipe_suggestions_104']</v>
+        <v>#recipe_suggestions_element_104</v>
       </c>
       <c r="P105" t="str">
         <v>Pass</v>
@@ -5994,7 +5994,7 @@
         <v>High</v>
       </c>
       <c r="E106" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F106" t="str">
         <v>Resize window to tablet</v>
@@ -6018,13 +6018,13 @@
         <v>Resize window to tablet on Family Sync completes successfully without errors</v>
       </c>
       <c r="L106">
-        <v>3954</v>
+        <v>1791</v>
       </c>
       <c r="M106" t="str">
         <v>Yes</v>
       </c>
       <c r="N106" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O106" t="str">
         <v>#family_sync_element_105</v>
@@ -6047,7 +6047,7 @@
         <v>Medium</v>
       </c>
       <c r="E107" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F107" t="str">
         <v>Resize window to desktop</v>
@@ -6071,13 +6071,13 @@
         <v>Resize window to desktop on Shopping List completes successfully without errors</v>
       </c>
       <c r="L107">
-        <v>1668</v>
+        <v>3739</v>
       </c>
       <c r="M107" t="str">
         <v>Yes</v>
       </c>
       <c r="N107" t="str">
-        <v>name</v>
+        <v>className</v>
       </c>
       <c r="O107" t="str">
         <v>#shopping_list_element_106</v>
@@ -6100,7 +6100,7 @@
         <v>Low</v>
       </c>
       <c r="E108" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F108" t="str">
         <v>Verify responsive layout</v>
@@ -6124,13 +6124,13 @@
         <v>Verify responsive layout on User Profile completes successfully without errors</v>
       </c>
       <c r="L108">
-        <v>3825</v>
+        <v>2369</v>
       </c>
       <c r="M108" t="str">
         <v>Yes</v>
       </c>
       <c r="N108" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O108" t="str">
         <v>#user_profile_element_107</v>
@@ -6177,7 +6177,7 @@
         <v>Keyboard navigation on Settings completes successfully without errors</v>
       </c>
       <c r="L109">
-        <v>1886</v>
+        <v>1624</v>
       </c>
       <c r="M109" t="str">
         <v>Yes</v>
@@ -6206,7 +6206,7 @@
         <v>High</v>
       </c>
       <c r="E110" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F110" t="str">
         <v>Verify focus state</v>
@@ -6230,13 +6230,13 @@
         <v>Verify focus state on Notifications completes successfully without errors</v>
       </c>
       <c r="L110">
-        <v>2971</v>
+        <v>557</v>
       </c>
       <c r="M110" t="str">
         <v>Yes</v>
       </c>
       <c r="N110" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O110" t="str">
         <v>#notifications_element_109</v>
@@ -6259,7 +6259,7 @@
         <v>Medium</v>
       </c>
       <c r="E111" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F111" t="str">
         <v>Verify hover state</v>
@@ -6283,13 +6283,13 @@
         <v>Verify hover state on Search completes successfully without errors</v>
       </c>
       <c r="L111">
-        <v>462</v>
+        <v>2003</v>
       </c>
       <c r="M111" t="str">
         <v>Yes</v>
       </c>
       <c r="N111" t="str">
-        <v>className</v>
+        <v>id</v>
       </c>
       <c r="O111" t="str">
         <v>#search_element_110</v>
@@ -6312,7 +6312,7 @@
         <v>Low</v>
       </c>
       <c r="E112" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F112" t="str">
         <v>Verify active state</v>
@@ -6336,16 +6336,16 @@
         <v>Verify active state on Reports completes successfully without errors</v>
       </c>
       <c r="L112">
-        <v>2919</v>
+        <v>1025</v>
       </c>
       <c r="M112" t="str">
         <v>Yes</v>
       </c>
       <c r="N112" t="str">
-        <v>xpath</v>
+        <v>tagName</v>
       </c>
       <c r="O112" t="str">
-        <v>//div[@id='reports_111']</v>
+        <v>#reports_element_111</v>
       </c>
       <c r="P112" t="str">
         <v>Pass</v>
@@ -6389,16 +6389,16 @@
         <v>Verify disabled state on Analytics completes successfully without errors</v>
       </c>
       <c r="L113">
-        <v>553</v>
+        <v>3045</v>
       </c>
       <c r="M113" t="str">
         <v>Yes</v>
       </c>
       <c r="N113" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O113" t="str">
-        <v>//div[@id='analytics_112']</v>
+        <v>#analytics_element_112</v>
       </c>
       <c r="P113" t="str">
         <v>Pass</v>
@@ -6418,7 +6418,7 @@
         <v>High</v>
       </c>
       <c r="E114" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F114" t="str">
         <v>Verify loading spinner</v>
@@ -6442,16 +6442,16 @@
         <v>Verify loading spinner on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L114">
-        <v>2128</v>
+        <v>1356</v>
       </c>
       <c r="M114" t="str">
         <v>Yes</v>
       </c>
       <c r="N114" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O114" t="str">
-        <v>//div[@id='storage_locations_113']</v>
+        <v>#storage_locations_element_113</v>
       </c>
       <c r="P114" t="str">
         <v>Pass</v>
@@ -6471,7 +6471,7 @@
         <v>Medium</v>
       </c>
       <c r="E115" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F115" t="str">
         <v>Verify skeleton loader</v>
@@ -6495,16 +6495,16 @@
         <v>Verify skeleton loader on Categories completes successfully without errors</v>
       </c>
       <c r="L115">
-        <v>1182</v>
+        <v>2198</v>
       </c>
       <c r="M115" t="str">
         <v>Yes</v>
       </c>
       <c r="N115" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O115" t="str">
-        <v>#categories_element_114</v>
+        <v>//div[@id='categories_114']</v>
       </c>
       <c r="P115" t="str">
         <v>Pass</v>
@@ -6524,7 +6524,7 @@
         <v>Low</v>
       </c>
       <c r="E116" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F116" t="str">
         <v>Verify empty state</v>
@@ -6548,16 +6548,16 @@
         <v>Verify empty state on Export completes successfully without errors</v>
       </c>
       <c r="L116">
-        <v>2414</v>
+        <v>783</v>
       </c>
       <c r="M116" t="str">
         <v>Yes</v>
       </c>
       <c r="N116" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O116" t="str">
-        <v>//div[@id='export_115']</v>
+        <v>#export_element_115</v>
       </c>
       <c r="P116" t="str">
         <v>Pass</v>
@@ -6577,7 +6577,7 @@
         <v>Critical</v>
       </c>
       <c r="E117" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F117" t="str">
         <v>Verify error state</v>
@@ -6601,16 +6601,16 @@
         <v>Verify error state on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L117">
-        <v>696</v>
+        <v>2965</v>
       </c>
       <c r="M117" t="str">
         <v>Yes</v>
       </c>
       <c r="N117" t="str">
-        <v>xpath</v>
+        <v>tagName</v>
       </c>
       <c r="O117" t="str">
-        <v>//div[@id='admin_panel_116']</v>
+        <v>#admin_panel_element_116</v>
       </c>
       <c r="P117" t="str">
         <v>Pass</v>
@@ -6630,7 +6630,7 @@
         <v>High</v>
       </c>
       <c r="E118" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F118" t="str">
         <v>Verify 404 page</v>
@@ -6654,13 +6654,13 @@
         <v>Verify 404 page on Onboarding completes successfully without errors</v>
       </c>
       <c r="L118">
-        <v>3288</v>
+        <v>3445</v>
       </c>
       <c r="M118" t="str">
         <v>Yes</v>
       </c>
       <c r="N118" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O118" t="str">
         <v>#onboarding_element_117</v>
@@ -6683,7 +6683,7 @@
         <v>Medium</v>
       </c>
       <c r="E119" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F119" t="str">
         <v>Verify back navigation</v>
@@ -6707,13 +6707,13 @@
         <v>Verify back navigation on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L119">
-        <v>3577</v>
+        <v>624</v>
       </c>
       <c r="M119" t="str">
         <v>Yes</v>
       </c>
       <c r="N119" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O119" t="str">
         <v>#help_&amp;_support_element_118</v>
@@ -6736,7 +6736,7 @@
         <v>Low</v>
       </c>
       <c r="E120" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F120" t="str">
         <v>Verify forward navigation</v>
@@ -6760,16 +6760,16 @@
         <v>Verify forward navigation on Session Management completes successfully without errors</v>
       </c>
       <c r="L120">
-        <v>3836</v>
+        <v>1975</v>
       </c>
       <c r="M120" t="str">
         <v>Yes</v>
       </c>
       <c r="N120" t="str">
-        <v>linkText</v>
+        <v>xpath</v>
       </c>
       <c r="O120" t="str">
-        <v>#session_management_element_119</v>
+        <v>//div[@id='session_management_119']</v>
       </c>
       <c r="P120" t="str">
         <v>Pass</v>
@@ -6789,7 +6789,7 @@
         <v>Critical</v>
       </c>
       <c r="E121" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F121" t="str">
         <v>Refresh page</v>
@@ -6813,13 +6813,13 @@
         <v>Refresh page on Authentication completes successfully without errors</v>
       </c>
       <c r="L121">
-        <v>1822</v>
+        <v>1689</v>
       </c>
       <c r="M121" t="str">
         <v>Yes</v>
       </c>
       <c r="N121" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O121" t="str">
         <v>#authentication_element_120</v>
@@ -6866,7 +6866,7 @@
         <v>Verify session persistence on Dashboard completes successfully without errors</v>
       </c>
       <c r="L122">
-        <v>2661</v>
+        <v>3849</v>
       </c>
       <c r="M122" t="str">
         <v>Yes</v>
@@ -6919,13 +6919,13 @@
         <v>Verify logout clears session on Inventory completes successfully without errors</v>
       </c>
       <c r="L123">
-        <v>2778</v>
+        <v>3777</v>
       </c>
       <c r="M123" t="str">
         <v>Yes</v>
       </c>
       <c r="N123" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O123" t="str">
         <v>#inventory_element_122</v>
@@ -6948,7 +6948,7 @@
         <v>Low</v>
       </c>
       <c r="E124" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F124" t="str">
         <v>Verify remember me</v>
@@ -6972,13 +6972,13 @@
         <v>Verify remember me on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L124">
-        <v>1866</v>
+        <v>2506</v>
       </c>
       <c r="M124" t="str">
         <v>Yes</v>
       </c>
       <c r="N124" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O124" t="str">
         <v>#barcode_scanner_element_123</v>
@@ -7001,7 +7001,7 @@
         <v>Critical</v>
       </c>
       <c r="E125" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F125" t="str">
         <v>Verify auto-logout</v>
@@ -7025,16 +7025,16 @@
         <v>Verify auto-logout on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L125">
-        <v>2010</v>
+        <v>2287</v>
       </c>
       <c r="M125" t="str">
         <v>Yes</v>
       </c>
       <c r="N125" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O125" t="str">
-        <v>#recipe_suggestions_element_124</v>
+        <v>//div[@id='recipe_suggestions_124']</v>
       </c>
       <c r="P125" t="str">
         <v>Pass</v>
@@ -7054,7 +7054,7 @@
         <v>High</v>
       </c>
       <c r="E126" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F126" t="str">
         <v>Verify concurrent session</v>
@@ -7078,13 +7078,13 @@
         <v>Verify concurrent session on Family Sync completes successfully without errors</v>
       </c>
       <c r="L126">
-        <v>3511</v>
+        <v>400</v>
       </c>
       <c r="M126" t="str">
         <v>Yes</v>
       </c>
       <c r="N126" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O126" t="str">
         <v>#family_sync_element_125</v>
@@ -7107,7 +7107,7 @@
         <v>Medium</v>
       </c>
       <c r="E127" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F127" t="str">
         <v>Verify page title</v>
@@ -7131,13 +7131,13 @@
         <v>Verify page title on Shopping List completes successfully without errors</v>
       </c>
       <c r="L127">
-        <v>2569</v>
+        <v>2037</v>
       </c>
       <c r="M127" t="str">
         <v>Yes</v>
       </c>
       <c r="N127" t="str">
-        <v>css</v>
+        <v>className</v>
       </c>
       <c r="O127" t="str">
         <v>#shopping_list_element_126</v>
@@ -7160,7 +7160,7 @@
         <v>Low</v>
       </c>
       <c r="E128" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F128" t="str">
         <v>Verify page loads</v>
@@ -7184,16 +7184,16 @@
         <v>Verify page loads on User Profile completes successfully without errors</v>
       </c>
       <c r="L128">
-        <v>2773</v>
+        <v>2119</v>
       </c>
       <c r="M128" t="str">
         <v>Yes</v>
       </c>
       <c r="N128" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O128" t="str">
-        <v>#user_profile_element_127</v>
+        <v>//div[@id='user_profile_127']</v>
       </c>
       <c r="P128" t="str">
         <v>Pass</v>
@@ -7237,16 +7237,16 @@
         <v>Click button on Settings completes successfully without errors</v>
       </c>
       <c r="L129">
-        <v>3504</v>
+        <v>1369</v>
       </c>
       <c r="M129" t="str">
         <v>Yes</v>
       </c>
       <c r="N129" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O129" t="str">
-        <v>//div[@id='settings_128']</v>
+        <v>#settings_element_128</v>
       </c>
       <c r="P129" t="str">
         <v>Pass</v>
@@ -7266,7 +7266,7 @@
         <v>High</v>
       </c>
       <c r="E130" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F130" t="str">
         <v>Enter valid input</v>
@@ -7290,13 +7290,13 @@
         <v>Enter valid input on Notifications completes successfully without errors</v>
       </c>
       <c r="L130">
-        <v>2379</v>
+        <v>601</v>
       </c>
       <c r="M130" t="str">
         <v>Yes</v>
       </c>
       <c r="N130" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O130" t="str">
         <v>#notifications_element_129</v>
@@ -7319,7 +7319,7 @@
         <v>Medium</v>
       </c>
       <c r="E131" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F131" t="str">
         <v>Enter invalid input</v>
@@ -7343,13 +7343,13 @@
         <v>Enter invalid input on Search completes successfully without errors</v>
       </c>
       <c r="L131">
-        <v>3345</v>
+        <v>1389</v>
       </c>
       <c r="M131" t="str">
         <v>Yes</v>
       </c>
       <c r="N131" t="str">
-        <v>linkText</v>
+        <v>id</v>
       </c>
       <c r="O131" t="str">
         <v>#search_element_130</v>
@@ -7372,7 +7372,7 @@
         <v>Low</v>
       </c>
       <c r="E132" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F132" t="str">
         <v>Submit form</v>
@@ -7396,7 +7396,7 @@
         <v>Submit form on Reports completes successfully without errors</v>
       </c>
       <c r="L132">
-        <v>407</v>
+        <v>3722</v>
       </c>
       <c r="M132" t="str">
         <v>Yes</v>
@@ -7425,7 +7425,7 @@
         <v>Critical</v>
       </c>
       <c r="E133" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F133" t="str">
         <v>Verify error message</v>
@@ -7449,16 +7449,16 @@
         <v>Verify error message on Analytics completes successfully without errors</v>
       </c>
       <c r="L133">
-        <v>405</v>
+        <v>3896</v>
       </c>
       <c r="M133" t="str">
         <v>Yes</v>
       </c>
       <c r="N133" t="str">
-        <v>xpath</v>
+        <v>id</v>
       </c>
       <c r="O133" t="str">
-        <v>//div[@id='analytics_132']</v>
+        <v>#analytics_element_132</v>
       </c>
       <c r="P133" t="str">
         <v>Pass</v>
@@ -7478,7 +7478,7 @@
         <v>High</v>
       </c>
       <c r="E134" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F134" t="str">
         <v>Verify success message</v>
@@ -7502,13 +7502,13 @@
         <v>Verify success message on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L134">
-        <v>2862</v>
+        <v>944</v>
       </c>
       <c r="M134" t="str">
         <v>Yes</v>
       </c>
       <c r="N134" t="str">
-        <v>tagName</v>
+        <v>linkText</v>
       </c>
       <c r="O134" t="str">
         <v>#storage_locations_element_133</v>
@@ -7555,13 +7555,13 @@
         <v>Verify redirect on Categories completes successfully without errors</v>
       </c>
       <c r="L135">
-        <v>2930</v>
+        <v>1334</v>
       </c>
       <c r="M135" t="str">
         <v>Yes</v>
       </c>
       <c r="N135" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O135" t="str">
         <v>#categories_element_134</v>
@@ -7584,7 +7584,7 @@
         <v>Low</v>
       </c>
       <c r="E136" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F136" t="str">
         <v>Verify element visible</v>
@@ -7608,13 +7608,13 @@
         <v>Verify element visible on Export completes successfully without errors</v>
       </c>
       <c r="L136">
-        <v>1442</v>
+        <v>240</v>
       </c>
       <c r="M136" t="str">
         <v>Yes</v>
       </c>
       <c r="N136" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O136" t="str">
         <v>#export_element_135</v>
@@ -7661,13 +7661,13 @@
         <v>Verify element hidden on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L137">
-        <v>1761</v>
+        <v>1905</v>
       </c>
       <c r="M137" t="str">
         <v>Yes</v>
       </c>
       <c r="N137" t="str">
-        <v>className</v>
+        <v>name</v>
       </c>
       <c r="O137" t="str">
         <v>#admin_panel_element_136</v>
@@ -7714,13 +7714,13 @@
         <v>Verify element disabled on Onboarding completes successfully without errors</v>
       </c>
       <c r="L138">
-        <v>2895</v>
+        <v>3693</v>
       </c>
       <c r="M138" t="str">
         <v>Yes</v>
       </c>
       <c r="N138" t="str">
-        <v>className</v>
+        <v>css</v>
       </c>
       <c r="O138" t="str">
         <v>#onboarding_element_137</v>
@@ -7743,7 +7743,7 @@
         <v>Medium</v>
       </c>
       <c r="E139" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F139" t="str">
         <v>Verify element enabled</v>
@@ -7767,13 +7767,13 @@
         <v>Verify element enabled on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L139">
-        <v>993</v>
+        <v>2695</v>
       </c>
       <c r="M139" t="str">
         <v>Yes</v>
       </c>
       <c r="N139" t="str">
-        <v>tagName</v>
+        <v>className</v>
       </c>
       <c r="O139" t="str">
         <v>#help_&amp;_support_element_138</v>
@@ -7820,16 +7820,16 @@
         <v>Hover over element on Session Management completes successfully without errors</v>
       </c>
       <c r="L140">
-        <v>1016</v>
+        <v>2338</v>
       </c>
       <c r="M140" t="str">
         <v>Yes</v>
       </c>
       <c r="N140" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O140" t="str">
-        <v>//div[@id='session_management_139']</v>
+        <v>#session_management_element_139</v>
       </c>
       <c r="P140" t="str">
         <v>Pass</v>
@@ -7849,7 +7849,7 @@
         <v>Critical</v>
       </c>
       <c r="E141" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F141" t="str">
         <v>Click dropdown</v>
@@ -7873,13 +7873,13 @@
         <v>Click dropdown on Authentication completes successfully without errors</v>
       </c>
       <c r="L141">
-        <v>1286</v>
+        <v>1728</v>
       </c>
       <c r="M141" t="str">
         <v>Yes</v>
       </c>
       <c r="N141" t="str">
-        <v>name</v>
+        <v>id</v>
       </c>
       <c r="O141" t="str">
         <v>#authentication_element_140</v>
@@ -7902,7 +7902,7 @@
         <v>High</v>
       </c>
       <c r="E142" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F142" t="str">
         <v>Select option from dropdown</v>
@@ -7926,13 +7926,13 @@
         <v>Select option from dropdown on Dashboard completes successfully without errors</v>
       </c>
       <c r="L142">
-        <v>3284</v>
+        <v>2926</v>
       </c>
       <c r="M142" t="str">
         <v>Yes</v>
       </c>
       <c r="N142" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O142" t="str">
         <v>#dashboard_element_141</v>
@@ -7979,13 +7979,13 @@
         <v>Verify dropdown options on Inventory completes successfully without errors</v>
       </c>
       <c r="L143">
-        <v>2659</v>
+        <v>473</v>
       </c>
       <c r="M143" t="str">
         <v>Yes</v>
       </c>
       <c r="N143" t="str">
-        <v>className</v>
+        <v>name</v>
       </c>
       <c r="O143" t="str">
         <v>#inventory_element_142</v>
@@ -8008,7 +8008,7 @@
         <v>Low</v>
       </c>
       <c r="E144" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F144" t="str">
         <v>Scroll to element</v>
@@ -8032,13 +8032,13 @@
         <v>Scroll to element on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L144">
-        <v>3157</v>
+        <v>2176</v>
       </c>
       <c r="M144" t="str">
         <v>Yes</v>
       </c>
       <c r="N144" t="str">
-        <v>css</v>
+        <v>className</v>
       </c>
       <c r="O144" t="str">
         <v>#barcode_scanner_element_143</v>
@@ -8061,7 +8061,7 @@
         <v>Critical</v>
       </c>
       <c r="E145" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F145" t="str">
         <v>Take screenshot</v>
@@ -8085,13 +8085,13 @@
         <v>Take screenshot on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L145">
-        <v>3285</v>
+        <v>3590</v>
       </c>
       <c r="M145" t="str">
         <v>Yes</v>
       </c>
       <c r="N145" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O145" t="str">
         <v>#recipe_suggestions_element_144</v>
@@ -8114,7 +8114,7 @@
         <v>High</v>
       </c>
       <c r="E146" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F146" t="str">
         <v>Verify URL</v>
@@ -8138,13 +8138,13 @@
         <v>Verify URL on Family Sync completes successfully without errors</v>
       </c>
       <c r="L146">
-        <v>449</v>
+        <v>547</v>
       </c>
       <c r="M146" t="str">
         <v>Yes</v>
       </c>
       <c r="N146" t="str">
-        <v>className</v>
+        <v>tagName</v>
       </c>
       <c r="O146" t="str">
         <v>#family_sync_element_145</v>
@@ -8167,7 +8167,7 @@
         <v>Medium</v>
       </c>
       <c r="E147" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F147" t="str">
         <v>Verify breadcrumb</v>
@@ -8191,7 +8191,7 @@
         <v>Verify breadcrumb on Shopping List completes successfully without errors</v>
       </c>
       <c r="L147">
-        <v>828</v>
+        <v>1166</v>
       </c>
       <c r="M147" t="str">
         <v>Yes</v>
@@ -8244,7 +8244,7 @@
         <v>Verify table data on User Profile completes successfully without errors</v>
       </c>
       <c r="L148">
-        <v>2710</v>
+        <v>1498</v>
       </c>
       <c r="M148" t="str">
         <v>Yes</v>
@@ -8273,7 +8273,7 @@
         <v>Critical</v>
       </c>
       <c r="E149" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F149" t="str">
         <v>Sort table column</v>
@@ -8297,16 +8297,16 @@
         <v>Sort table column on Settings completes successfully without errors</v>
       </c>
       <c r="L149">
-        <v>3708</v>
+        <v>464</v>
       </c>
       <c r="M149" t="str">
         <v>Yes</v>
       </c>
       <c r="N149" t="str">
-        <v>className</v>
+        <v>xpath</v>
       </c>
       <c r="O149" t="str">
-        <v>#settings_element_148</v>
+        <v>//div[@id='settings_148']</v>
       </c>
       <c r="P149" t="str">
         <v>Pass</v>
@@ -8350,7 +8350,7 @@
         <v>Filter table on Notifications completes successfully without errors</v>
       </c>
       <c r="L150">
-        <v>2808</v>
+        <v>2667</v>
       </c>
       <c r="M150" t="str">
         <v>Yes</v>
@@ -8379,7 +8379,7 @@
         <v>Medium</v>
       </c>
       <c r="E151" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F151" t="str">
         <v>Verify pagination</v>
@@ -8403,13 +8403,13 @@
         <v>Verify pagination on Search completes successfully without errors</v>
       </c>
       <c r="L151">
-        <v>3808</v>
+        <v>3777</v>
       </c>
       <c r="M151" t="str">
         <v>Yes</v>
       </c>
       <c r="N151" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O151" t="str">
         <v>#search_element_150</v>
@@ -8456,13 +8456,13 @@
         <v>Click pagination next on Reports completes successfully without errors</v>
       </c>
       <c r="L152">
-        <v>3954</v>
+        <v>742</v>
       </c>
       <c r="M152" t="str">
         <v>Yes</v>
       </c>
       <c r="N152" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O152" t="str">
         <v>#reports_element_151</v>
@@ -8485,7 +8485,7 @@
         <v>Critical</v>
       </c>
       <c r="E153" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F153" t="str">
         <v>Click pagination prev</v>
@@ -8509,16 +8509,16 @@
         <v>Click pagination prev on Analytics completes successfully without errors</v>
       </c>
       <c r="L153">
-        <v>3665</v>
+        <v>3550</v>
       </c>
       <c r="M153" t="str">
         <v>Yes</v>
       </c>
       <c r="N153" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O153" t="str">
-        <v>//div[@id='analytics_152']</v>
+        <v>#analytics_element_152</v>
       </c>
       <c r="P153" t="str">
         <v>Pass</v>
@@ -8538,7 +8538,7 @@
         <v>High</v>
       </c>
       <c r="E154" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F154" t="str">
         <v>Verify modal opens</v>
@@ -8562,16 +8562,16 @@
         <v>Verify modal opens on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L154">
-        <v>2927</v>
+        <v>2134</v>
       </c>
       <c r="M154" t="str">
         <v>Yes</v>
       </c>
       <c r="N154" t="str">
-        <v>linkText</v>
+        <v>xpath</v>
       </c>
       <c r="O154" t="str">
-        <v>#storage_locations_element_153</v>
+        <v>//div[@id='storage_locations_153']</v>
       </c>
       <c r="P154" t="str">
         <v>Pass</v>
@@ -8591,7 +8591,7 @@
         <v>Medium</v>
       </c>
       <c r="E155" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F155" t="str">
         <v>Verify modal closes</v>
@@ -8615,13 +8615,13 @@
         <v>Verify modal closes on Categories completes successfully without errors</v>
       </c>
       <c r="L155">
-        <v>2902</v>
+        <v>1723</v>
       </c>
       <c r="M155" t="str">
         <v>Yes</v>
       </c>
       <c r="N155" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O155" t="str">
         <v>#categories_element_154</v>
@@ -8644,7 +8644,7 @@
         <v>Low</v>
       </c>
       <c r="E156" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F156" t="str">
         <v>Verify toast notification</v>
@@ -8668,16 +8668,16 @@
         <v>Verify toast notification on Export completes successfully without errors</v>
       </c>
       <c r="L156">
-        <v>1272</v>
+        <v>777</v>
       </c>
       <c r="M156" t="str">
         <v>Yes</v>
       </c>
       <c r="N156" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O156" t="str">
-        <v>#export_element_155</v>
+        <v>//div[@id='export_155']</v>
       </c>
       <c r="P156" t="str">
         <v>Pass</v>
@@ -8697,7 +8697,7 @@
         <v>Critical</v>
       </c>
       <c r="E157" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F157" t="str">
         <v>Verify alert dialog</v>
@@ -8721,13 +8721,13 @@
         <v>Verify alert dialog on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L157">
-        <v>2111</v>
+        <v>2988</v>
       </c>
       <c r="M157" t="str">
         <v>Yes</v>
       </c>
       <c r="N157" t="str">
-        <v>className</v>
+        <v>name</v>
       </c>
       <c r="O157" t="str">
         <v>#admin_panel_element_156</v>
@@ -8750,7 +8750,7 @@
         <v>High</v>
       </c>
       <c r="E158" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F158" t="str">
         <v>Accept alert</v>
@@ -8774,13 +8774,13 @@
         <v>Accept alert on Onboarding completes successfully without errors</v>
       </c>
       <c r="L158">
-        <v>341</v>
+        <v>1861</v>
       </c>
       <c r="M158" t="str">
         <v>Yes</v>
       </c>
       <c r="N158" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O158" t="str">
         <v>#onboarding_element_157</v>
@@ -8827,7 +8827,7 @@
         <v>Dismiss alert on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L159">
-        <v>1421</v>
+        <v>3299</v>
       </c>
       <c r="M159" t="str">
         <v>Yes</v>
@@ -8880,13 +8880,13 @@
         <v>Verify placeholder text on Session Management completes successfully without errors</v>
       </c>
       <c r="L160">
-        <v>2020</v>
+        <v>2791</v>
       </c>
       <c r="M160" t="str">
         <v>Yes</v>
       </c>
       <c r="N160" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O160" t="str">
         <v>#session_management_element_159</v>
@@ -8909,7 +8909,7 @@
         <v>Critical</v>
       </c>
       <c r="E161" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F161" t="str">
         <v>Clear input field</v>
@@ -8933,13 +8933,13 @@
         <v>Clear input field on Authentication completes successfully without errors</v>
       </c>
       <c r="L161">
-        <v>3144</v>
+        <v>2487</v>
       </c>
       <c r="M161" t="str">
         <v>Yes</v>
       </c>
       <c r="N161" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O161" t="str">
         <v>#authentication_element_160</v>
@@ -8962,7 +8962,7 @@
         <v>High</v>
       </c>
       <c r="E162" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F162" t="str">
         <v>Tab through fields</v>
@@ -8986,7 +8986,7 @@
         <v>Tab through fields on Dashboard completes successfully without errors</v>
       </c>
       <c r="L162">
-        <v>2593</v>
+        <v>1637</v>
       </c>
       <c r="M162" t="str">
         <v>Yes</v>
@@ -9015,7 +9015,7 @@
         <v>Medium</v>
       </c>
       <c r="E163" t="str">
-        <v>Chrome</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F163" t="str">
         <v>Verify field validation</v>
@@ -9039,13 +9039,13 @@
         <v>Verify field validation on Inventory completes successfully without errors</v>
       </c>
       <c r="L163">
-        <v>3153</v>
+        <v>309</v>
       </c>
       <c r="M163" t="str">
         <v>Yes</v>
       </c>
       <c r="N163" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O163" t="str">
         <v>#inventory_element_162</v>
@@ -9068,7 +9068,7 @@
         <v>Low</v>
       </c>
       <c r="E164" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F164" t="str">
         <v>Upload file</v>
@@ -9092,13 +9092,13 @@
         <v>Upload file on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L164">
-        <v>3810</v>
+        <v>3826</v>
       </c>
       <c r="M164" t="str">
         <v>Yes</v>
       </c>
       <c r="N164" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O164" t="str">
         <v>#barcode_scanner_element_163</v>
@@ -9121,7 +9121,7 @@
         <v>Critical</v>
       </c>
       <c r="E165" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F165" t="str">
         <v>Verify file upload success</v>
@@ -9145,7 +9145,7 @@
         <v>Verify file upload success on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L165">
-        <v>1431</v>
+        <v>1850</v>
       </c>
       <c r="M165" t="str">
         <v>Yes</v>
@@ -9174,7 +9174,7 @@
         <v>High</v>
       </c>
       <c r="E166" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F166" t="str">
         <v>Download file</v>
@@ -9198,13 +9198,13 @@
         <v>Download file on Family Sync completes successfully without errors</v>
       </c>
       <c r="L166">
-        <v>3507</v>
+        <v>2434</v>
       </c>
       <c r="M166" t="str">
         <v>Yes</v>
       </c>
       <c r="N166" t="str">
-        <v>className</v>
+        <v>css</v>
       </c>
       <c r="O166" t="str">
         <v>#family_sync_element_165</v>
@@ -9227,7 +9227,7 @@
         <v>Medium</v>
       </c>
       <c r="E167" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F167" t="str">
         <v>Verify download</v>
@@ -9251,13 +9251,13 @@
         <v>Verify download on Shopping List completes successfully without errors</v>
       </c>
       <c r="L167">
-        <v>2756</v>
+        <v>857</v>
       </c>
       <c r="M167" t="str">
         <v>Yes</v>
       </c>
       <c r="N167" t="str">
-        <v>name</v>
+        <v>id</v>
       </c>
       <c r="O167" t="str">
         <v>#shopping_list_element_166</v>
@@ -9280,7 +9280,7 @@
         <v>Low</v>
       </c>
       <c r="E168" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F168" t="str">
         <v>Resize window to mobile</v>
@@ -9304,13 +9304,13 @@
         <v>Resize window to mobile on User Profile completes successfully without errors</v>
       </c>
       <c r="L168">
-        <v>268</v>
+        <v>835</v>
       </c>
       <c r="M168" t="str">
         <v>Yes</v>
       </c>
       <c r="N168" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O168" t="str">
         <v>#user_profile_element_167</v>
@@ -9357,13 +9357,13 @@
         <v>Resize window to tablet on Settings completes successfully without errors</v>
       </c>
       <c r="L169">
-        <v>2882</v>
+        <v>1957</v>
       </c>
       <c r="M169" t="str">
         <v>Yes</v>
       </c>
       <c r="N169" t="str">
-        <v>name</v>
+        <v>id</v>
       </c>
       <c r="O169" t="str">
         <v>#settings_element_168</v>
@@ -9386,7 +9386,7 @@
         <v>High</v>
       </c>
       <c r="E170" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F170" t="str">
         <v>Resize window to desktop</v>
@@ -9410,13 +9410,13 @@
         <v>Resize window to desktop on Notifications completes successfully without errors</v>
       </c>
       <c r="L170">
-        <v>1360</v>
+        <v>1496</v>
       </c>
       <c r="M170" t="str">
         <v>Yes</v>
       </c>
       <c r="N170" t="str">
-        <v>id</v>
+        <v>css</v>
       </c>
       <c r="O170" t="str">
         <v>#notifications_element_169</v>
@@ -9463,13 +9463,13 @@
         <v>Verify responsive layout on Search completes successfully without errors</v>
       </c>
       <c r="L171">
-        <v>480</v>
+        <v>774</v>
       </c>
       <c r="M171" t="str">
         <v>Yes</v>
       </c>
       <c r="N171" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O171" t="str">
         <v>#search_element_170</v>
@@ -9492,7 +9492,7 @@
         <v>Low</v>
       </c>
       <c r="E172" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F172" t="str">
         <v>Keyboard navigation</v>
@@ -9516,13 +9516,13 @@
         <v>Keyboard navigation on Reports completes successfully without errors</v>
       </c>
       <c r="L172">
-        <v>2214</v>
+        <v>3959</v>
       </c>
       <c r="M172" t="str">
         <v>Yes</v>
       </c>
       <c r="N172" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O172" t="str">
         <v>#reports_element_171</v>
@@ -9545,7 +9545,7 @@
         <v>Critical</v>
       </c>
       <c r="E173" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F173" t="str">
         <v>Verify focus state</v>
@@ -9569,13 +9569,13 @@
         <v>Verify focus state on Analytics completes successfully without errors</v>
       </c>
       <c r="L173">
-        <v>1666</v>
+        <v>2308</v>
       </c>
       <c r="M173" t="str">
         <v>Yes</v>
       </c>
       <c r="N173" t="str">
-        <v>tagName</v>
+        <v>css</v>
       </c>
       <c r="O173" t="str">
         <v>#analytics_element_172</v>
@@ -9598,7 +9598,7 @@
         <v>High</v>
       </c>
       <c r="E174" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F174" t="str">
         <v>Verify hover state</v>
@@ -9622,16 +9622,16 @@
         <v>Verify hover state on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L174">
-        <v>2610</v>
+        <v>3993</v>
       </c>
       <c r="M174" t="str">
         <v>Yes</v>
       </c>
       <c r="N174" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O174" t="str">
-        <v>#storage_locations_element_173</v>
+        <v>//div[@id='storage_locations_173']</v>
       </c>
       <c r="P174" t="str">
         <v>Pass</v>
@@ -9651,7 +9651,7 @@
         <v>Medium</v>
       </c>
       <c r="E175" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F175" t="str">
         <v>Verify active state</v>
@@ -9675,16 +9675,16 @@
         <v>Verify active state on Categories completes successfully without errors</v>
       </c>
       <c r="L175">
-        <v>1068</v>
+        <v>3991</v>
       </c>
       <c r="M175" t="str">
         <v>Yes</v>
       </c>
       <c r="N175" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O175" t="str">
-        <v>#categories_element_174</v>
+        <v>//div[@id='categories_174']</v>
       </c>
       <c r="P175" t="str">
         <v>Pass</v>
@@ -9704,7 +9704,7 @@
         <v>Low</v>
       </c>
       <c r="E176" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F176" t="str">
         <v>Verify disabled state</v>
@@ -9728,7 +9728,7 @@
         <v>Verify disabled state on Export completes successfully without errors</v>
       </c>
       <c r="L176">
-        <v>795</v>
+        <v>646</v>
       </c>
       <c r="M176" t="str">
         <v>Yes</v>
@@ -9781,13 +9781,13 @@
         <v>Verify loading spinner on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L177">
-        <v>3869</v>
+        <v>2164</v>
       </c>
       <c r="M177" t="str">
         <v>Yes</v>
       </c>
       <c r="N177" t="str">
-        <v>id</v>
+        <v>tagName</v>
       </c>
       <c r="O177" t="str">
         <v>#admin_panel_element_176</v>
@@ -9810,7 +9810,7 @@
         <v>High</v>
       </c>
       <c r="E178" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F178" t="str">
         <v>Verify skeleton loader</v>
@@ -9834,16 +9834,16 @@
         <v>Verify skeleton loader on Onboarding completes successfully without errors</v>
       </c>
       <c r="L178">
-        <v>3515</v>
+        <v>575</v>
       </c>
       <c r="M178" t="str">
         <v>Yes</v>
       </c>
       <c r="N178" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O178" t="str">
-        <v>#onboarding_element_177</v>
+        <v>//div[@id='onboarding_177']</v>
       </c>
       <c r="P178" t="str">
         <v>Pass</v>
@@ -9863,7 +9863,7 @@
         <v>Medium</v>
       </c>
       <c r="E179" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F179" t="str">
         <v>Verify empty state</v>
@@ -9887,13 +9887,13 @@
         <v>Verify empty state on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L179">
-        <v>1298</v>
+        <v>633</v>
       </c>
       <c r="M179" t="str">
         <v>Yes</v>
       </c>
       <c r="N179" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O179" t="str">
         <v>#help_&amp;_support_element_178</v>
@@ -9916,7 +9916,7 @@
         <v>Low</v>
       </c>
       <c r="E180" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F180" t="str">
         <v>Verify error state</v>
@@ -9940,13 +9940,13 @@
         <v>Verify error state on Session Management completes successfully without errors</v>
       </c>
       <c r="L180">
-        <v>312</v>
+        <v>2075</v>
       </c>
       <c r="M180" t="str">
         <v>Yes</v>
       </c>
       <c r="N180" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O180" t="str">
         <v>#session_management_element_179</v>
@@ -9969,7 +9969,7 @@
         <v>Critical</v>
       </c>
       <c r="E181" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F181" t="str">
         <v>Verify 404 page</v>
@@ -9993,13 +9993,13 @@
         <v>Verify 404 page on Authentication completes successfully without errors</v>
       </c>
       <c r="L181">
-        <v>1707</v>
+        <v>3707</v>
       </c>
       <c r="M181" t="str">
         <v>Yes</v>
       </c>
       <c r="N181" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O181" t="str">
         <v>#authentication_element_180</v>
@@ -10022,7 +10022,7 @@
         <v>High</v>
       </c>
       <c r="E182" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F182" t="str">
         <v>Verify back navigation</v>
@@ -10046,16 +10046,16 @@
         <v>Verify back navigation on Dashboard completes successfully without errors</v>
       </c>
       <c r="L182">
-        <v>1825</v>
+        <v>2543</v>
       </c>
       <c r="M182" t="str">
         <v>Yes</v>
       </c>
       <c r="N182" t="str">
-        <v>id</v>
+        <v>xpath</v>
       </c>
       <c r="O182" t="str">
-        <v>#dashboard_element_181</v>
+        <v>//div[@id='dashboard_181']</v>
       </c>
       <c r="P182" t="str">
         <v>Pass</v>
@@ -10099,13 +10099,13 @@
         <v>Verify forward navigation on Inventory completes successfully without errors</v>
       </c>
       <c r="L183">
-        <v>3981</v>
+        <v>1534</v>
       </c>
       <c r="M183" t="str">
         <v>Yes</v>
       </c>
       <c r="N183" t="str">
-        <v>id</v>
+        <v>name</v>
       </c>
       <c r="O183" t="str">
         <v>#inventory_element_182</v>
@@ -10128,7 +10128,7 @@
         <v>Low</v>
       </c>
       <c r="E184" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F184" t="str">
         <v>Refresh page</v>
@@ -10152,7 +10152,7 @@
         <v>Refresh page on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L184">
-        <v>497</v>
+        <v>3591</v>
       </c>
       <c r="M184" t="str">
         <v>Yes</v>
@@ -10181,7 +10181,7 @@
         <v>Critical</v>
       </c>
       <c r="E185" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F185" t="str">
         <v>Verify session persistence</v>
@@ -10205,13 +10205,13 @@
         <v>Verify session persistence on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L185">
-        <v>282</v>
+        <v>2477</v>
       </c>
       <c r="M185" t="str">
         <v>Yes</v>
       </c>
       <c r="N185" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O185" t="str">
         <v>#recipe_suggestions_element_184</v>
@@ -10234,7 +10234,7 @@
         <v>High</v>
       </c>
       <c r="E186" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F186" t="str">
         <v>Verify logout clears session</v>
@@ -10258,13 +10258,13 @@
         <v>Verify logout clears session on Family Sync completes successfully without errors</v>
       </c>
       <c r="L186">
-        <v>2631</v>
+        <v>426</v>
       </c>
       <c r="M186" t="str">
         <v>Yes</v>
       </c>
       <c r="N186" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O186" t="str">
         <v>#family_sync_element_185</v>
@@ -10287,7 +10287,7 @@
         <v>Medium</v>
       </c>
       <c r="E187" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F187" t="str">
         <v>Verify remember me</v>
@@ -10311,7 +10311,7 @@
         <v>Verify remember me on Shopping List completes successfully without errors</v>
       </c>
       <c r="L187">
-        <v>638</v>
+        <v>831</v>
       </c>
       <c r="M187" t="str">
         <v>Yes</v>
@@ -10340,7 +10340,7 @@
         <v>Low</v>
       </c>
       <c r="E188" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F188" t="str">
         <v>Verify auto-logout</v>
@@ -10364,16 +10364,16 @@
         <v>Verify auto-logout on User Profile completes successfully without errors</v>
       </c>
       <c r="L188">
-        <v>2342</v>
+        <v>2069</v>
       </c>
       <c r="M188" t="str">
         <v>Yes</v>
       </c>
       <c r="N188" t="str">
-        <v>linkText</v>
+        <v>xpath</v>
       </c>
       <c r="O188" t="str">
-        <v>#user_profile_element_187</v>
+        <v>//div[@id='user_profile_187']</v>
       </c>
       <c r="P188" t="str">
         <v>Pass</v>
@@ -10393,7 +10393,7 @@
         <v>Critical</v>
       </c>
       <c r="E189" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F189" t="str">
         <v>Verify concurrent session</v>
@@ -10417,13 +10417,13 @@
         <v>Verify concurrent session on Settings completes successfully without errors</v>
       </c>
       <c r="L189">
-        <v>410</v>
+        <v>1839</v>
       </c>
       <c r="M189" t="str">
         <v>Yes</v>
       </c>
       <c r="N189" t="str">
-        <v>id</v>
+        <v>linkText</v>
       </c>
       <c r="O189" t="str">
         <v>#settings_element_188</v>
@@ -10446,7 +10446,7 @@
         <v>High</v>
       </c>
       <c r="E190" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F190" t="str">
         <v>Verify page title</v>
@@ -10470,16 +10470,16 @@
         <v>Verify page title on Notifications completes successfully without errors</v>
       </c>
       <c r="L190">
-        <v>3304</v>
+        <v>1474</v>
       </c>
       <c r="M190" t="str">
         <v>Yes</v>
       </c>
       <c r="N190" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O190" t="str">
-        <v>#notifications_element_189</v>
+        <v>//div[@id='notifications_189']</v>
       </c>
       <c r="P190" t="str">
         <v>Pass</v>
@@ -10523,13 +10523,13 @@
         <v>Verify page loads on Search completes successfully without errors</v>
       </c>
       <c r="L191">
-        <v>2821</v>
+        <v>1880</v>
       </c>
       <c r="M191" t="str">
         <v>Yes</v>
       </c>
       <c r="N191" t="str">
-        <v>id</v>
+        <v>css</v>
       </c>
       <c r="O191" t="str">
         <v>#search_element_190</v>
@@ -10552,7 +10552,7 @@
         <v>Low</v>
       </c>
       <c r="E192" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F192" t="str">
         <v>Click button</v>
@@ -10576,13 +10576,13 @@
         <v>Click button on Reports completes successfully without errors</v>
       </c>
       <c r="L192">
-        <v>3054</v>
+        <v>1097</v>
       </c>
       <c r="M192" t="str">
         <v>Yes</v>
       </c>
       <c r="N192" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O192" t="str">
         <v>#reports_element_191</v>
@@ -10605,7 +10605,7 @@
         <v>Critical</v>
       </c>
       <c r="E193" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F193" t="str">
         <v>Enter valid input</v>
@@ -10629,13 +10629,13 @@
         <v>Enter valid input on Analytics completes successfully without errors</v>
       </c>
       <c r="L193">
-        <v>1533</v>
+        <v>1680</v>
       </c>
       <c r="M193" t="str">
         <v>Yes</v>
       </c>
       <c r="N193" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O193" t="str">
         <v>#analytics_element_192</v>
@@ -10682,16 +10682,16 @@
         <v>Enter invalid input on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L194">
-        <v>981</v>
+        <v>250</v>
       </c>
       <c r="M194" t="str">
         <v>Yes</v>
       </c>
       <c r="N194" t="str">
-        <v>xpath</v>
+        <v>id</v>
       </c>
       <c r="O194" t="str">
-        <v>//div[@id='storage_locations_193']</v>
+        <v>#storage_locations_element_193</v>
       </c>
       <c r="P194" t="str">
         <v>Pass</v>
@@ -10711,7 +10711,7 @@
         <v>Medium</v>
       </c>
       <c r="E195" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F195" t="str">
         <v>Submit form</v>
@@ -10735,13 +10735,13 @@
         <v>Submit form on Categories completes successfully without errors</v>
       </c>
       <c r="L195">
-        <v>1580</v>
+        <v>3611</v>
       </c>
       <c r="M195" t="str">
         <v>Yes</v>
       </c>
       <c r="N195" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O195" t="str">
         <v>#categories_element_194</v>
@@ -10764,7 +10764,7 @@
         <v>Low</v>
       </c>
       <c r="E196" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F196" t="str">
         <v>Verify error message</v>
@@ -10788,13 +10788,13 @@
         <v>Verify error message on Export completes successfully without errors</v>
       </c>
       <c r="L196">
-        <v>3371</v>
+        <v>207</v>
       </c>
       <c r="M196" t="str">
         <v>Yes</v>
       </c>
       <c r="N196" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O196" t="str">
         <v>#export_element_195</v>
@@ -10817,7 +10817,7 @@
         <v>Critical</v>
       </c>
       <c r="E197" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F197" t="str">
         <v>Verify success message</v>
@@ -10841,13 +10841,13 @@
         <v>Verify success message on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L197">
-        <v>1256</v>
+        <v>1078</v>
       </c>
       <c r="M197" t="str">
         <v>Yes</v>
       </c>
       <c r="N197" t="str">
-        <v>tagName</v>
+        <v>className</v>
       </c>
       <c r="O197" t="str">
         <v>#admin_panel_element_196</v>
@@ -10870,7 +10870,7 @@
         <v>High</v>
       </c>
       <c r="E198" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F198" t="str">
         <v>Verify redirect</v>
@@ -10894,7 +10894,7 @@
         <v>Verify redirect on Onboarding completes successfully without errors</v>
       </c>
       <c r="L198">
-        <v>814</v>
+        <v>267</v>
       </c>
       <c r="M198" t="str">
         <v>Yes</v>
@@ -10947,13 +10947,13 @@
         <v>Verify element visible on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L199">
-        <v>2201</v>
+        <v>2795</v>
       </c>
       <c r="M199" t="str">
         <v>Yes</v>
       </c>
       <c r="N199" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O199" t="str">
         <v>#help_&amp;_support_element_198</v>
@@ -10976,7 +10976,7 @@
         <v>Low</v>
       </c>
       <c r="E200" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F200" t="str">
         <v>Verify element hidden</v>
@@ -11000,13 +11000,13 @@
         <v>Verify element hidden on Session Management completes successfully without errors</v>
       </c>
       <c r="L200">
-        <v>2105</v>
+        <v>401</v>
       </c>
       <c r="M200" t="str">
         <v>Yes</v>
       </c>
       <c r="N200" t="str">
-        <v>className</v>
+        <v>id</v>
       </c>
       <c r="O200" t="str">
         <v>#session_management_element_199</v>
@@ -11029,7 +11029,7 @@
         <v>Critical</v>
       </c>
       <c r="E201" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F201" t="str">
         <v>Verify element disabled</v>
@@ -11053,13 +11053,13 @@
         <v>Verify element disabled on Authentication completes successfully without errors</v>
       </c>
       <c r="L201">
-        <v>2054</v>
+        <v>3255</v>
       </c>
       <c r="M201" t="str">
         <v>Yes</v>
       </c>
       <c r="N201" t="str">
-        <v>id</v>
+        <v>name</v>
       </c>
       <c r="O201" t="str">
         <v>#authentication_element_200</v>
@@ -11106,13 +11106,13 @@
         <v>Verify element enabled on Dashboard completes successfully without errors</v>
       </c>
       <c r="L202">
-        <v>3384</v>
+        <v>2996</v>
       </c>
       <c r="M202" t="str">
         <v>Yes</v>
       </c>
       <c r="N202" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O202" t="str">
         <v>#dashboard_element_201</v>
@@ -11135,7 +11135,7 @@
         <v>Medium</v>
       </c>
       <c r="E203" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F203" t="str">
         <v>Hover over element</v>
@@ -11159,13 +11159,13 @@
         <v>Hover over element on Inventory completes successfully without errors</v>
       </c>
       <c r="L203">
-        <v>2982</v>
+        <v>2343</v>
       </c>
       <c r="M203" t="str">
         <v>Yes</v>
       </c>
       <c r="N203" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O203" t="str">
         <v>#inventory_element_202</v>
@@ -11188,7 +11188,7 @@
         <v>Low</v>
       </c>
       <c r="E204" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F204" t="str">
         <v>Click dropdown</v>
@@ -11212,16 +11212,16 @@
         <v>Click dropdown on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L204">
-        <v>2917</v>
+        <v>2313</v>
       </c>
       <c r="M204" t="str">
         <v>Yes</v>
       </c>
       <c r="N204" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O204" t="str">
-        <v>//div[@id='barcode_scanner_203']</v>
+        <v>#barcode_scanner_element_203</v>
       </c>
       <c r="P204" t="str">
         <v>Pass</v>
@@ -11241,7 +11241,7 @@
         <v>Critical</v>
       </c>
       <c r="E205" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F205" t="str">
         <v>Select option from dropdown</v>
@@ -11265,13 +11265,13 @@
         <v>Select option from dropdown on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L205">
-        <v>3945</v>
+        <v>3516</v>
       </c>
       <c r="M205" t="str">
         <v>Yes</v>
       </c>
       <c r="N205" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O205" t="str">
         <v>#recipe_suggestions_element_204</v>
@@ -11294,7 +11294,7 @@
         <v>High</v>
       </c>
       <c r="E206" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F206" t="str">
         <v>Verify dropdown options</v>
@@ -11318,13 +11318,13 @@
         <v>Verify dropdown options on Family Sync completes successfully without errors</v>
       </c>
       <c r="L206">
-        <v>3598</v>
+        <v>490</v>
       </c>
       <c r="M206" t="str">
         <v>Yes</v>
       </c>
       <c r="N206" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O206" t="str">
         <v>#family_sync_element_205</v>
@@ -11371,13 +11371,13 @@
         <v>Scroll to element on Shopping List completes successfully without errors</v>
       </c>
       <c r="L207">
-        <v>253</v>
+        <v>3510</v>
       </c>
       <c r="M207" t="str">
         <v>Yes</v>
       </c>
       <c r="N207" t="str">
-        <v>id</v>
+        <v>tagName</v>
       </c>
       <c r="O207" t="str">
         <v>#shopping_list_element_206</v>
@@ -11400,7 +11400,7 @@
         <v>Low</v>
       </c>
       <c r="E208" t="str">
-        <v>Chrome</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F208" t="str">
         <v>Take screenshot</v>
@@ -11424,7 +11424,7 @@
         <v>Take screenshot on User Profile completes successfully without errors</v>
       </c>
       <c r="L208">
-        <v>1863</v>
+        <v>1416</v>
       </c>
       <c r="M208" t="str">
         <v>Yes</v>
@@ -11477,13 +11477,13 @@
         <v>Verify URL on Settings completes successfully without errors</v>
       </c>
       <c r="L209">
-        <v>1099</v>
+        <v>2356</v>
       </c>
       <c r="M209" t="str">
         <v>Yes</v>
       </c>
       <c r="N209" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O209" t="str">
         <v>#settings_element_208</v>
@@ -11506,7 +11506,7 @@
         <v>High</v>
       </c>
       <c r="E210" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F210" t="str">
         <v>Verify breadcrumb</v>
@@ -11530,13 +11530,13 @@
         <v>Verify breadcrumb on Notifications completes successfully without errors</v>
       </c>
       <c r="L210">
-        <v>3554</v>
+        <v>1559</v>
       </c>
       <c r="M210" t="str">
         <v>Yes</v>
       </c>
       <c r="N210" t="str">
-        <v>name</v>
+        <v>id</v>
       </c>
       <c r="O210" t="str">
         <v>#notifications_element_209</v>
@@ -11583,13 +11583,13 @@
         <v>Verify table data on Search completes successfully without errors</v>
       </c>
       <c r="L211">
-        <v>688</v>
+        <v>3753</v>
       </c>
       <c r="M211" t="str">
         <v>Yes</v>
       </c>
       <c r="N211" t="str">
-        <v>id</v>
+        <v>tagName</v>
       </c>
       <c r="O211" t="str">
         <v>#search_element_210</v>
@@ -11612,7 +11612,7 @@
         <v>Low</v>
       </c>
       <c r="E212" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F212" t="str">
         <v>Sort table column</v>
@@ -11636,13 +11636,13 @@
         <v>Sort table column on Reports completes successfully without errors</v>
       </c>
       <c r="L212">
-        <v>1117</v>
+        <v>1595</v>
       </c>
       <c r="M212" t="str">
         <v>Yes</v>
       </c>
       <c r="N212" t="str">
-        <v>tagName</v>
+        <v>linkText</v>
       </c>
       <c r="O212" t="str">
         <v>#reports_element_211</v>
@@ -11689,13 +11689,13 @@
         <v>Filter table on Analytics completes successfully without errors</v>
       </c>
       <c r="L213">
-        <v>3695</v>
+        <v>354</v>
       </c>
       <c r="M213" t="str">
         <v>Yes</v>
       </c>
       <c r="N213" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O213" t="str">
         <v>#analytics_element_212</v>
@@ -11718,7 +11718,7 @@
         <v>High</v>
       </c>
       <c r="E214" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F214" t="str">
         <v>Verify pagination</v>
@@ -11742,13 +11742,13 @@
         <v>Verify pagination on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L214">
-        <v>2023</v>
+        <v>747</v>
       </c>
       <c r="M214" t="str">
         <v>Yes</v>
       </c>
       <c r="N214" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O214" t="str">
         <v>#storage_locations_element_213</v>
@@ -11771,7 +11771,7 @@
         <v>Medium</v>
       </c>
       <c r="E215" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F215" t="str">
         <v>Click pagination next</v>
@@ -11795,13 +11795,13 @@
         <v>Click pagination next on Categories completes successfully without errors</v>
       </c>
       <c r="L215">
-        <v>1325</v>
+        <v>3053</v>
       </c>
       <c r="M215" t="str">
         <v>Yes</v>
       </c>
       <c r="N215" t="str">
-        <v>id</v>
+        <v>name</v>
       </c>
       <c r="O215" t="str">
         <v>#categories_element_214</v>
@@ -11824,7 +11824,7 @@
         <v>Low</v>
       </c>
       <c r="E216" t="str">
-        <v>Chrome</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F216" t="str">
         <v>Click pagination prev</v>
@@ -11848,13 +11848,13 @@
         <v>Click pagination prev on Export completes successfully without errors</v>
       </c>
       <c r="L216">
-        <v>484</v>
+        <v>1204</v>
       </c>
       <c r="M216" t="str">
         <v>Yes</v>
       </c>
       <c r="N216" t="str">
-        <v>tagName</v>
+        <v>className</v>
       </c>
       <c r="O216" t="str">
         <v>#export_element_215</v>
@@ -11877,7 +11877,7 @@
         <v>Critical</v>
       </c>
       <c r="E217" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F217" t="str">
         <v>Verify modal opens</v>
@@ -11901,13 +11901,13 @@
         <v>Verify modal opens on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L217">
-        <v>3707</v>
+        <v>2414</v>
       </c>
       <c r="M217" t="str">
         <v>Yes</v>
       </c>
       <c r="N217" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O217" t="str">
         <v>#admin_panel_element_216</v>
@@ -11954,16 +11954,16 @@
         <v>Verify modal closes on Onboarding completes successfully without errors</v>
       </c>
       <c r="L218">
-        <v>2015</v>
+        <v>3319</v>
       </c>
       <c r="M218" t="str">
         <v>Yes</v>
       </c>
       <c r="N218" t="str">
-        <v>xpath</v>
+        <v>name</v>
       </c>
       <c r="O218" t="str">
-        <v>//div[@id='onboarding_217']</v>
+        <v>#onboarding_element_217</v>
       </c>
       <c r="P218" t="str">
         <v>Pass</v>
@@ -11983,7 +11983,7 @@
         <v>Medium</v>
       </c>
       <c r="E219" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F219" t="str">
         <v>Verify toast notification</v>
@@ -12007,7 +12007,7 @@
         <v>Verify toast notification on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L219">
-        <v>1465</v>
+        <v>740</v>
       </c>
       <c r="M219" t="str">
         <v>Yes</v>
@@ -12036,7 +12036,7 @@
         <v>Low</v>
       </c>
       <c r="E220" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F220" t="str">
         <v>Verify alert dialog</v>
@@ -12060,13 +12060,13 @@
         <v>Verify alert dialog on Session Management completes successfully without errors</v>
       </c>
       <c r="L220">
-        <v>1038</v>
+        <v>2716</v>
       </c>
       <c r="M220" t="str">
         <v>Yes</v>
       </c>
       <c r="N220" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O220" t="str">
         <v>#session_management_element_219</v>
@@ -12089,7 +12089,7 @@
         <v>Critical</v>
       </c>
       <c r="E221" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F221" t="str">
         <v>Accept alert</v>
@@ -12113,16 +12113,16 @@
         <v>Accept alert on Authentication completes successfully without errors</v>
       </c>
       <c r="L221">
-        <v>2911</v>
+        <v>3882</v>
       </c>
       <c r="M221" t="str">
         <v>Yes</v>
       </c>
       <c r="N221" t="str">
-        <v>xpath</v>
+        <v>id</v>
       </c>
       <c r="O221" t="str">
-        <v>//div[@id='authentication_220']</v>
+        <v>#authentication_element_220</v>
       </c>
       <c r="P221" t="str">
         <v>Pass</v>
@@ -12142,7 +12142,7 @@
         <v>High</v>
       </c>
       <c r="E222" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F222" t="str">
         <v>Dismiss alert</v>
@@ -12166,13 +12166,13 @@
         <v>Dismiss alert on Dashboard completes successfully without errors</v>
       </c>
       <c r="L222">
-        <v>1616</v>
+        <v>3980</v>
       </c>
       <c r="M222" t="str">
         <v>Yes</v>
       </c>
       <c r="N222" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O222" t="str">
         <v>#dashboard_element_221</v>
@@ -12195,7 +12195,7 @@
         <v>Medium</v>
       </c>
       <c r="E223" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F223" t="str">
         <v>Verify placeholder text</v>
@@ -12219,7 +12219,7 @@
         <v>Verify placeholder text on Inventory completes successfully without errors</v>
       </c>
       <c r="L223">
-        <v>2616</v>
+        <v>3675</v>
       </c>
       <c r="M223" t="str">
         <v>Yes</v>
@@ -12248,7 +12248,7 @@
         <v>Low</v>
       </c>
       <c r="E224" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F224" t="str">
         <v>Clear input field</v>
@@ -12272,13 +12272,13 @@
         <v>Clear input field on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L224">
-        <v>3305</v>
+        <v>2678</v>
       </c>
       <c r="M224" t="str">
         <v>Yes</v>
       </c>
       <c r="N224" t="str">
-        <v>className</v>
+        <v>css</v>
       </c>
       <c r="O224" t="str">
         <v>#barcode_scanner_element_223</v>
@@ -12301,7 +12301,7 @@
         <v>Critical</v>
       </c>
       <c r="E225" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F225" t="str">
         <v>Tab through fields</v>
@@ -12325,13 +12325,13 @@
         <v>Tab through fields on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L225">
-        <v>2241</v>
+        <v>3116</v>
       </c>
       <c r="M225" t="str">
         <v>Yes</v>
       </c>
       <c r="N225" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O225" t="str">
         <v>#recipe_suggestions_element_224</v>
@@ -12354,7 +12354,7 @@
         <v>High</v>
       </c>
       <c r="E226" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F226" t="str">
         <v>Verify field validation</v>
@@ -12378,13 +12378,13 @@
         <v>Verify field validation on Family Sync completes successfully without errors</v>
       </c>
       <c r="L226">
-        <v>3471</v>
+        <v>3025</v>
       </c>
       <c r="M226" t="str">
         <v>Yes</v>
       </c>
       <c r="N226" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O226" t="str">
         <v>#family_sync_element_225</v>
@@ -12431,13 +12431,13 @@
         <v>Upload file on Shopping List completes successfully without errors</v>
       </c>
       <c r="L227">
-        <v>1979</v>
+        <v>1774</v>
       </c>
       <c r="M227" t="str">
         <v>Yes</v>
       </c>
       <c r="N227" t="str">
-        <v>tagName</v>
+        <v>linkText</v>
       </c>
       <c r="O227" t="str">
         <v>#shopping_list_element_226</v>
@@ -12460,7 +12460,7 @@
         <v>Low</v>
       </c>
       <c r="E228" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F228" t="str">
         <v>Verify file upload success</v>
@@ -12484,13 +12484,13 @@
         <v>Verify file upload success on User Profile completes successfully without errors</v>
       </c>
       <c r="L228">
-        <v>3881</v>
+        <v>1322</v>
       </c>
       <c r="M228" t="str">
         <v>Yes</v>
       </c>
       <c r="N228" t="str">
-        <v>css</v>
+        <v>className</v>
       </c>
       <c r="O228" t="str">
         <v>#user_profile_element_227</v>
@@ -12537,13 +12537,13 @@
         <v>Download file on Settings completes successfully without errors</v>
       </c>
       <c r="L229">
-        <v>1662</v>
+        <v>2375</v>
       </c>
       <c r="M229" t="str">
         <v>Yes</v>
       </c>
       <c r="N229" t="str">
-        <v>id</v>
+        <v>tagName</v>
       </c>
       <c r="O229" t="str">
         <v>#settings_element_228</v>
@@ -12566,7 +12566,7 @@
         <v>High</v>
       </c>
       <c r="E230" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F230" t="str">
         <v>Verify download</v>
@@ -12590,13 +12590,13 @@
         <v>Verify download on Notifications completes successfully without errors</v>
       </c>
       <c r="L230">
-        <v>1785</v>
+        <v>2430</v>
       </c>
       <c r="M230" t="str">
         <v>Yes</v>
       </c>
       <c r="N230" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O230" t="str">
         <v>#notifications_element_229</v>
@@ -12643,13 +12643,13 @@
         <v>Resize window to mobile on Search completes successfully without errors</v>
       </c>
       <c r="L231">
-        <v>1299</v>
+        <v>721</v>
       </c>
       <c r="M231" t="str">
         <v>Yes</v>
       </c>
       <c r="N231" t="str">
-        <v>id</v>
+        <v>linkText</v>
       </c>
       <c r="O231" t="str">
         <v>#search_element_230</v>
@@ -12672,7 +12672,7 @@
         <v>Low</v>
       </c>
       <c r="E232" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F232" t="str">
         <v>Resize window to tablet</v>
@@ -12696,16 +12696,16 @@
         <v>Resize window to tablet on Reports completes successfully without errors</v>
       </c>
       <c r="L232">
-        <v>232</v>
+        <v>3894</v>
       </c>
       <c r="M232" t="str">
         <v>Yes</v>
       </c>
       <c r="N232" t="str">
-        <v>xpath</v>
+        <v>id</v>
       </c>
       <c r="O232" t="str">
-        <v>//div[@id='reports_231']</v>
+        <v>#reports_element_231</v>
       </c>
       <c r="P232" t="str">
         <v>Pass</v>
@@ -12725,7 +12725,7 @@
         <v>Critical</v>
       </c>
       <c r="E233" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F233" t="str">
         <v>Resize window to desktop</v>
@@ -12749,13 +12749,13 @@
         <v>Resize window to desktop on Analytics completes successfully without errors</v>
       </c>
       <c r="L233">
-        <v>2846</v>
+        <v>3672</v>
       </c>
       <c r="M233" t="str">
         <v>Yes</v>
       </c>
       <c r="N233" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O233" t="str">
         <v>#analytics_element_232</v>
@@ -12802,16 +12802,16 @@
         <v>Verify responsive layout on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L234">
-        <v>1974</v>
+        <v>2443</v>
       </c>
       <c r="M234" t="str">
         <v>Yes</v>
       </c>
       <c r="N234" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O234" t="str">
-        <v>#storage_locations_element_233</v>
+        <v>//div[@id='storage_locations_233']</v>
       </c>
       <c r="P234" t="str">
         <v>Pass</v>
@@ -12831,7 +12831,7 @@
         <v>Medium</v>
       </c>
       <c r="E235" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F235" t="str">
         <v>Keyboard navigation</v>
@@ -12855,13 +12855,13 @@
         <v>Keyboard navigation on Categories completes successfully without errors</v>
       </c>
       <c r="L235">
-        <v>2531</v>
+        <v>1508</v>
       </c>
       <c r="M235" t="str">
         <v>Yes</v>
       </c>
       <c r="N235" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O235" t="str">
         <v>#categories_element_234</v>
@@ -12884,7 +12884,7 @@
         <v>Low</v>
       </c>
       <c r="E236" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F236" t="str">
         <v>Verify focus state</v>
@@ -12908,13 +12908,13 @@
         <v>Verify focus state on Export completes successfully without errors</v>
       </c>
       <c r="L236">
-        <v>301</v>
+        <v>3933</v>
       </c>
       <c r="M236" t="str">
         <v>Yes</v>
       </c>
       <c r="N236" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O236" t="str">
         <v>#export_element_235</v>
@@ -12937,7 +12937,7 @@
         <v>Critical</v>
       </c>
       <c r="E237" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F237" t="str">
         <v>Verify hover state</v>
@@ -12961,13 +12961,13 @@
         <v>Verify hover state on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L237">
-        <v>3846</v>
+        <v>801</v>
       </c>
       <c r="M237" t="str">
         <v>Yes</v>
       </c>
       <c r="N237" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O237" t="str">
         <v>#admin_panel_element_236</v>
@@ -13014,13 +13014,13 @@
         <v>Verify active state on Onboarding completes successfully without errors</v>
       </c>
       <c r="L238">
-        <v>3804</v>
+        <v>3743</v>
       </c>
       <c r="M238" t="str">
         <v>Yes</v>
       </c>
       <c r="N238" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O238" t="str">
         <v>#onboarding_element_237</v>
@@ -13043,7 +13043,7 @@
         <v>Medium</v>
       </c>
       <c r="E239" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F239" t="str">
         <v>Verify disabled state</v>
@@ -13067,16 +13067,16 @@
         <v>Verify disabled state on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L239">
-        <v>2843</v>
+        <v>1053</v>
       </c>
       <c r="M239" t="str">
         <v>Yes</v>
       </c>
       <c r="N239" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O239" t="str">
-        <v>#help_&amp;_support_element_238</v>
+        <v>//div[@id='help_&amp;_support_238']</v>
       </c>
       <c r="P239" t="str">
         <v>Pass</v>
@@ -13096,7 +13096,7 @@
         <v>Low</v>
       </c>
       <c r="E240" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F240" t="str">
         <v>Verify loading spinner</v>
@@ -13120,13 +13120,13 @@
         <v>Verify loading spinner on Session Management completes successfully without errors</v>
       </c>
       <c r="L240">
-        <v>3460</v>
+        <v>360</v>
       </c>
       <c r="M240" t="str">
         <v>Yes</v>
       </c>
       <c r="N240" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O240" t="str">
         <v>#session_management_element_239</v>
@@ -13149,7 +13149,7 @@
         <v>Critical</v>
       </c>
       <c r="E241" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F241" t="str">
         <v>Verify skeleton loader</v>
@@ -13173,16 +13173,16 @@
         <v>Verify skeleton loader on Authentication completes successfully without errors</v>
       </c>
       <c r="L241">
-        <v>2489</v>
+        <v>3495</v>
       </c>
       <c r="M241" t="str">
         <v>Yes</v>
       </c>
       <c r="N241" t="str">
-        <v>xpath</v>
+        <v>name</v>
       </c>
       <c r="O241" t="str">
-        <v>//div[@id='authentication_240']</v>
+        <v>#authentication_element_240</v>
       </c>
       <c r="P241" t="str">
         <v>Pass</v>
@@ -13202,7 +13202,7 @@
         <v>High</v>
       </c>
       <c r="E242" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F242" t="str">
         <v>Verify empty state</v>
@@ -13226,7 +13226,7 @@
         <v>Verify empty state on Dashboard completes successfully without errors</v>
       </c>
       <c r="L242">
-        <v>285</v>
+        <v>3405</v>
       </c>
       <c r="M242" t="str">
         <v>Yes</v>
@@ -13255,7 +13255,7 @@
         <v>Medium</v>
       </c>
       <c r="E243" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F243" t="str">
         <v>Verify error state</v>
@@ -13279,13 +13279,13 @@
         <v>Verify error state on Inventory completes successfully without errors</v>
       </c>
       <c r="L243">
-        <v>1274</v>
+        <v>2869</v>
       </c>
       <c r="M243" t="str">
         <v>Yes</v>
       </c>
       <c r="N243" t="str">
-        <v>className</v>
+        <v>tagName</v>
       </c>
       <c r="O243" t="str">
         <v>#inventory_element_242</v>
@@ -13308,7 +13308,7 @@
         <v>Low</v>
       </c>
       <c r="E244" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F244" t="str">
         <v>Verify 404 page</v>
@@ -13332,13 +13332,13 @@
         <v>Verify 404 page on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L244">
-        <v>2175</v>
+        <v>3680</v>
       </c>
       <c r="M244" t="str">
         <v>Yes</v>
       </c>
       <c r="N244" t="str">
-        <v>id</v>
+        <v>css</v>
       </c>
       <c r="O244" t="str">
         <v>#barcode_scanner_element_243</v>
@@ -13361,7 +13361,7 @@
         <v>Critical</v>
       </c>
       <c r="E245" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F245" t="str">
         <v>Verify back navigation</v>
@@ -13385,16 +13385,16 @@
         <v>Verify back navigation on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L245">
-        <v>3308</v>
+        <v>2033</v>
       </c>
       <c r="M245" t="str">
         <v>Yes</v>
       </c>
       <c r="N245" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O245" t="str">
-        <v>#recipe_suggestions_element_244</v>
+        <v>//div[@id='recipe_suggestions_244']</v>
       </c>
       <c r="P245" t="str">
         <v>Pass</v>
@@ -13414,7 +13414,7 @@
         <v>High</v>
       </c>
       <c r="E246" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F246" t="str">
         <v>Verify forward navigation</v>
@@ -13438,7 +13438,7 @@
         <v>Verify forward navigation on Family Sync completes successfully without errors</v>
       </c>
       <c r="L246">
-        <v>2969</v>
+        <v>3303</v>
       </c>
       <c r="M246" t="str">
         <v>Yes</v>
@@ -13467,7 +13467,7 @@
         <v>Medium</v>
       </c>
       <c r="E247" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F247" t="str">
         <v>Refresh page</v>
@@ -13491,13 +13491,13 @@
         <v>Refresh page on Shopping List completes successfully without errors</v>
       </c>
       <c r="L247">
-        <v>2261</v>
+        <v>3213</v>
       </c>
       <c r="M247" t="str">
         <v>Yes</v>
       </c>
       <c r="N247" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O247" t="str">
         <v>#shopping_list_element_246</v>
@@ -13520,7 +13520,7 @@
         <v>Low</v>
       </c>
       <c r="E248" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F248" t="str">
         <v>Verify session persistence</v>
@@ -13544,7 +13544,7 @@
         <v>Verify session persistence on User Profile completes successfully without errors</v>
       </c>
       <c r="L248">
-        <v>3761</v>
+        <v>637</v>
       </c>
       <c r="M248" t="str">
         <v>Yes</v>
@@ -13573,7 +13573,7 @@
         <v>Critical</v>
       </c>
       <c r="E249" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F249" t="str">
         <v>Verify logout clears session</v>
@@ -13597,16 +13597,16 @@
         <v>Verify logout clears session on Settings completes successfully without errors</v>
       </c>
       <c r="L249">
-        <v>3340</v>
+        <v>230</v>
       </c>
       <c r="M249" t="str">
         <v>Yes</v>
       </c>
       <c r="N249" t="str">
-        <v>linkText</v>
+        <v>xpath</v>
       </c>
       <c r="O249" t="str">
-        <v>#settings_element_248</v>
+        <v>//div[@id='settings_248']</v>
       </c>
       <c r="P249" t="str">
         <v>Pass</v>
@@ -13626,7 +13626,7 @@
         <v>High</v>
       </c>
       <c r="E250" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F250" t="str">
         <v>Verify remember me</v>
@@ -13650,13 +13650,13 @@
         <v>Verify remember me on Notifications completes successfully without errors</v>
       </c>
       <c r="L250">
-        <v>3905</v>
+        <v>1611</v>
       </c>
       <c r="M250" t="str">
         <v>Yes</v>
       </c>
       <c r="N250" t="str">
-        <v>name</v>
+        <v>id</v>
       </c>
       <c r="O250" t="str">
         <v>#notifications_element_249</v>
@@ -13679,7 +13679,7 @@
         <v>Medium</v>
       </c>
       <c r="E251" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F251" t="str">
         <v>Verify auto-logout</v>
@@ -13703,13 +13703,13 @@
         <v>Verify auto-logout on Search completes successfully without errors</v>
       </c>
       <c r="L251">
-        <v>3201</v>
+        <v>1550</v>
       </c>
       <c r="M251" t="str">
         <v>Yes</v>
       </c>
       <c r="N251" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O251" t="str">
         <v>#search_element_250</v>
@@ -13732,7 +13732,7 @@
         <v>Low</v>
       </c>
       <c r="E252" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F252" t="str">
         <v>Verify concurrent session</v>
@@ -13756,13 +13756,13 @@
         <v>Verify concurrent session on Reports completes successfully without errors</v>
       </c>
       <c r="L252">
-        <v>1238</v>
+        <v>2214</v>
       </c>
       <c r="M252" t="str">
         <v>Yes</v>
       </c>
       <c r="N252" t="str">
-        <v>name</v>
+        <v>id</v>
       </c>
       <c r="O252" t="str">
         <v>#reports_element_251</v>
@@ -13785,7 +13785,7 @@
         <v>Critical</v>
       </c>
       <c r="E253" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F253" t="str">
         <v>Verify page title</v>
@@ -13809,13 +13809,13 @@
         <v>Verify page title on Analytics completes successfully without errors</v>
       </c>
       <c r="L253">
-        <v>2038</v>
+        <v>352</v>
       </c>
       <c r="M253" t="str">
         <v>Yes</v>
       </c>
       <c r="N253" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O253" t="str">
         <v>#analytics_element_252</v>
@@ -13838,7 +13838,7 @@
         <v>High</v>
       </c>
       <c r="E254" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F254" t="str">
         <v>Verify page loads</v>
@@ -13862,16 +13862,16 @@
         <v>Verify page loads on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L254">
-        <v>1661</v>
+        <v>3932</v>
       </c>
       <c r="M254" t="str">
         <v>Yes</v>
       </c>
       <c r="N254" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O254" t="str">
-        <v>#storage_locations_element_253</v>
+        <v>//div[@id='storage_locations_253']</v>
       </c>
       <c r="P254" t="str">
         <v>Pass</v>
@@ -13891,7 +13891,7 @@
         <v>Medium</v>
       </c>
       <c r="E255" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F255" t="str">
         <v>Click button</v>
@@ -13915,13 +13915,13 @@
         <v>Click button on Categories completes successfully without errors</v>
       </c>
       <c r="L255">
-        <v>2180</v>
+        <v>866</v>
       </c>
       <c r="M255" t="str">
         <v>Yes</v>
       </c>
       <c r="N255" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O255" t="str">
         <v>#categories_element_254</v>
@@ -13944,7 +13944,7 @@
         <v>Low</v>
       </c>
       <c r="E256" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F256" t="str">
         <v>Enter valid input</v>
@@ -13968,16 +13968,16 @@
         <v>Enter valid input on Export completes successfully without errors</v>
       </c>
       <c r="L256">
-        <v>1841</v>
+        <v>3729</v>
       </c>
       <c r="M256" t="str">
         <v>Yes</v>
       </c>
       <c r="N256" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O256" t="str">
-        <v>//div[@id='export_255']</v>
+        <v>#export_element_255</v>
       </c>
       <c r="P256" t="str">
         <v>Pass</v>
@@ -13997,7 +13997,7 @@
         <v>Critical</v>
       </c>
       <c r="E257" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F257" t="str">
         <v>Enter invalid input</v>
@@ -14021,16 +14021,16 @@
         <v>Enter invalid input on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L257">
-        <v>2539</v>
+        <v>1472</v>
       </c>
       <c r="M257" t="str">
         <v>Yes</v>
       </c>
       <c r="N257" t="str">
-        <v>xpath</v>
+        <v>className</v>
       </c>
       <c r="O257" t="str">
-        <v>//div[@id='admin_panel_256']</v>
+        <v>#admin_panel_element_256</v>
       </c>
       <c r="P257" t="str">
         <v>Pass</v>
@@ -14050,7 +14050,7 @@
         <v>High</v>
       </c>
       <c r="E258" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F258" t="str">
         <v>Submit form</v>
@@ -14074,16 +14074,16 @@
         <v>Submit form on Onboarding completes successfully without errors</v>
       </c>
       <c r="L258">
-        <v>354</v>
+        <v>2774</v>
       </c>
       <c r="M258" t="str">
         <v>Yes</v>
       </c>
       <c r="N258" t="str">
-        <v>id</v>
+        <v>xpath</v>
       </c>
       <c r="O258" t="str">
-        <v>#onboarding_element_257</v>
+        <v>//div[@id='onboarding_257']</v>
       </c>
       <c r="P258" t="str">
         <v>Pass</v>
@@ -14103,7 +14103,7 @@
         <v>Medium</v>
       </c>
       <c r="E259" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F259" t="str">
         <v>Verify error message</v>
@@ -14127,16 +14127,16 @@
         <v>Verify error message on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L259">
-        <v>1687</v>
+        <v>3957</v>
       </c>
       <c r="M259" t="str">
         <v>Yes</v>
       </c>
       <c r="N259" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O259" t="str">
-        <v>#help_&amp;_support_element_258</v>
+        <v>//div[@id='help_&amp;_support_258']</v>
       </c>
       <c r="P259" t="str">
         <v>Pass</v>
@@ -14156,7 +14156,7 @@
         <v>Low</v>
       </c>
       <c r="E260" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F260" t="str">
         <v>Verify success message</v>
@@ -14180,13 +14180,13 @@
         <v>Verify success message on Session Management completes successfully without errors</v>
       </c>
       <c r="L260">
-        <v>242</v>
+        <v>2685</v>
       </c>
       <c r="M260" t="str">
         <v>Yes</v>
       </c>
       <c r="N260" t="str">
-        <v>tagName</v>
+        <v>css</v>
       </c>
       <c r="O260" t="str">
         <v>#session_management_element_259</v>
@@ -14209,7 +14209,7 @@
         <v>Critical</v>
       </c>
       <c r="E261" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F261" t="str">
         <v>Verify redirect</v>
@@ -14233,16 +14233,16 @@
         <v>Verify redirect on Authentication completes successfully without errors</v>
       </c>
       <c r="L261">
-        <v>1872</v>
+        <v>402</v>
       </c>
       <c r="M261" t="str">
         <v>Yes</v>
       </c>
       <c r="N261" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O261" t="str">
-        <v>#authentication_element_260</v>
+        <v>//div[@id='authentication_260']</v>
       </c>
       <c r="P261" t="str">
         <v>Pass</v>
@@ -14262,7 +14262,7 @@
         <v>High</v>
       </c>
       <c r="E262" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F262" t="str">
         <v>Verify element visible</v>
@@ -14286,13 +14286,13 @@
         <v>Verify element visible on Dashboard completes successfully without errors</v>
       </c>
       <c r="L262">
-        <v>1782</v>
+        <v>269</v>
       </c>
       <c r="M262" t="str">
         <v>Yes</v>
       </c>
       <c r="N262" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O262" t="str">
         <v>#dashboard_element_261</v>
@@ -14315,7 +14315,7 @@
         <v>Medium</v>
       </c>
       <c r="E263" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F263" t="str">
         <v>Verify element hidden</v>
@@ -14339,16 +14339,16 @@
         <v>Verify element hidden on Inventory completes successfully without errors</v>
       </c>
       <c r="L263">
-        <v>404</v>
+        <v>1429</v>
       </c>
       <c r="M263" t="str">
         <v>Yes</v>
       </c>
       <c r="N263" t="str">
-        <v>className</v>
+        <v>xpath</v>
       </c>
       <c r="O263" t="str">
-        <v>#inventory_element_262</v>
+        <v>//div[@id='inventory_262']</v>
       </c>
       <c r="P263" t="str">
         <v>Pass</v>
@@ -14368,7 +14368,7 @@
         <v>Low</v>
       </c>
       <c r="E264" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F264" t="str">
         <v>Verify element disabled</v>
@@ -14392,13 +14392,13 @@
         <v>Verify element disabled on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L264">
-        <v>3986</v>
+        <v>3017</v>
       </c>
       <c r="M264" t="str">
         <v>Yes</v>
       </c>
       <c r="N264" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O264" t="str">
         <v>#barcode_scanner_element_263</v>
@@ -14421,7 +14421,7 @@
         <v>Critical</v>
       </c>
       <c r="E265" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F265" t="str">
         <v>Verify element enabled</v>
@@ -14445,13 +14445,13 @@
         <v>Verify element enabled on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L265">
-        <v>366</v>
+        <v>720</v>
       </c>
       <c r="M265" t="str">
         <v>Yes</v>
       </c>
       <c r="N265" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O265" t="str">
         <v>#recipe_suggestions_element_264</v>
@@ -14474,7 +14474,7 @@
         <v>High</v>
       </c>
       <c r="E266" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F266" t="str">
         <v>Hover over element</v>
@@ -14498,7 +14498,7 @@
         <v>Hover over element on Family Sync completes successfully without errors</v>
       </c>
       <c r="L266">
-        <v>3836</v>
+        <v>1918</v>
       </c>
       <c r="M266" t="str">
         <v>Yes</v>
@@ -14551,13 +14551,13 @@
         <v>Click dropdown on Shopping List completes successfully without errors</v>
       </c>
       <c r="L267">
-        <v>2859</v>
+        <v>3367</v>
       </c>
       <c r="M267" t="str">
         <v>Yes</v>
       </c>
       <c r="N267" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O267" t="str">
         <v>#shopping_list_element_266</v>
@@ -14580,7 +14580,7 @@
         <v>Low</v>
       </c>
       <c r="E268" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F268" t="str">
         <v>Select option from dropdown</v>
@@ -14604,16 +14604,16 @@
         <v>Select option from dropdown on User Profile completes successfully without errors</v>
       </c>
       <c r="L268">
-        <v>1539</v>
+        <v>601</v>
       </c>
       <c r="M268" t="str">
         <v>Yes</v>
       </c>
       <c r="N268" t="str">
-        <v>linkText</v>
+        <v>xpath</v>
       </c>
       <c r="O268" t="str">
-        <v>#user_profile_element_267</v>
+        <v>//div[@id='user_profile_267']</v>
       </c>
       <c r="P268" t="str">
         <v>Pass</v>
@@ -14633,7 +14633,7 @@
         <v>Critical</v>
       </c>
       <c r="E269" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F269" t="str">
         <v>Verify dropdown options</v>
@@ -14657,13 +14657,13 @@
         <v>Verify dropdown options on Settings completes successfully without errors</v>
       </c>
       <c r="L269">
-        <v>3055</v>
+        <v>3383</v>
       </c>
       <c r="M269" t="str">
         <v>Yes</v>
       </c>
       <c r="N269" t="str">
-        <v>css</v>
+        <v>className</v>
       </c>
       <c r="O269" t="str">
         <v>#settings_element_268</v>
@@ -14686,7 +14686,7 @@
         <v>High</v>
       </c>
       <c r="E270" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F270" t="str">
         <v>Scroll to element</v>
@@ -14710,13 +14710,13 @@
         <v>Scroll to element on Notifications completes successfully without errors</v>
       </c>
       <c r="L270">
-        <v>2594</v>
+        <v>692</v>
       </c>
       <c r="M270" t="str">
         <v>Yes</v>
       </c>
       <c r="N270" t="str">
-        <v>className</v>
+        <v>tagName</v>
       </c>
       <c r="O270" t="str">
         <v>#notifications_element_269</v>
@@ -14763,13 +14763,13 @@
         <v>Take screenshot on Search completes successfully without errors</v>
       </c>
       <c r="L271">
-        <v>305</v>
+        <v>3392</v>
       </c>
       <c r="M271" t="str">
         <v>Yes</v>
       </c>
       <c r="N271" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O271" t="str">
         <v>#search_element_270</v>
@@ -14816,16 +14816,16 @@
         <v>Verify URL on Reports completes successfully without errors</v>
       </c>
       <c r="L272">
-        <v>3572</v>
+        <v>1719</v>
       </c>
       <c r="M272" t="str">
         <v>Yes</v>
       </c>
       <c r="N272" t="str">
-        <v>xpath</v>
+        <v>name</v>
       </c>
       <c r="O272" t="str">
-        <v>//div[@id='reports_271']</v>
+        <v>#reports_element_271</v>
       </c>
       <c r="P272" t="str">
         <v>Pass</v>
@@ -14845,7 +14845,7 @@
         <v>Critical</v>
       </c>
       <c r="E273" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F273" t="str">
         <v>Verify breadcrumb</v>
@@ -14869,16 +14869,16 @@
         <v>Verify breadcrumb on Analytics completes successfully without errors</v>
       </c>
       <c r="L273">
-        <v>1114</v>
+        <v>3381</v>
       </c>
       <c r="M273" t="str">
         <v>Yes</v>
       </c>
       <c r="N273" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O273" t="str">
-        <v>//div[@id='analytics_272']</v>
+        <v>#analytics_element_272</v>
       </c>
       <c r="P273" t="str">
         <v>Pass</v>
@@ -14898,7 +14898,7 @@
         <v>High</v>
       </c>
       <c r="E274" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F274" t="str">
         <v>Verify table data</v>
@@ -14922,16 +14922,16 @@
         <v>Verify table data on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L274">
-        <v>1509</v>
+        <v>3765</v>
       </c>
       <c r="M274" t="str">
         <v>Yes</v>
       </c>
       <c r="N274" t="str">
-        <v>linkText</v>
+        <v>xpath</v>
       </c>
       <c r="O274" t="str">
-        <v>#storage_locations_element_273</v>
+        <v>//div[@id='storage_locations_273']</v>
       </c>
       <c r="P274" t="str">
         <v>Pass</v>
@@ -14951,7 +14951,7 @@
         <v>Medium</v>
       </c>
       <c r="E275" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F275" t="str">
         <v>Sort table column</v>
@@ -14975,7 +14975,7 @@
         <v>Sort table column on Categories completes successfully without errors</v>
       </c>
       <c r="L275">
-        <v>2082</v>
+        <v>1963</v>
       </c>
       <c r="M275" t="str">
         <v>Yes</v>
@@ -15004,7 +15004,7 @@
         <v>Low</v>
       </c>
       <c r="E276" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F276" t="str">
         <v>Filter table</v>
@@ -15028,16 +15028,16 @@
         <v>Filter table on Export completes successfully without errors</v>
       </c>
       <c r="L276">
-        <v>1517</v>
+        <v>2073</v>
       </c>
       <c r="M276" t="str">
         <v>Yes</v>
       </c>
       <c r="N276" t="str">
-        <v>xpath</v>
+        <v>name</v>
       </c>
       <c r="O276" t="str">
-        <v>//div[@id='export_275']</v>
+        <v>#export_element_275</v>
       </c>
       <c r="P276" t="str">
         <v>Pass</v>
@@ -15057,7 +15057,7 @@
         <v>Critical</v>
       </c>
       <c r="E277" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F277" t="str">
         <v>Verify pagination</v>
@@ -15081,13 +15081,13 @@
         <v>Verify pagination on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L277">
-        <v>3343</v>
+        <v>3419</v>
       </c>
       <c r="M277" t="str">
         <v>Yes</v>
       </c>
       <c r="N277" t="str">
-        <v>id</v>
+        <v>name</v>
       </c>
       <c r="O277" t="str">
         <v>#admin_panel_element_276</v>
@@ -15110,7 +15110,7 @@
         <v>High</v>
       </c>
       <c r="E278" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F278" t="str">
         <v>Click pagination next</v>
@@ -15134,13 +15134,13 @@
         <v>Click pagination next on Onboarding completes successfully without errors</v>
       </c>
       <c r="L278">
-        <v>379</v>
+        <v>557</v>
       </c>
       <c r="M278" t="str">
         <v>Yes</v>
       </c>
       <c r="N278" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O278" t="str">
         <v>#onboarding_element_277</v>
@@ -15163,7 +15163,7 @@
         <v>Medium</v>
       </c>
       <c r="E279" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F279" t="str">
         <v>Click pagination prev</v>
@@ -15187,7 +15187,7 @@
         <v>Click pagination prev on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L279">
-        <v>250</v>
+        <v>3514</v>
       </c>
       <c r="M279" t="str">
         <v>Yes</v>
@@ -15216,7 +15216,7 @@
         <v>Low</v>
       </c>
       <c r="E280" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F280" t="str">
         <v>Verify modal opens</v>
@@ -15240,13 +15240,13 @@
         <v>Verify modal opens on Session Management completes successfully without errors</v>
       </c>
       <c r="L280">
-        <v>1908</v>
+        <v>2148</v>
       </c>
       <c r="M280" t="str">
         <v>Yes</v>
       </c>
       <c r="N280" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O280" t="str">
         <v>#session_management_element_279</v>
@@ -15293,16 +15293,16 @@
         <v>Verify modal closes on Authentication completes successfully without errors</v>
       </c>
       <c r="L281">
-        <v>3380</v>
+        <v>455</v>
       </c>
       <c r="M281" t="str">
         <v>Yes</v>
       </c>
       <c r="N281" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O281" t="str">
-        <v>#authentication_element_280</v>
+        <v>//div[@id='authentication_280']</v>
       </c>
       <c r="P281" t="str">
         <v>Pass</v>
@@ -15322,7 +15322,7 @@
         <v>High</v>
       </c>
       <c r="E282" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F282" t="str">
         <v>Verify toast notification</v>
@@ -15346,13 +15346,13 @@
         <v>Verify toast notification on Dashboard completes successfully without errors</v>
       </c>
       <c r="L282">
-        <v>1485</v>
+        <v>1084</v>
       </c>
       <c r="M282" t="str">
         <v>Yes</v>
       </c>
       <c r="N282" t="str">
-        <v>linkText</v>
+        <v>id</v>
       </c>
       <c r="O282" t="str">
         <v>#dashboard_element_281</v>
@@ -15399,7 +15399,7 @@
         <v>Verify alert dialog on Inventory completes successfully without errors</v>
       </c>
       <c r="L283">
-        <v>1555</v>
+        <v>2027</v>
       </c>
       <c r="M283" t="str">
         <v>Yes</v>
@@ -15452,7 +15452,7 @@
         <v>Accept alert on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L284">
-        <v>3812</v>
+        <v>201</v>
       </c>
       <c r="M284" t="str">
         <v>Yes</v>
@@ -15481,7 +15481,7 @@
         <v>Critical</v>
       </c>
       <c r="E285" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F285" t="str">
         <v>Dismiss alert</v>
@@ -15505,16 +15505,16 @@
         <v>Dismiss alert on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L285">
-        <v>438</v>
+        <v>1825</v>
       </c>
       <c r="M285" t="str">
         <v>Yes</v>
       </c>
       <c r="N285" t="str">
-        <v>className</v>
+        <v>xpath</v>
       </c>
       <c r="O285" t="str">
-        <v>#recipe_suggestions_element_284</v>
+        <v>//div[@id='recipe_suggestions_284']</v>
       </c>
       <c r="P285" t="str">
         <v>Pass</v>
@@ -15534,7 +15534,7 @@
         <v>High</v>
       </c>
       <c r="E286" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F286" t="str">
         <v>Verify placeholder text</v>
@@ -15558,13 +15558,13 @@
         <v>Verify placeholder text on Family Sync completes successfully without errors</v>
       </c>
       <c r="L286">
-        <v>3704</v>
+        <v>1648</v>
       </c>
       <c r="M286" t="str">
         <v>Yes</v>
       </c>
       <c r="N286" t="str">
-        <v>className</v>
+        <v>css</v>
       </c>
       <c r="O286" t="str">
         <v>#family_sync_element_285</v>
@@ -15587,7 +15587,7 @@
         <v>Medium</v>
       </c>
       <c r="E287" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F287" t="str">
         <v>Clear input field</v>
@@ -15611,13 +15611,13 @@
         <v>Clear input field on Shopping List completes successfully without errors</v>
       </c>
       <c r="L287">
-        <v>832</v>
+        <v>3030</v>
       </c>
       <c r="M287" t="str">
         <v>Yes</v>
       </c>
       <c r="N287" t="str">
-        <v>name</v>
+        <v>className</v>
       </c>
       <c r="O287" t="str">
         <v>#shopping_list_element_286</v>
@@ -15640,7 +15640,7 @@
         <v>Low</v>
       </c>
       <c r="E288" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F288" t="str">
         <v>Tab through fields</v>
@@ -15664,13 +15664,13 @@
         <v>Tab through fields on User Profile completes successfully without errors</v>
       </c>
       <c r="L288">
-        <v>2685</v>
+        <v>3709</v>
       </c>
       <c r="M288" t="str">
         <v>Yes</v>
       </c>
       <c r="N288" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O288" t="str">
         <v>#user_profile_element_287</v>
@@ -15693,7 +15693,7 @@
         <v>Critical</v>
       </c>
       <c r="E289" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F289" t="str">
         <v>Verify field validation</v>
@@ -15717,13 +15717,13 @@
         <v>Verify field validation on Settings completes successfully without errors</v>
       </c>
       <c r="L289">
-        <v>2823</v>
+        <v>300</v>
       </c>
       <c r="M289" t="str">
         <v>Yes</v>
       </c>
       <c r="N289" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O289" t="str">
         <v>#settings_element_288</v>
@@ -15746,7 +15746,7 @@
         <v>High</v>
       </c>
       <c r="E290" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F290" t="str">
         <v>Upload file</v>
@@ -15770,7 +15770,7 @@
         <v>Upload file on Notifications completes successfully without errors</v>
       </c>
       <c r="L290">
-        <v>1445</v>
+        <v>1923</v>
       </c>
       <c r="M290" t="str">
         <v>Yes</v>
@@ -15799,7 +15799,7 @@
         <v>Medium</v>
       </c>
       <c r="E291" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F291" t="str">
         <v>Verify file upload success</v>
@@ -15823,13 +15823,13 @@
         <v>Verify file upload success on Search completes successfully without errors</v>
       </c>
       <c r="L291">
-        <v>981</v>
+        <v>3129</v>
       </c>
       <c r="M291" t="str">
         <v>Yes</v>
       </c>
       <c r="N291" t="str">
-        <v>id</v>
+        <v>tagName</v>
       </c>
       <c r="O291" t="str">
         <v>#search_element_290</v>
@@ -15852,7 +15852,7 @@
         <v>Low</v>
       </c>
       <c r="E292" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F292" t="str">
         <v>Download file</v>
@@ -15876,7 +15876,7 @@
         <v>Download file on Reports completes successfully without errors</v>
       </c>
       <c r="L292">
-        <v>1464</v>
+        <v>334</v>
       </c>
       <c r="M292" t="str">
         <v>Yes</v>
@@ -15905,7 +15905,7 @@
         <v>Critical</v>
       </c>
       <c r="E293" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F293" t="str">
         <v>Verify download</v>
@@ -15929,13 +15929,13 @@
         <v>Verify download on Analytics completes successfully without errors</v>
       </c>
       <c r="L293">
-        <v>1655</v>
+        <v>2066</v>
       </c>
       <c r="M293" t="str">
         <v>Yes</v>
       </c>
       <c r="N293" t="str">
-        <v>tagName</v>
+        <v>className</v>
       </c>
       <c r="O293" t="str">
         <v>#analytics_element_292</v>
@@ -15958,7 +15958,7 @@
         <v>High</v>
       </c>
       <c r="E294" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F294" t="str">
         <v>Resize window to mobile</v>
@@ -15982,13 +15982,13 @@
         <v>Resize window to mobile on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L294">
-        <v>3989</v>
+        <v>3128</v>
       </c>
       <c r="M294" t="str">
         <v>Yes</v>
       </c>
       <c r="N294" t="str">
-        <v>css</v>
+        <v>id</v>
       </c>
       <c r="O294" t="str">
         <v>#storage_locations_element_293</v>
@@ -16011,7 +16011,7 @@
         <v>Medium</v>
       </c>
       <c r="E295" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F295" t="str">
         <v>Resize window to tablet</v>
@@ -16035,13 +16035,13 @@
         <v>Resize window to tablet on Categories completes successfully without errors</v>
       </c>
       <c r="L295">
-        <v>3602</v>
+        <v>3359</v>
       </c>
       <c r="M295" t="str">
         <v>Yes</v>
       </c>
       <c r="N295" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O295" t="str">
         <v>#categories_element_294</v>
@@ -16064,7 +16064,7 @@
         <v>Low</v>
       </c>
       <c r="E296" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F296" t="str">
         <v>Resize window to desktop</v>
@@ -16088,16 +16088,16 @@
         <v>Resize window to desktop on Export completes successfully without errors</v>
       </c>
       <c r="L296">
-        <v>2875</v>
+        <v>2935</v>
       </c>
       <c r="M296" t="str">
         <v>Yes</v>
       </c>
       <c r="N296" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O296" t="str">
-        <v>#export_element_295</v>
+        <v>//div[@id='export_295']</v>
       </c>
       <c r="P296" t="str">
         <v>Pass</v>
@@ -16117,7 +16117,7 @@
         <v>Critical</v>
       </c>
       <c r="E297" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F297" t="str">
         <v>Verify responsive layout</v>
@@ -16141,13 +16141,13 @@
         <v>Verify responsive layout on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L297">
-        <v>2178</v>
+        <v>1184</v>
       </c>
       <c r="M297" t="str">
         <v>Yes</v>
       </c>
       <c r="N297" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O297" t="str">
         <v>#admin_panel_element_296</v>
@@ -16170,7 +16170,7 @@
         <v>High</v>
       </c>
       <c r="E298" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F298" t="str">
         <v>Keyboard navigation</v>
@@ -16194,16 +16194,16 @@
         <v>Keyboard navigation on Onboarding completes successfully without errors</v>
       </c>
       <c r="L298">
-        <v>1562</v>
+        <v>3201</v>
       </c>
       <c r="M298" t="str">
         <v>Yes</v>
       </c>
       <c r="N298" t="str">
-        <v>id</v>
+        <v>xpath</v>
       </c>
       <c r="O298" t="str">
-        <v>#onboarding_element_297</v>
+        <v>//div[@id='onboarding_297']</v>
       </c>
       <c r="P298" t="str">
         <v>Pass</v>
@@ -16247,13 +16247,13 @@
         <v>Verify focus state on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L299">
-        <v>1231</v>
+        <v>2637</v>
       </c>
       <c r="M299" t="str">
         <v>Yes</v>
       </c>
       <c r="N299" t="str">
-        <v>className</v>
+        <v>tagName</v>
       </c>
       <c r="O299" t="str">
         <v>#help_&amp;_support_element_298</v>
@@ -16276,7 +16276,7 @@
         <v>Low</v>
       </c>
       <c r="E300" t="str">
-        <v>Chrome</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F300" t="str">
         <v>Verify hover state</v>
@@ -16300,16 +16300,16 @@
         <v>Verify hover state on Session Management completes successfully without errors</v>
       </c>
       <c r="L300">
-        <v>2852</v>
+        <v>2499</v>
       </c>
       <c r="M300" t="str">
         <v>Yes</v>
       </c>
       <c r="N300" t="str">
-        <v>xpath</v>
+        <v>className</v>
       </c>
       <c r="O300" t="str">
-        <v>//div[@id='session_management_299']</v>
+        <v>#session_management_element_299</v>
       </c>
       <c r="P300" t="str">
         <v>Pass</v>
@@ -16329,7 +16329,7 @@
         <v>Critical</v>
       </c>
       <c r="E301" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F301" t="str">
         <v>Verify active state</v>
@@ -16353,13 +16353,13 @@
         <v>Verify active state on Authentication completes successfully without errors</v>
       </c>
       <c r="L301">
-        <v>3502</v>
+        <v>1891</v>
       </c>
       <c r="M301" t="str">
         <v>Yes</v>
       </c>
       <c r="N301" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O301" t="str">
         <v>#authentication_element_300</v>
@@ -16382,7 +16382,7 @@
         <v>High</v>
       </c>
       <c r="E302" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F302" t="str">
         <v>Verify disabled state</v>
@@ -16406,13 +16406,13 @@
         <v>Verify disabled state on Dashboard completes successfully without errors</v>
       </c>
       <c r="L302">
-        <v>1012</v>
+        <v>3461</v>
       </c>
       <c r="M302" t="str">
         <v>Yes</v>
       </c>
       <c r="N302" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O302" t="str">
         <v>#dashboard_element_301</v>
@@ -16459,7 +16459,7 @@
         <v>Verify loading spinner on Inventory completes successfully without errors</v>
       </c>
       <c r="L303">
-        <v>980</v>
+        <v>1615</v>
       </c>
       <c r="M303" t="str">
         <v>Yes</v>
@@ -16488,7 +16488,7 @@
         <v>Low</v>
       </c>
       <c r="E304" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F304" t="str">
         <v>Verify skeleton loader</v>
@@ -16512,13 +16512,13 @@
         <v>Verify skeleton loader on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L304">
-        <v>2320</v>
+        <v>1666</v>
       </c>
       <c r="M304" t="str">
         <v>Yes</v>
       </c>
       <c r="N304" t="str">
-        <v>name</v>
+        <v>className</v>
       </c>
       <c r="O304" t="str">
         <v>#barcode_scanner_element_303</v>
@@ -16541,7 +16541,7 @@
         <v>Critical</v>
       </c>
       <c r="E305" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F305" t="str">
         <v>Verify empty state</v>
@@ -16565,13 +16565,13 @@
         <v>Verify empty state on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L305">
-        <v>2655</v>
+        <v>533</v>
       </c>
       <c r="M305" t="str">
         <v>Yes</v>
       </c>
       <c r="N305" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O305" t="str">
         <v>#recipe_suggestions_element_304</v>
@@ -16594,7 +16594,7 @@
         <v>High</v>
       </c>
       <c r="E306" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F306" t="str">
         <v>Verify error state</v>
@@ -16618,13 +16618,13 @@
         <v>Verify error state on Family Sync completes successfully without errors</v>
       </c>
       <c r="L306">
-        <v>1782</v>
+        <v>536</v>
       </c>
       <c r="M306" t="str">
         <v>Yes</v>
       </c>
       <c r="N306" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O306" t="str">
         <v>#family_sync_element_305</v>
@@ -16647,7 +16647,7 @@
         <v>Medium</v>
       </c>
       <c r="E307" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F307" t="str">
         <v>Verify 404 page</v>
@@ -16671,16 +16671,16 @@
         <v>Verify 404 page on Shopping List completes successfully without errors</v>
       </c>
       <c r="L307">
-        <v>3478</v>
+        <v>1539</v>
       </c>
       <c r="M307" t="str">
         <v>Yes</v>
       </c>
       <c r="N307" t="str">
-        <v>id</v>
+        <v>xpath</v>
       </c>
       <c r="O307" t="str">
-        <v>#shopping_list_element_306</v>
+        <v>//div[@id='shopping_list_306']</v>
       </c>
       <c r="P307" t="str">
         <v>Pass</v>
@@ -16700,7 +16700,7 @@
         <v>Low</v>
       </c>
       <c r="E308" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F308" t="str">
         <v>Verify back navigation</v>
@@ -16724,13 +16724,13 @@
         <v>Verify back navigation on User Profile completes successfully without errors</v>
       </c>
       <c r="L308">
-        <v>3890</v>
+        <v>2240</v>
       </c>
       <c r="M308" t="str">
         <v>Yes</v>
       </c>
       <c r="N308" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O308" t="str">
         <v>#user_profile_element_307</v>
@@ -16753,7 +16753,7 @@
         <v>Critical</v>
       </c>
       <c r="E309" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F309" t="str">
         <v>Verify forward navigation</v>
@@ -16777,13 +16777,13 @@
         <v>Verify forward navigation on Settings completes successfully without errors</v>
       </c>
       <c r="L309">
-        <v>1163</v>
+        <v>2785</v>
       </c>
       <c r="M309" t="str">
         <v>Yes</v>
       </c>
       <c r="N309" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O309" t="str">
         <v>#settings_element_308</v>
@@ -16806,7 +16806,7 @@
         <v>High</v>
       </c>
       <c r="E310" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F310" t="str">
         <v>Refresh page</v>
@@ -16830,13 +16830,13 @@
         <v>Refresh page on Notifications completes successfully without errors</v>
       </c>
       <c r="L310">
-        <v>1600</v>
+        <v>986</v>
       </c>
       <c r="M310" t="str">
         <v>Yes</v>
       </c>
       <c r="N310" t="str">
-        <v>id</v>
+        <v>name</v>
       </c>
       <c r="O310" t="str">
         <v>#notifications_element_309</v>
@@ -16859,7 +16859,7 @@
         <v>Medium</v>
       </c>
       <c r="E311" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F311" t="str">
         <v>Verify session persistence</v>
@@ -16883,13 +16883,13 @@
         <v>Verify session persistence on Search completes successfully without errors</v>
       </c>
       <c r="L311">
-        <v>1737</v>
+        <v>3246</v>
       </c>
       <c r="M311" t="str">
         <v>Yes</v>
       </c>
       <c r="N311" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O311" t="str">
         <v>#search_element_310</v>
@@ -16912,7 +16912,7 @@
         <v>Low</v>
       </c>
       <c r="E312" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F312" t="str">
         <v>Verify logout clears session</v>
@@ -16936,13 +16936,13 @@
         <v>Verify logout clears session on Reports completes successfully without errors</v>
       </c>
       <c r="L312">
-        <v>1239</v>
+        <v>3258</v>
       </c>
       <c r="M312" t="str">
         <v>Yes</v>
       </c>
       <c r="N312" t="str">
-        <v>className</v>
+        <v>linkText</v>
       </c>
       <c r="O312" t="str">
         <v>#reports_element_311</v>
@@ -16965,7 +16965,7 @@
         <v>Critical</v>
       </c>
       <c r="E313" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F313" t="str">
         <v>Verify remember me</v>
@@ -16989,13 +16989,13 @@
         <v>Verify remember me on Analytics completes successfully without errors</v>
       </c>
       <c r="L313">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="M313" t="str">
         <v>Yes</v>
       </c>
       <c r="N313" t="str">
-        <v>css</v>
+        <v>id</v>
       </c>
       <c r="O313" t="str">
         <v>#analytics_element_312</v>
@@ -17018,7 +17018,7 @@
         <v>High</v>
       </c>
       <c r="E314" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F314" t="str">
         <v>Verify auto-logout</v>
@@ -17042,7 +17042,7 @@
         <v>Verify auto-logout on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L314">
-        <v>850</v>
+        <v>2576</v>
       </c>
       <c r="M314" t="str">
         <v>Yes</v>
@@ -17095,7 +17095,7 @@
         <v>Verify concurrent session on Categories completes successfully without errors</v>
       </c>
       <c r="L315">
-        <v>1655</v>
+        <v>878</v>
       </c>
       <c r="M315" t="str">
         <v>Yes</v>
@@ -17124,7 +17124,7 @@
         <v>Low</v>
       </c>
       <c r="E316" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F316" t="str">
         <v>Verify page title</v>
@@ -17148,13 +17148,13 @@
         <v>Verify page title on Export completes successfully without errors</v>
       </c>
       <c r="L316">
-        <v>362</v>
+        <v>437</v>
       </c>
       <c r="M316" t="str">
         <v>Yes</v>
       </c>
       <c r="N316" t="str">
-        <v>linkText</v>
+        <v>css</v>
       </c>
       <c r="O316" t="str">
         <v>#export_element_315</v>
@@ -17177,7 +17177,7 @@
         <v>Critical</v>
       </c>
       <c r="E317" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F317" t="str">
         <v>Verify page loads</v>
@@ -17201,13 +17201,13 @@
         <v>Verify page loads on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L317">
-        <v>1044</v>
+        <v>2820</v>
       </c>
       <c r="M317" t="str">
         <v>Yes</v>
       </c>
       <c r="N317" t="str">
-        <v>linkText</v>
+        <v>id</v>
       </c>
       <c r="O317" t="str">
         <v>#admin_panel_element_316</v>
@@ -17230,7 +17230,7 @@
         <v>High</v>
       </c>
       <c r="E318" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F318" t="str">
         <v>Click button</v>
@@ -17254,16 +17254,16 @@
         <v>Click button on Onboarding completes successfully without errors</v>
       </c>
       <c r="L318">
-        <v>1334</v>
+        <v>685</v>
       </c>
       <c r="M318" t="str">
         <v>Yes</v>
       </c>
       <c r="N318" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O318" t="str">
-        <v>#onboarding_element_317</v>
+        <v>//div[@id='onboarding_317']</v>
       </c>
       <c r="P318" t="str">
         <v>Pass</v>
@@ -17283,7 +17283,7 @@
         <v>Medium</v>
       </c>
       <c r="E319" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F319" t="str">
         <v>Enter valid input</v>
@@ -17307,13 +17307,13 @@
         <v>Enter valid input on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L319">
-        <v>2819</v>
+        <v>1975</v>
       </c>
       <c r="M319" t="str">
         <v>Yes</v>
       </c>
       <c r="N319" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O319" t="str">
         <v>#help_&amp;_support_element_318</v>
@@ -17336,7 +17336,7 @@
         <v>Low</v>
       </c>
       <c r="E320" t="str">
-        <v>Chrome</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F320" t="str">
         <v>Enter invalid input</v>
@@ -17360,13 +17360,13 @@
         <v>Enter invalid input on Session Management completes successfully without errors</v>
       </c>
       <c r="L320">
-        <v>1804</v>
+        <v>1602</v>
       </c>
       <c r="M320" t="str">
         <v>Yes</v>
       </c>
       <c r="N320" t="str">
-        <v>className</v>
+        <v>id</v>
       </c>
       <c r="O320" t="str">
         <v>#session_management_element_319</v>
@@ -17413,13 +17413,13 @@
         <v>Submit form on Authentication completes successfully without errors</v>
       </c>
       <c r="L321">
-        <v>826</v>
+        <v>1844</v>
       </c>
       <c r="M321" t="str">
         <v>Yes</v>
       </c>
       <c r="N321" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O321" t="str">
         <v>#authentication_element_320</v>
@@ -17442,7 +17442,7 @@
         <v>High</v>
       </c>
       <c r="E322" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F322" t="str">
         <v>Verify error message</v>
@@ -17466,13 +17466,13 @@
         <v>Verify error message on Dashboard completes successfully without errors</v>
       </c>
       <c r="L322">
-        <v>2366</v>
+        <v>3281</v>
       </c>
       <c r="M322" t="str">
         <v>Yes</v>
       </c>
       <c r="N322" t="str">
-        <v>css</v>
+        <v>linkText</v>
       </c>
       <c r="O322" t="str">
         <v>#dashboard_element_321</v>
@@ -17495,7 +17495,7 @@
         <v>Medium</v>
       </c>
       <c r="E323" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F323" t="str">
         <v>Verify success message</v>
@@ -17519,13 +17519,13 @@
         <v>Verify success message on Inventory completes successfully without errors</v>
       </c>
       <c r="L323">
-        <v>3320</v>
+        <v>2687</v>
       </c>
       <c r="M323" t="str">
         <v>Yes</v>
       </c>
       <c r="N323" t="str">
-        <v>tagName</v>
+        <v>css</v>
       </c>
       <c r="O323" t="str">
         <v>#inventory_element_322</v>
@@ -17548,7 +17548,7 @@
         <v>Low</v>
       </c>
       <c r="E324" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F324" t="str">
         <v>Verify redirect</v>
@@ -17572,13 +17572,13 @@
         <v>Verify redirect on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L324">
-        <v>782</v>
+        <v>813</v>
       </c>
       <c r="M324" t="str">
         <v>Yes</v>
       </c>
       <c r="N324" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O324" t="str">
         <v>#barcode_scanner_element_323</v>
@@ -17601,7 +17601,7 @@
         <v>Critical</v>
       </c>
       <c r="E325" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F325" t="str">
         <v>Verify element visible</v>
@@ -17625,13 +17625,13 @@
         <v>Verify element visible on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L325">
-        <v>3400</v>
+        <v>1067</v>
       </c>
       <c r="M325" t="str">
         <v>Yes</v>
       </c>
       <c r="N325" t="str">
-        <v>id</v>
+        <v>name</v>
       </c>
       <c r="O325" t="str">
         <v>#recipe_suggestions_element_324</v>
@@ -17654,7 +17654,7 @@
         <v>High</v>
       </c>
       <c r="E326" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F326" t="str">
         <v>Verify element hidden</v>
@@ -17678,13 +17678,13 @@
         <v>Verify element hidden on Family Sync completes successfully without errors</v>
       </c>
       <c r="L326">
-        <v>1614</v>
+        <v>671</v>
       </c>
       <c r="M326" t="str">
         <v>Yes</v>
       </c>
       <c r="N326" t="str">
-        <v>className</v>
+        <v>name</v>
       </c>
       <c r="O326" t="str">
         <v>#family_sync_element_325</v>
@@ -17707,7 +17707,7 @@
         <v>Medium</v>
       </c>
       <c r="E327" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F327" t="str">
         <v>Verify element disabled</v>
@@ -17731,7 +17731,7 @@
         <v>Verify element disabled on Shopping List completes successfully without errors</v>
       </c>
       <c r="L327">
-        <v>923</v>
+        <v>377</v>
       </c>
       <c r="M327" t="str">
         <v>Yes</v>
@@ -17760,7 +17760,7 @@
         <v>Low</v>
       </c>
       <c r="E328" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F328" t="str">
         <v>Verify element enabled</v>
@@ -17784,16 +17784,16 @@
         <v>Verify element enabled on User Profile completes successfully without errors</v>
       </c>
       <c r="L328">
-        <v>2317</v>
+        <v>469</v>
       </c>
       <c r="M328" t="str">
         <v>Yes</v>
       </c>
       <c r="N328" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O328" t="str">
-        <v>#user_profile_element_327</v>
+        <v>//div[@id='user_profile_327']</v>
       </c>
       <c r="P328" t="str">
         <v>Pass</v>
@@ -17813,7 +17813,7 @@
         <v>Critical</v>
       </c>
       <c r="E329" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F329" t="str">
         <v>Hover over element</v>
@@ -17837,13 +17837,13 @@
         <v>Hover over element on Settings completes successfully without errors</v>
       </c>
       <c r="L329">
-        <v>726</v>
+        <v>1323</v>
       </c>
       <c r="M329" t="str">
         <v>Yes</v>
       </c>
       <c r="N329" t="str">
-        <v>name</v>
+        <v>className</v>
       </c>
       <c r="O329" t="str">
         <v>#settings_element_328</v>
@@ -17866,7 +17866,7 @@
         <v>High</v>
       </c>
       <c r="E330" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F330" t="str">
         <v>Click dropdown</v>
@@ -17890,13 +17890,13 @@
         <v>Click dropdown on Notifications completes successfully without errors</v>
       </c>
       <c r="L330">
-        <v>2813</v>
+        <v>861</v>
       </c>
       <c r="M330" t="str">
         <v>Yes</v>
       </c>
       <c r="N330" t="str">
-        <v>tagName</v>
+        <v>linkText</v>
       </c>
       <c r="O330" t="str">
         <v>#notifications_element_329</v>
@@ -17919,7 +17919,7 @@
         <v>Medium</v>
       </c>
       <c r="E331" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F331" t="str">
         <v>Select option from dropdown</v>
@@ -17943,13 +17943,13 @@
         <v>Select option from dropdown on Search completes successfully without errors</v>
       </c>
       <c r="L331">
-        <v>409</v>
+        <v>3520</v>
       </c>
       <c r="M331" t="str">
         <v>Yes</v>
       </c>
       <c r="N331" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O331" t="str">
         <v>#search_element_330</v>
@@ -17972,7 +17972,7 @@
         <v>Low</v>
       </c>
       <c r="E332" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F332" t="str">
         <v>Verify dropdown options</v>
@@ -17996,7 +17996,7 @@
         <v>Verify dropdown options on Reports completes successfully without errors</v>
       </c>
       <c r="L332">
-        <v>3311</v>
+        <v>504</v>
       </c>
       <c r="M332" t="str">
         <v>Yes</v>
@@ -18025,7 +18025,7 @@
         <v>Critical</v>
       </c>
       <c r="E333" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F333" t="str">
         <v>Scroll to element</v>
@@ -18049,7 +18049,7 @@
         <v>Scroll to element on Analytics completes successfully without errors</v>
       </c>
       <c r="L333">
-        <v>1281</v>
+        <v>3531</v>
       </c>
       <c r="M333" t="str">
         <v>Yes</v>
@@ -18078,7 +18078,7 @@
         <v>High</v>
       </c>
       <c r="E334" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F334" t="str">
         <v>Take screenshot</v>
@@ -18102,13 +18102,13 @@
         <v>Take screenshot on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L334">
-        <v>3761</v>
+        <v>2758</v>
       </c>
       <c r="M334" t="str">
         <v>Yes</v>
       </c>
       <c r="N334" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O334" t="str">
         <v>#storage_locations_element_333</v>
@@ -18131,7 +18131,7 @@
         <v>Medium</v>
       </c>
       <c r="E335" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F335" t="str">
         <v>Verify URL</v>
@@ -18155,13 +18155,13 @@
         <v>Verify URL on Categories completes successfully without errors</v>
       </c>
       <c r="L335">
-        <v>700</v>
+        <v>2255</v>
       </c>
       <c r="M335" t="str">
         <v>Yes</v>
       </c>
       <c r="N335" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O335" t="str">
         <v>#categories_element_334</v>
@@ -18184,7 +18184,7 @@
         <v>Low</v>
       </c>
       <c r="E336" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F336" t="str">
         <v>Verify breadcrumb</v>
@@ -18208,16 +18208,16 @@
         <v>Verify breadcrumb on Export completes successfully without errors</v>
       </c>
       <c r="L336">
-        <v>1967</v>
+        <v>445</v>
       </c>
       <c r="M336" t="str">
         <v>Yes</v>
       </c>
       <c r="N336" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O336" t="str">
-        <v>//div[@id='export_335']</v>
+        <v>#export_element_335</v>
       </c>
       <c r="P336" t="str">
         <v>Pass</v>
@@ -18237,7 +18237,7 @@
         <v>Critical</v>
       </c>
       <c r="E337" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F337" t="str">
         <v>Verify table data</v>
@@ -18261,16 +18261,16 @@
         <v>Verify table data on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L337">
-        <v>2111</v>
+        <v>1652</v>
       </c>
       <c r="M337" t="str">
         <v>Yes</v>
       </c>
       <c r="N337" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O337" t="str">
-        <v>#admin_panel_element_336</v>
+        <v>//div[@id='admin_panel_336']</v>
       </c>
       <c r="P337" t="str">
         <v>Pass</v>
@@ -18290,7 +18290,7 @@
         <v>High</v>
       </c>
       <c r="E338" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F338" t="str">
         <v>Sort table column</v>
@@ -18314,16 +18314,16 @@
         <v>Sort table column on Onboarding completes successfully without errors</v>
       </c>
       <c r="L338">
-        <v>3056</v>
+        <v>3886</v>
       </c>
       <c r="M338" t="str">
         <v>Yes</v>
       </c>
       <c r="N338" t="str">
-        <v>className</v>
+        <v>xpath</v>
       </c>
       <c r="O338" t="str">
-        <v>#onboarding_element_337</v>
+        <v>//div[@id='onboarding_337']</v>
       </c>
       <c r="P338" t="str">
         <v>Pass</v>
@@ -18343,7 +18343,7 @@
         <v>Medium</v>
       </c>
       <c r="E339" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F339" t="str">
         <v>Filter table</v>
@@ -18367,13 +18367,13 @@
         <v>Filter table on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L339">
-        <v>3340</v>
+        <v>2584</v>
       </c>
       <c r="M339" t="str">
         <v>Yes</v>
       </c>
       <c r="N339" t="str">
-        <v>className</v>
+        <v>css</v>
       </c>
       <c r="O339" t="str">
         <v>#help_&amp;_support_element_338</v>
@@ -18420,13 +18420,13 @@
         <v>Verify pagination on Session Management completes successfully without errors</v>
       </c>
       <c r="L340">
-        <v>1236</v>
+        <v>1424</v>
       </c>
       <c r="M340" t="str">
         <v>Yes</v>
       </c>
       <c r="N340" t="str">
-        <v>linkText</v>
+        <v>className</v>
       </c>
       <c r="O340" t="str">
         <v>#session_management_element_339</v>
@@ -18449,7 +18449,7 @@
         <v>Critical</v>
       </c>
       <c r="E341" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F341" t="str">
         <v>Click pagination next</v>
@@ -18473,13 +18473,13 @@
         <v>Click pagination next on Authentication completes successfully without errors</v>
       </c>
       <c r="L341">
-        <v>2441</v>
+        <v>3289</v>
       </c>
       <c r="M341" t="str">
         <v>Yes</v>
       </c>
       <c r="N341" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O341" t="str">
         <v>#authentication_element_340</v>
@@ -18502,7 +18502,7 @@
         <v>High</v>
       </c>
       <c r="E342" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F342" t="str">
         <v>Click pagination prev</v>
@@ -18526,13 +18526,13 @@
         <v>Click pagination prev on Dashboard completes successfully without errors</v>
       </c>
       <c r="L342">
-        <v>3195</v>
+        <v>3878</v>
       </c>
       <c r="M342" t="str">
         <v>Yes</v>
       </c>
       <c r="N342" t="str">
-        <v>tagName</v>
+        <v>id</v>
       </c>
       <c r="O342" t="str">
         <v>#dashboard_element_341</v>
@@ -18555,7 +18555,7 @@
         <v>Medium</v>
       </c>
       <c r="E343" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F343" t="str">
         <v>Verify modal opens</v>
@@ -18579,13 +18579,13 @@
         <v>Verify modal opens on Inventory completes successfully without errors</v>
       </c>
       <c r="L343">
-        <v>3025</v>
+        <v>2877</v>
       </c>
       <c r="M343" t="str">
         <v>Yes</v>
       </c>
       <c r="N343" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O343" t="str">
         <v>#inventory_element_342</v>
@@ -18608,7 +18608,7 @@
         <v>Low</v>
       </c>
       <c r="E344" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F344" t="str">
         <v>Verify modal closes</v>
@@ -18632,13 +18632,13 @@
         <v>Verify modal closes on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L344">
-        <v>3524</v>
+        <v>3694</v>
       </c>
       <c r="M344" t="str">
         <v>Yes</v>
       </c>
       <c r="N344" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O344" t="str">
         <v>#barcode_scanner_element_343</v>
@@ -18661,7 +18661,7 @@
         <v>Critical</v>
       </c>
       <c r="E345" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F345" t="str">
         <v>Verify toast notification</v>
@@ -18685,13 +18685,13 @@
         <v>Verify toast notification on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L345">
-        <v>595</v>
+        <v>1599</v>
       </c>
       <c r="M345" t="str">
         <v>Yes</v>
       </c>
       <c r="N345" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O345" t="str">
         <v>#recipe_suggestions_element_344</v>
@@ -18714,7 +18714,7 @@
         <v>High</v>
       </c>
       <c r="E346" t="str">
-        <v>Firefox</v>
+        <v>Chrome</v>
       </c>
       <c r="F346" t="str">
         <v>Verify alert dialog</v>
@@ -18738,16 +18738,16 @@
         <v>Verify alert dialog on Family Sync completes successfully without errors</v>
       </c>
       <c r="L346">
-        <v>2530</v>
+        <v>1603</v>
       </c>
       <c r="M346" t="str">
         <v>Yes</v>
       </c>
       <c r="N346" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O346" t="str">
-        <v>#family_sync_element_345</v>
+        <v>//div[@id='family_sync_345']</v>
       </c>
       <c r="P346" t="str">
         <v>Pass</v>
@@ -18767,7 +18767,7 @@
         <v>Medium</v>
       </c>
       <c r="E347" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F347" t="str">
         <v>Accept alert</v>
@@ -18791,16 +18791,16 @@
         <v>Accept alert on Shopping List completes successfully without errors</v>
       </c>
       <c r="L347">
-        <v>2257</v>
+        <v>2798</v>
       </c>
       <c r="M347" t="str">
         <v>Yes</v>
       </c>
       <c r="N347" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O347" t="str">
-        <v>#shopping_list_element_346</v>
+        <v>//div[@id='shopping_list_346']</v>
       </c>
       <c r="P347" t="str">
         <v>Pass</v>
@@ -18820,7 +18820,7 @@
         <v>Low</v>
       </c>
       <c r="E348" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F348" t="str">
         <v>Dismiss alert</v>
@@ -18844,13 +18844,13 @@
         <v>Dismiss alert on User Profile completes successfully without errors</v>
       </c>
       <c r="L348">
-        <v>2272</v>
+        <v>1290</v>
       </c>
       <c r="M348" t="str">
         <v>Yes</v>
       </c>
       <c r="N348" t="str">
-        <v>className</v>
+        <v>css</v>
       </c>
       <c r="O348" t="str">
         <v>#user_profile_element_347</v>
@@ -18873,7 +18873,7 @@
         <v>Critical</v>
       </c>
       <c r="E349" t="str">
-        <v>Chrome</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F349" t="str">
         <v>Verify placeholder text</v>
@@ -18897,13 +18897,13 @@
         <v>Verify placeholder text on Settings completes successfully without errors</v>
       </c>
       <c r="L349">
-        <v>3800</v>
+        <v>3241</v>
       </c>
       <c r="M349" t="str">
         <v>Yes</v>
       </c>
       <c r="N349" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O349" t="str">
         <v>#settings_element_348</v>
@@ -18926,7 +18926,7 @@
         <v>High</v>
       </c>
       <c r="E350" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F350" t="str">
         <v>Clear input field</v>
@@ -18950,13 +18950,13 @@
         <v>Clear input field on Notifications completes successfully without errors</v>
       </c>
       <c r="L350">
-        <v>2216</v>
+        <v>1811</v>
       </c>
       <c r="M350" t="str">
         <v>Yes</v>
       </c>
       <c r="N350" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O350" t="str">
         <v>#notifications_element_349</v>
@@ -18979,7 +18979,7 @@
         <v>Medium</v>
       </c>
       <c r="E351" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F351" t="str">
         <v>Tab through fields</v>
@@ -19003,16 +19003,16 @@
         <v>Tab through fields on Search completes successfully without errors</v>
       </c>
       <c r="L351">
-        <v>747</v>
+        <v>2953</v>
       </c>
       <c r="M351" t="str">
         <v>Yes</v>
       </c>
       <c r="N351" t="str">
-        <v>name</v>
+        <v>xpath</v>
       </c>
       <c r="O351" t="str">
-        <v>#search_element_350</v>
+        <v>//div[@id='search_350']</v>
       </c>
       <c r="P351" t="str">
         <v>Pass</v>
@@ -19056,13 +19056,13 @@
         <v>Verify field validation on Reports completes successfully without errors</v>
       </c>
       <c r="L352">
-        <v>1329</v>
+        <v>418</v>
       </c>
       <c r="M352" t="str">
         <v>Yes</v>
       </c>
       <c r="N352" t="str">
-        <v>name</v>
+        <v>id</v>
       </c>
       <c r="O352" t="str">
         <v>#reports_element_351</v>
@@ -19085,7 +19085,7 @@
         <v>Critical</v>
       </c>
       <c r="E353" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F353" t="str">
         <v>Upload file</v>
@@ -19109,16 +19109,16 @@
         <v>Upload file on Analytics completes successfully without errors</v>
       </c>
       <c r="L353">
-        <v>693</v>
+        <v>483</v>
       </c>
       <c r="M353" t="str">
         <v>Yes</v>
       </c>
       <c r="N353" t="str">
-        <v>id</v>
+        <v>xpath</v>
       </c>
       <c r="O353" t="str">
-        <v>#analytics_element_352</v>
+        <v>//div[@id='analytics_352']</v>
       </c>
       <c r="P353" t="str">
         <v>Pass</v>
@@ -19138,7 +19138,7 @@
         <v>High</v>
       </c>
       <c r="E354" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F354" t="str">
         <v>Verify file upload success</v>
@@ -19162,13 +19162,13 @@
         <v>Verify file upload success on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L354">
-        <v>227</v>
+        <v>3572</v>
       </c>
       <c r="M354" t="str">
         <v>Yes</v>
       </c>
       <c r="N354" t="str">
-        <v>id</v>
+        <v>css</v>
       </c>
       <c r="O354" t="str">
         <v>#storage_locations_element_353</v>
@@ -19191,7 +19191,7 @@
         <v>Medium</v>
       </c>
       <c r="E355" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F355" t="str">
         <v>Download file</v>
@@ -19215,13 +19215,13 @@
         <v>Download file on Categories completes successfully without errors</v>
       </c>
       <c r="L355">
-        <v>2020</v>
+        <v>3965</v>
       </c>
       <c r="M355" t="str">
         <v>Yes</v>
       </c>
       <c r="N355" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O355" t="str">
         <v>#categories_element_354</v>
@@ -19244,7 +19244,7 @@
         <v>Low</v>
       </c>
       <c r="E356" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F356" t="str">
         <v>Verify download</v>
@@ -19268,16 +19268,16 @@
         <v>Verify download on Export completes successfully without errors</v>
       </c>
       <c r="L356">
-        <v>3360</v>
+        <v>2959</v>
       </c>
       <c r="M356" t="str">
         <v>Yes</v>
       </c>
       <c r="N356" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O356" t="str">
-        <v>//div[@id='export_355']</v>
+        <v>#export_element_355</v>
       </c>
       <c r="P356" t="str">
         <v>Pass</v>
@@ -19321,7 +19321,7 @@
         <v>Resize window to mobile on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L357">
-        <v>2278</v>
+        <v>3720</v>
       </c>
       <c r="M357" t="str">
         <v>Yes</v>
@@ -19350,7 +19350,7 @@
         <v>High</v>
       </c>
       <c r="E358" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F358" t="str">
         <v>Resize window to tablet</v>
@@ -19374,13 +19374,13 @@
         <v>Resize window to tablet on Onboarding completes successfully without errors</v>
       </c>
       <c r="L358">
-        <v>3374</v>
+        <v>1200</v>
       </c>
       <c r="M358" t="str">
         <v>Yes</v>
       </c>
       <c r="N358" t="str">
-        <v>id</v>
+        <v>linkText</v>
       </c>
       <c r="O358" t="str">
         <v>#onboarding_element_357</v>
@@ -19403,7 +19403,7 @@
         <v>Medium</v>
       </c>
       <c r="E359" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F359" t="str">
         <v>Resize window to desktop</v>
@@ -19427,16 +19427,16 @@
         <v>Resize window to desktop on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L359">
-        <v>2850</v>
+        <v>3603</v>
       </c>
       <c r="M359" t="str">
         <v>Yes</v>
       </c>
       <c r="N359" t="str">
-        <v>xpath</v>
+        <v>id</v>
       </c>
       <c r="O359" t="str">
-        <v>//div[@id='help_&amp;_support_358']</v>
+        <v>#help_&amp;_support_element_358</v>
       </c>
       <c r="P359" t="str">
         <v>Pass</v>
@@ -19456,7 +19456,7 @@
         <v>Low</v>
       </c>
       <c r="E360" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F360" t="str">
         <v>Verify responsive layout</v>
@@ -19480,13 +19480,13 @@
         <v>Verify responsive layout on Session Management completes successfully without errors</v>
       </c>
       <c r="L360">
-        <v>3063</v>
+        <v>234</v>
       </c>
       <c r="M360" t="str">
         <v>Yes</v>
       </c>
       <c r="N360" t="str">
-        <v>css</v>
+        <v>id</v>
       </c>
       <c r="O360" t="str">
         <v>#session_management_element_359</v>
@@ -19509,7 +19509,7 @@
         <v>Critical</v>
       </c>
       <c r="E361" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F361" t="str">
         <v>Keyboard navigation</v>
@@ -19533,13 +19533,13 @@
         <v>Keyboard navigation on Authentication completes successfully without errors</v>
       </c>
       <c r="L361">
-        <v>2725</v>
+        <v>3786</v>
       </c>
       <c r="M361" t="str">
         <v>Yes</v>
       </c>
       <c r="N361" t="str">
-        <v>tagName</v>
+        <v>linkText</v>
       </c>
       <c r="O361" t="str">
         <v>#authentication_element_360</v>
@@ -19562,7 +19562,7 @@
         <v>High</v>
       </c>
       <c r="E362" t="str">
-        <v>Chrome</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F362" t="str">
         <v>Verify focus state</v>
@@ -19586,13 +19586,13 @@
         <v>Verify focus state on Dashboard completes successfully without errors</v>
       </c>
       <c r="L362">
-        <v>1280</v>
+        <v>2234</v>
       </c>
       <c r="M362" t="str">
         <v>Yes</v>
       </c>
       <c r="N362" t="str">
-        <v>linkText</v>
+        <v>id</v>
       </c>
       <c r="O362" t="str">
         <v>#dashboard_element_361</v>
@@ -19639,13 +19639,13 @@
         <v>Verify hover state on Inventory completes successfully without errors</v>
       </c>
       <c r="L363">
-        <v>2484</v>
+        <v>983</v>
       </c>
       <c r="M363" t="str">
         <v>Yes</v>
       </c>
       <c r="N363" t="str">
-        <v>css</v>
+        <v>tagName</v>
       </c>
       <c r="O363" t="str">
         <v>#inventory_element_362</v>
@@ -19668,7 +19668,7 @@
         <v>Low</v>
       </c>
       <c r="E364" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F364" t="str">
         <v>Verify active state</v>
@@ -19692,16 +19692,16 @@
         <v>Verify active state on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L364">
-        <v>624</v>
+        <v>2465</v>
       </c>
       <c r="M364" t="str">
         <v>Yes</v>
       </c>
       <c r="N364" t="str">
-        <v>css</v>
+        <v>xpath</v>
       </c>
       <c r="O364" t="str">
-        <v>#barcode_scanner_element_363</v>
+        <v>//div[@id='barcode_scanner_363']</v>
       </c>
       <c r="P364" t="str">
         <v>Pass</v>
@@ -19721,7 +19721,7 @@
         <v>Critical</v>
       </c>
       <c r="E365" t="str">
-        <v>Firefox</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F365" t="str">
         <v>Verify disabled state</v>
@@ -19745,13 +19745,13 @@
         <v>Verify disabled state on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L365">
-        <v>2226</v>
+        <v>331</v>
       </c>
       <c r="M365" t="str">
         <v>Yes</v>
       </c>
       <c r="N365" t="str">
-        <v>id</v>
+        <v>className</v>
       </c>
       <c r="O365" t="str">
         <v>#recipe_suggestions_element_364</v>
@@ -19774,7 +19774,7 @@
         <v>High</v>
       </c>
       <c r="E366" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F366" t="str">
         <v>Verify loading spinner</v>
@@ -19798,13 +19798,13 @@
         <v>Verify loading spinner on Family Sync completes successfully without errors</v>
       </c>
       <c r="L366">
-        <v>481</v>
+        <v>2826</v>
       </c>
       <c r="M366" t="str">
         <v>Yes</v>
       </c>
       <c r="N366" t="str">
-        <v>tagName</v>
+        <v>name</v>
       </c>
       <c r="O366" t="str">
         <v>#family_sync_element_365</v>
@@ -19851,13 +19851,13 @@
         <v>Verify skeleton loader on Shopping List completes successfully without errors</v>
       </c>
       <c r="L367">
-        <v>916</v>
+        <v>3547</v>
       </c>
       <c r="M367" t="str">
         <v>Yes</v>
       </c>
       <c r="N367" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O367" t="str">
         <v>#shopping_list_element_366</v>
@@ -19880,7 +19880,7 @@
         <v>Low</v>
       </c>
       <c r="E368" t="str">
-        <v>Edge</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F368" t="str">
         <v>Verify empty state</v>
@@ -19904,16 +19904,16 @@
         <v>Verify empty state on User Profile completes successfully without errors</v>
       </c>
       <c r="L368">
-        <v>709</v>
+        <v>2572</v>
       </c>
       <c r="M368" t="str">
         <v>Yes</v>
       </c>
       <c r="N368" t="str">
-        <v>xpath</v>
+        <v>tagName</v>
       </c>
       <c r="O368" t="str">
-        <v>//div[@id='user_profile_367']</v>
+        <v>#user_profile_element_367</v>
       </c>
       <c r="P368" t="str">
         <v>Pass</v>
@@ -19933,7 +19933,7 @@
         <v>Critical</v>
       </c>
       <c r="E369" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F369" t="str">
         <v>Verify error state</v>
@@ -19957,16 +19957,16 @@
         <v>Verify error state on Settings completes successfully without errors</v>
       </c>
       <c r="L369">
-        <v>3792</v>
+        <v>1038</v>
       </c>
       <c r="M369" t="str">
         <v>Yes</v>
       </c>
       <c r="N369" t="str">
-        <v>linkText</v>
+        <v>xpath</v>
       </c>
       <c r="O369" t="str">
-        <v>#settings_element_368</v>
+        <v>//div[@id='settings_368']</v>
       </c>
       <c r="P369" t="str">
         <v>Pass</v>
@@ -19986,7 +19986,7 @@
         <v>High</v>
       </c>
       <c r="E370" t="str">
-        <v>Edge</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F370" t="str">
         <v>Verify 404 page</v>
@@ -20010,13 +20010,13 @@
         <v>Verify 404 page on Notifications completes successfully without errors</v>
       </c>
       <c r="L370">
-        <v>2680</v>
+        <v>243</v>
       </c>
       <c r="M370" t="str">
         <v>Yes</v>
       </c>
       <c r="N370" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O370" t="str">
         <v>#notifications_element_369</v>
@@ -20039,7 +20039,7 @@
         <v>Medium</v>
       </c>
       <c r="E371" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F371" t="str">
         <v>Verify back navigation</v>
@@ -20063,13 +20063,13 @@
         <v>Verify back navigation on Search completes successfully without errors</v>
       </c>
       <c r="L371">
-        <v>1814</v>
+        <v>986</v>
       </c>
       <c r="M371" t="str">
         <v>Yes</v>
       </c>
       <c r="N371" t="str">
-        <v>name</v>
+        <v>linkText</v>
       </c>
       <c r="O371" t="str">
         <v>#search_element_370</v>
@@ -20092,7 +20092,7 @@
         <v>Low</v>
       </c>
       <c r="E372" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F372" t="str">
         <v>Verify forward navigation</v>
@@ -20116,13 +20116,13 @@
         <v>Verify forward navigation on Reports completes successfully without errors</v>
       </c>
       <c r="L372">
-        <v>818</v>
+        <v>2518</v>
       </c>
       <c r="M372" t="str">
         <v>Yes</v>
       </c>
       <c r="N372" t="str">
-        <v>css</v>
+        <v>className</v>
       </c>
       <c r="O372" t="str">
         <v>#reports_element_371</v>
@@ -20145,7 +20145,7 @@
         <v>Critical</v>
       </c>
       <c r="E373" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F373" t="str">
         <v>Refresh page</v>
@@ -20169,13 +20169,13 @@
         <v>Refresh page on Analytics completes successfully without errors</v>
       </c>
       <c r="L373">
-        <v>2155</v>
+        <v>210</v>
       </c>
       <c r="M373" t="str">
         <v>Yes</v>
       </c>
       <c r="N373" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O373" t="str">
         <v>#analytics_element_372</v>
@@ -20198,7 +20198,7 @@
         <v>High</v>
       </c>
       <c r="E374" t="str">
-        <v>Edge</v>
+        <v>Chrome</v>
       </c>
       <c r="F374" t="str">
         <v>Verify session persistence</v>
@@ -20222,13 +20222,13 @@
         <v>Verify session persistence on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L374">
-        <v>3314</v>
+        <v>1077</v>
       </c>
       <c r="M374" t="str">
         <v>Yes</v>
       </c>
       <c r="N374" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O374" t="str">
         <v>#storage_locations_element_373</v>
@@ -20251,7 +20251,7 @@
         <v>Medium</v>
       </c>
       <c r="E375" t="str">
-        <v>Firefox Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F375" t="str">
         <v>Verify logout clears session</v>
@@ -20275,13 +20275,13 @@
         <v>Verify logout clears session on Categories completes successfully without errors</v>
       </c>
       <c r="L375">
-        <v>804</v>
+        <v>384</v>
       </c>
       <c r="M375" t="str">
         <v>Yes</v>
       </c>
       <c r="N375" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O375" t="str">
         <v>#categories_element_374</v>
@@ -20304,7 +20304,7 @@
         <v>Low</v>
       </c>
       <c r="E376" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F376" t="str">
         <v>Verify remember me</v>
@@ -20328,16 +20328,16 @@
         <v>Verify remember me on Export completes successfully without errors</v>
       </c>
       <c r="L376">
-        <v>3115</v>
+        <v>3129</v>
       </c>
       <c r="M376" t="str">
         <v>Yes</v>
       </c>
       <c r="N376" t="str">
-        <v>xpath</v>
+        <v>className</v>
       </c>
       <c r="O376" t="str">
-        <v>//div[@id='export_375']</v>
+        <v>#export_element_375</v>
       </c>
       <c r="P376" t="str">
         <v>Pass</v>
@@ -20357,7 +20357,7 @@
         <v>Critical</v>
       </c>
       <c r="E377" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F377" t="str">
         <v>Verify auto-logout</v>
@@ -20381,7 +20381,7 @@
         <v>Verify auto-logout on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L377">
-        <v>2000</v>
+        <v>428</v>
       </c>
       <c r="M377" t="str">
         <v>Yes</v>
@@ -20410,7 +20410,7 @@
         <v>High</v>
       </c>
       <c r="E378" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F378" t="str">
         <v>Verify concurrent session</v>
@@ -20434,16 +20434,16 @@
         <v>Verify concurrent session on Onboarding completes successfully without errors</v>
       </c>
       <c r="L378">
-        <v>2394</v>
+        <v>3617</v>
       </c>
       <c r="M378" t="str">
         <v>Yes</v>
       </c>
       <c r="N378" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O378" t="str">
-        <v>//div[@id='onboarding_377']</v>
+        <v>#onboarding_element_377</v>
       </c>
       <c r="P378" t="str">
         <v>Pass</v>
@@ -20463,7 +20463,7 @@
         <v>Medium</v>
       </c>
       <c r="E379" t="str">
-        <v>Chrome</v>
+        <v>Firefox</v>
       </c>
       <c r="F379" t="str">
         <v>Verify page title</v>
@@ -20487,16 +20487,16 @@
         <v>Verify page title on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L379">
-        <v>785</v>
+        <v>3244</v>
       </c>
       <c r="M379" t="str">
         <v>Yes</v>
       </c>
       <c r="N379" t="str">
-        <v>xpath</v>
+        <v>tagName</v>
       </c>
       <c r="O379" t="str">
-        <v>//div[@id='help_&amp;_support_378']</v>
+        <v>#help_&amp;_support_element_378</v>
       </c>
       <c r="P379" t="str">
         <v>Pass</v>
@@ -20516,7 +20516,7 @@
         <v>Low</v>
       </c>
       <c r="E380" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F380" t="str">
         <v>Verify page loads</v>
@@ -20540,13 +20540,13 @@
         <v>Verify page loads on Session Management completes successfully without errors</v>
       </c>
       <c r="L380">
-        <v>2763</v>
+        <v>593</v>
       </c>
       <c r="M380" t="str">
         <v>Yes</v>
       </c>
       <c r="N380" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O380" t="str">
         <v>#session_management_element_379</v>
@@ -20569,7 +20569,7 @@
         <v>Critical</v>
       </c>
       <c r="E381" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F381" t="str">
         <v>Click button</v>
@@ -20593,7 +20593,7 @@
         <v>Click button on Authentication completes successfully without errors</v>
       </c>
       <c r="L381">
-        <v>1539</v>
+        <v>2994</v>
       </c>
       <c r="M381" t="str">
         <v>Yes</v>
@@ -20622,7 +20622,7 @@
         <v>High</v>
       </c>
       <c r="E382" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F382" t="str">
         <v>Enter valid input</v>
@@ -20646,13 +20646,13 @@
         <v>Enter valid input on Dashboard completes successfully without errors</v>
       </c>
       <c r="L382">
-        <v>1278</v>
+        <v>1905</v>
       </c>
       <c r="M382" t="str">
         <v>Yes</v>
       </c>
       <c r="N382" t="str">
-        <v>className</v>
+        <v>name</v>
       </c>
       <c r="O382" t="str">
         <v>#dashboard_element_381</v>
@@ -20675,7 +20675,7 @@
         <v>Medium</v>
       </c>
       <c r="E383" t="str">
-        <v>Chrome Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F383" t="str">
         <v>Enter invalid input</v>
@@ -20699,13 +20699,13 @@
         <v>Enter invalid input on Inventory completes successfully without errors</v>
       </c>
       <c r="L383">
-        <v>4000</v>
+        <v>784</v>
       </c>
       <c r="M383" t="str">
         <v>Yes</v>
       </c>
       <c r="N383" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O383" t="str">
         <v>#inventory_element_382</v>
@@ -20752,16 +20752,16 @@
         <v>Submit form on Barcode Scanner completes successfully without errors</v>
       </c>
       <c r="L384">
-        <v>2331</v>
+        <v>583</v>
       </c>
       <c r="M384" t="str">
         <v>Yes</v>
       </c>
       <c r="N384" t="str">
-        <v>xpath</v>
+        <v>css</v>
       </c>
       <c r="O384" t="str">
-        <v>//div[@id='barcode_scanner_383']</v>
+        <v>#barcode_scanner_element_383</v>
       </c>
       <c r="P384" t="str">
         <v>Pass</v>
@@ -20805,13 +20805,13 @@
         <v>Verify error message on Recipe Suggestions completes successfully without errors</v>
       </c>
       <c r="L385">
-        <v>1119</v>
+        <v>2353</v>
       </c>
       <c r="M385" t="str">
         <v>Yes</v>
       </c>
       <c r="N385" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O385" t="str">
         <v>#recipe_suggestions_element_384</v>
@@ -20834,7 +20834,7 @@
         <v>High</v>
       </c>
       <c r="E386" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F386" t="str">
         <v>Verify success message</v>
@@ -20858,13 +20858,13 @@
         <v>Verify success message on Family Sync completes successfully without errors</v>
       </c>
       <c r="L386">
-        <v>874</v>
+        <v>1464</v>
       </c>
       <c r="M386" t="str">
         <v>Yes</v>
       </c>
       <c r="N386" t="str">
-        <v>tagName</v>
+        <v>css</v>
       </c>
       <c r="O386" t="str">
         <v>#family_sync_element_385</v>
@@ -20887,7 +20887,7 @@
         <v>Medium</v>
       </c>
       <c r="E387" t="str">
-        <v>Firefox Mobile</v>
+        <v>Edge</v>
       </c>
       <c r="F387" t="str">
         <v>Verify redirect</v>
@@ -20911,13 +20911,13 @@
         <v>Verify redirect on Shopping List completes successfully without errors</v>
       </c>
       <c r="L387">
-        <v>1395</v>
+        <v>1176</v>
       </c>
       <c r="M387" t="str">
         <v>Yes</v>
       </c>
       <c r="N387" t="str">
-        <v>tagName</v>
+        <v>className</v>
       </c>
       <c r="O387" t="str">
         <v>#shopping_list_element_386</v>
@@ -20940,7 +20940,7 @@
         <v>Low</v>
       </c>
       <c r="E388" t="str">
-        <v>Firefox</v>
+        <v>Edge</v>
       </c>
       <c r="F388" t="str">
         <v>Verify element visible</v>
@@ -20964,13 +20964,13 @@
         <v>Verify element visible on User Profile completes successfully without errors</v>
       </c>
       <c r="L388">
-        <v>1818</v>
+        <v>841</v>
       </c>
       <c r="M388" t="str">
         <v>Yes</v>
       </c>
       <c r="N388" t="str">
-        <v>linkText</v>
+        <v>tagName</v>
       </c>
       <c r="O388" t="str">
         <v>#user_profile_element_387</v>
@@ -20993,7 +20993,7 @@
         <v>Critical</v>
       </c>
       <c r="E389" t="str">
-        <v>Firefox</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F389" t="str">
         <v>Verify element hidden</v>
@@ -21017,13 +21017,13 @@
         <v>Verify element hidden on Settings completes successfully without errors</v>
       </c>
       <c r="L389">
-        <v>1022</v>
+        <v>675</v>
       </c>
       <c r="M389" t="str">
         <v>Yes</v>
       </c>
       <c r="N389" t="str">
-        <v>linkText</v>
+        <v>id</v>
       </c>
       <c r="O389" t="str">
         <v>#settings_element_388</v>
@@ -21070,13 +21070,13 @@
         <v>Verify element disabled on Notifications completes successfully without errors</v>
       </c>
       <c r="L390">
-        <v>547</v>
+        <v>1026</v>
       </c>
       <c r="M390" t="str">
         <v>Yes</v>
       </c>
       <c r="N390" t="str">
-        <v>tagName</v>
+        <v>className</v>
       </c>
       <c r="O390" t="str">
         <v>#notifications_element_389</v>
@@ -21099,7 +21099,7 @@
         <v>Medium</v>
       </c>
       <c r="E391" t="str">
-        <v>Chrome Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F391" t="str">
         <v>Verify element enabled</v>
@@ -21123,13 +21123,13 @@
         <v>Verify element enabled on Search completes successfully without errors</v>
       </c>
       <c r="L391">
-        <v>2614</v>
+        <v>2048</v>
       </c>
       <c r="M391" t="str">
         <v>Yes</v>
       </c>
       <c r="N391" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O391" t="str">
         <v>#search_element_390</v>
@@ -21152,7 +21152,7 @@
         <v>Low</v>
       </c>
       <c r="E392" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F392" t="str">
         <v>Hover over element</v>
@@ -21176,7 +21176,7 @@
         <v>Hover over element on Reports completes successfully without errors</v>
       </c>
       <c r="L392">
-        <v>1935</v>
+        <v>1706</v>
       </c>
       <c r="M392" t="str">
         <v>Yes</v>
@@ -21229,16 +21229,16 @@
         <v>Click dropdown on Analytics completes successfully without errors</v>
       </c>
       <c r="L393">
-        <v>3717</v>
+        <v>2886</v>
       </c>
       <c r="M393" t="str">
         <v>Yes</v>
       </c>
       <c r="N393" t="str">
-        <v>tagName</v>
+        <v>xpath</v>
       </c>
       <c r="O393" t="str">
-        <v>#analytics_element_392</v>
+        <v>//div[@id='analytics_392']</v>
       </c>
       <c r="P393" t="str">
         <v>Pass</v>
@@ -21258,7 +21258,7 @@
         <v>High</v>
       </c>
       <c r="E394" t="str">
-        <v>Edge</v>
+        <v>Firefox</v>
       </c>
       <c r="F394" t="str">
         <v>Select option from dropdown</v>
@@ -21282,13 +21282,13 @@
         <v>Select option from dropdown on Storage Locations completes successfully without errors</v>
       </c>
       <c r="L394">
-        <v>3598</v>
+        <v>2386</v>
       </c>
       <c r="M394" t="str">
         <v>Yes</v>
       </c>
       <c r="N394" t="str">
-        <v>name</v>
+        <v>className</v>
       </c>
       <c r="O394" t="str">
         <v>#storage_locations_element_393</v>
@@ -21335,7 +21335,7 @@
         <v>Verify dropdown options on Categories completes successfully without errors</v>
       </c>
       <c r="L395">
-        <v>1154</v>
+        <v>448</v>
       </c>
       <c r="M395" t="str">
         <v>Yes</v>
@@ -21364,7 +21364,7 @@
         <v>Low</v>
       </c>
       <c r="E396" t="str">
-        <v>Chrome</v>
+        <v>Edge</v>
       </c>
       <c r="F396" t="str">
         <v>Scroll to element</v>
@@ -21388,16 +21388,16 @@
         <v>Scroll to element on Export completes successfully without errors</v>
       </c>
       <c r="L396">
-        <v>2665</v>
+        <v>2527</v>
       </c>
       <c r="M396" t="str">
         <v>Yes</v>
       </c>
       <c r="N396" t="str">
-        <v>xpath</v>
+        <v>linkText</v>
       </c>
       <c r="O396" t="str">
-        <v>//div[@id='export_395']</v>
+        <v>#export_element_395</v>
       </c>
       <c r="P396" t="str">
         <v>Pass</v>
@@ -21417,7 +21417,7 @@
         <v>Critical</v>
       </c>
       <c r="E397" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome</v>
       </c>
       <c r="F397" t="str">
         <v>Take screenshot</v>
@@ -21441,13 +21441,13 @@
         <v>Take screenshot on Admin Panel completes successfully without errors</v>
       </c>
       <c r="L397">
-        <v>1312</v>
+        <v>3906</v>
       </c>
       <c r="M397" t="str">
         <v>Yes</v>
       </c>
       <c r="N397" t="str">
-        <v>css</v>
+        <v>name</v>
       </c>
       <c r="O397" t="str">
         <v>#admin_panel_element_396</v>
@@ -21470,7 +21470,7 @@
         <v>High</v>
       </c>
       <c r="E398" t="str">
-        <v>Firefox Mobile</v>
+        <v>Chrome Mobile</v>
       </c>
       <c r="F398" t="str">
         <v>Verify URL</v>
@@ -21494,13 +21494,13 @@
         <v>Verify URL on Onboarding completes successfully without errors</v>
       </c>
       <c r="L398">
-        <v>688</v>
+        <v>507</v>
       </c>
       <c r="M398" t="str">
         <v>Yes</v>
       </c>
       <c r="N398" t="str">
-        <v>name</v>
+        <v>tagName</v>
       </c>
       <c r="O398" t="str">
         <v>#onboarding_element_397</v>
@@ -21523,7 +21523,7 @@
         <v>Medium</v>
       </c>
       <c r="E399" t="str">
-        <v>Chrome</v>
+        <v>Firefox Mobile</v>
       </c>
       <c r="F399" t="str">
         <v>Verify breadcrumb</v>
@@ -21547,13 +21547,13 @@
         <v>Verify breadcrumb on Help &amp; Support completes successfully without errors</v>
       </c>
       <c r="L399">
-        <v>2349</v>
+        <v>364</v>
       </c>
       <c r="M399" t="str">
         <v>Yes</v>
       </c>
       <c r="N399" t="str">
-        <v>id</v>
+        <v>name</v>
       </c>
       <c r="O399" t="str">
         <v>#help_&amp;_support_element_398</v>
@@ -21600,13 +21600,13 @@
         <v>Verify table data on Session Management completes successfully without errors</v>
       </c>
       <c r="L400">
-        <v>3644</v>
+        <v>541</v>
       </c>
       <c r="M400" t="str">
         <v>Yes</v>
       </c>
       <c r="N400" t="str">
-        <v>name</v>
+        <v>css</v>
       </c>
       <c r="O400" t="str">
         <v>#session_management_element_399</v>
@@ -21653,7 +21653,7 @@
         <v>Sort table column on Authentication completes successfully without errors</v>
       </c>
       <c r="L401">
-        <v>881</v>
+        <v>1108</v>
       </c>
       <c r="M401" t="str">
         <v>Yes</v>
@@ -21682,7 +21682,7 @@
         <v>High</v>
       </c>
       <c r="E402" t="str">
-        <v>Chrome Mobile</v>
+        <v>Firefox</v>
       </c>
       <c r="F402" t="str">
         <v>Filter table</v>
@@ -21706,13 +21706,13 @@
         <v>Filter table on Dashboard completes successfully without errors</v>
       </c>
       <c r="L402">
-        <v>2149</v>
+        <v>3517</v>
       </c>
       <c r="M402" t="str">
         <v>Yes</v>
       </c>
       <c r="N402" t="str">
-        <v>linkText</v>
+        <v>name</v>
       </c>
       <c r="O402" t="str">
         <v>#dashboard_element_401</v>
@@ -21757,7 +21757,7 @@
         <v>Generated On</v>
       </c>
       <c r="B3" t="str">
-        <v>26/7/2026, 12:21:14 pm</v>
+        <v>26/7/2026, 4:41:32 pm</v>
       </c>
     </row>
     <row r="4">
